--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="F14" t="n">
-        <v>5.22</v>
+        <v>5.56</v>
       </c>
       <c r="G14" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>35.95</v>
+        <v>50.07</v>
       </c>
       <c r="K14" t="n">
-        <v>34.84</v>
+        <v>-16.01</v>
       </c>
       <c r="L14" t="n">
-        <v>50.06</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:31:15</t>
+          <t>06:31:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="F15" t="n">
-        <v>4.86</v>
+        <v>5.28</v>
       </c>
       <c r="G15" t="n">
-        <v>108.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>75.73</v>
+        <v>-36.42</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.14</v>
+        <v>-39.96</v>
       </c>
       <c r="L15" t="n">
-        <v>85.25</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:32:13</t>
+          <t>06:32:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="F16" t="n">
-        <v>6.08</v>
+        <v>5.72</v>
       </c>
       <c r="G16" t="n">
-        <v>90.40000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>23.29</v>
+        <v>90.11</v>
       </c>
       <c r="K16" t="n">
-        <v>65.34999999999999</v>
+        <v>-47.84</v>
       </c>
       <c r="L16" t="n">
-        <v>69.38</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:35:40</t>
+          <t>06:36:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="F17" t="n">
-        <v>5.29</v>
+        <v>5.89</v>
       </c>
       <c r="G17" t="n">
-        <v>103.1</v>
+        <v>83.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>47.61</v>
+        <v>-54.18</v>
       </c>
       <c r="K17" t="n">
-        <v>44.77</v>
+        <v>52.33</v>
       </c>
       <c r="L17" t="n">
-        <v>65.34999999999999</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:36:39</t>
+          <t>06:37:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="F18" t="n">
-        <v>5.22</v>
+        <v>5.83</v>
       </c>
       <c r="G18" t="n">
-        <v>105.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>175.73</v>
+        <v>-28.48</v>
       </c>
       <c r="K18" t="n">
-        <v>-69.28</v>
+        <v>44.49</v>
       </c>
       <c r="L18" t="n">
-        <v>188.9</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:37:49</t>
+          <t>06:39:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="F19" t="n">
-        <v>4.78</v>
+        <v>5.51</v>
       </c>
       <c r="G19" t="n">
-        <v>104.5</v>
+        <v>100.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-53.58</v>
+        <v>-62.61</v>
       </c>
       <c r="K19" t="n">
-        <v>96.31</v>
+        <v>120.15</v>
       </c>
       <c r="L19" t="n">
-        <v>110.21</v>
+        <v>135.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:43:07</t>
+          <t>06:44:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.62</v>
+        <v>1.28</v>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>5.06</v>
       </c>
       <c r="G20" t="n">
-        <v>101.3</v>
+        <v>101.7</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.1</v>
+        <v>167.56</v>
       </c>
       <c r="K20" t="n">
-        <v>359.74</v>
+        <v>117.12</v>
       </c>
       <c r="L20" t="n">
-        <v>360.06</v>
+        <v>204.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:44:18</t>
+          <t>06:46:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="F21" t="n">
-        <v>5.34</v>
+        <v>5.43</v>
       </c>
       <c r="G21" t="n">
-        <v>90.5</v>
+        <v>104.2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>12.36</v>
+        <v>29.89</v>
       </c>
       <c r="K21" t="n">
-        <v>-269.69</v>
+        <v>-70.73</v>
       </c>
       <c r="L21" t="n">
-        <v>269.98</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:46:56</t>
+          <t>06:48:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="F22" t="n">
-        <v>5.27</v>
+        <v>5.51</v>
       </c>
       <c r="G22" t="n">
-        <v>88.5</v>
+        <v>105.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.92</v>
+        <v>207.67</v>
       </c>
       <c r="K22" t="n">
-        <v>-55.12</v>
+        <v>-108.6</v>
       </c>
       <c r="L22" t="n">
-        <v>56.61</v>
+        <v>234.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:51:35</t>
+          <t>06:52:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="F23" t="n">
-        <v>5.39</v>
+        <v>5.87</v>
       </c>
       <c r="G23" t="n">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-97.06999999999999</v>
+        <v>-59.81</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.48</v>
+        <v>24.68</v>
       </c>
       <c r="L23" t="n">
-        <v>120.55</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:52:24</t>
+          <t>06:54:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="F24" t="n">
-        <v>5.9</v>
+        <v>5.53</v>
       </c>
       <c r="G24" t="n">
-        <v>94.3</v>
+        <v>103.4</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>203.98</v>
+        <v>140.95</v>
       </c>
       <c r="K24" t="n">
-        <v>-50.65</v>
+        <v>-97.59999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>210.18</v>
+        <v>171.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:53:59</t>
+          <t>06:55:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="F25" t="n">
-        <v>5.61</v>
+        <v>5.43</v>
       </c>
       <c r="G25" t="n">
-        <v>108.8</v>
+        <v>92.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>248.69</v>
+        <v>399.65</v>
       </c>
       <c r="K25" t="n">
-        <v>141.11</v>
+        <v>356.98</v>
       </c>
       <c r="L25" t="n">
-        <v>285.93</v>
+        <v>535.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:58:05</t>
+          <t>07:00:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="F26" t="n">
-        <v>5.39</v>
+        <v>5.35</v>
       </c>
       <c r="G26" t="n">
-        <v>105.1</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-41.74</v>
+        <v>-319.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.06</v>
+        <v>56.75</v>
       </c>
       <c r="L26" t="n">
-        <v>41.94</v>
+        <v>324.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:59:47</t>
+          <t>07:02:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3</v>
+        <v>2.68</v>
       </c>
       <c r="F27" t="n">
-        <v>5.26</v>
+        <v>5.86</v>
       </c>
       <c r="G27" t="n">
-        <v>92.90000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>162.89</v>
+        <v>-23.8</v>
       </c>
       <c r="K27" t="n">
-        <v>537.6799999999999</v>
+        <v>205.72</v>
       </c>
       <c r="L27" t="n">
-        <v>561.8099999999999</v>
+        <v>207.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:01:14</t>
+          <t>07:03:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="F28" t="n">
-        <v>6.16</v>
+        <v>4.95</v>
       </c>
       <c r="G28" t="n">
-        <v>92.7</v>
+        <v>114.7</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-599.55</v>
+        <v>105.57</v>
       </c>
       <c r="K28" t="n">
-        <v>-279.34</v>
+        <v>86.61</v>
       </c>
       <c r="L28" t="n">
-        <v>661.4299999999999</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:12:29</t>
+          <t>07:16:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="F29" t="n">
-        <v>5.25</v>
+        <v>4.79</v>
       </c>
       <c r="G29" t="n">
-        <v>82.2</v>
+        <v>99.5</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>80.2</v>
+        <v>-26.79</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.42</v>
+        <v>31.08</v>
       </c>
       <c r="L29" t="n">
-        <v>83.27</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:13:21</t>
+          <t>07:17:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="F30" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="G30" t="n">
-        <v>103.8</v>
+        <v>102.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>115.26</v>
+        <v>-83.73</v>
       </c>
       <c r="K30" t="n">
-        <v>-12.6</v>
+        <v>-26.59</v>
       </c>
       <c r="L30" t="n">
-        <v>115.95</v>
+        <v>87.84999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:14:23</t>
+          <t>07:20:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F31" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="G31" t="n">
-        <v>96.09999999999999</v>
+        <v>101.8</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>24.38</v>
+        <v>81.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-152.07</v>
+        <v>-2.69</v>
       </c>
       <c r="L31" t="n">
-        <v>154.01</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:18:29</t>
+          <t>07:25:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="F32" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="G32" t="n">
-        <v>98</v>
+        <v>111.3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>12.57</v>
+        <v>43.58</v>
       </c>
       <c r="K32" t="n">
-        <v>25.29</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>28.24</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:20:18</t>
+          <t>07:26:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="F33" t="n">
-        <v>5.59</v>
+        <v>5.71</v>
       </c>
       <c r="G33" t="n">
-        <v>104.1</v>
+        <v>95.2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>91.01000000000001</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>82.27</v>
+        <v>-86.64</v>
       </c>
       <c r="L33" t="n">
-        <v>122.68</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:21:42</t>
+          <t>07:28:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="F34" t="n">
-        <v>5.3</v>
+        <v>6.37</v>
       </c>
       <c r="G34" t="n">
-        <v>87.7</v>
+        <v>96.3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>20.71</v>
+        <v>63.58</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.449999999999999</v>
+        <v>-89.14</v>
       </c>
       <c r="L34" t="n">
-        <v>22.37</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:26:23</t>
+          <t>07:32:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.33</v>
+        <v>1.27</v>
       </c>
       <c r="F35" t="n">
-        <v>4.86</v>
+        <v>6.72</v>
       </c>
       <c r="G35" t="n">
-        <v>104.2</v>
+        <v>98.3</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.91</v>
+        <v>47.08</v>
       </c>
       <c r="K35" t="n">
-        <v>-200.96</v>
+        <v>-89.52</v>
       </c>
       <c r="L35" t="n">
-        <v>219.34</v>
+        <v>101.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:28:40</t>
+          <t>07:34:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="F36" t="n">
-        <v>4.8</v>
+        <v>5.89</v>
       </c>
       <c r="G36" t="n">
-        <v>94.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>115.03</v>
+        <v>-172.53</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.6</v>
+        <v>-50.12</v>
       </c>
       <c r="L36" t="n">
-        <v>115.03</v>
+        <v>179.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:29:15</t>
+          <t>07:36:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.55</v>
+        <v>2.53</v>
       </c>
       <c r="F37" t="n">
-        <v>5.16</v>
+        <v>5.21</v>
       </c>
       <c r="G37" t="n">
-        <v>89</v>
+        <v>90.5</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>161.24</v>
+        <v>208.76</v>
       </c>
       <c r="K37" t="n">
-        <v>53.28</v>
+        <v>144.68</v>
       </c>
       <c r="L37" t="n">
-        <v>169.81</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:35:03</t>
+          <t>07:41:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="F38" t="n">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="G38" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>36.36</v>
+        <v>19.39</v>
       </c>
       <c r="K38" t="n">
-        <v>321.38</v>
+        <v>-54.69</v>
       </c>
       <c r="L38" t="n">
-        <v>323.43</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:36:57</t>
+          <t>07:43:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="F39" t="n">
-        <v>5.47</v>
+        <v>4.68</v>
       </c>
       <c r="G39" t="n">
-        <v>115.3</v>
+        <v>107.8</v>
       </c>
       <c r="H39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>151.66</v>
+        <v>-35.9</v>
       </c>
       <c r="K39" t="n">
-        <v>-221.14</v>
+        <v>27.7</v>
       </c>
       <c r="L39" t="n">
-        <v>268.15</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:37:41</t>
+          <t>07:44:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="F40" t="n">
-        <v>5.82</v>
+        <v>6.11</v>
       </c>
       <c r="G40" t="n">
-        <v>106</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>219.51</v>
+        <v>169.02</v>
       </c>
       <c r="K40" t="n">
-        <v>62.93</v>
+        <v>-209.5</v>
       </c>
       <c r="L40" t="n">
-        <v>228.36</v>
+        <v>269.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:42:47</t>
+          <t>07:49:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="F41" t="n">
-        <v>5.16</v>
+        <v>4.81</v>
       </c>
       <c r="G41" t="n">
-        <v>104.8</v>
+        <v>98.3</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-217.43</v>
+        <v>74.87</v>
       </c>
       <c r="K41" t="n">
-        <v>651.62</v>
+        <v>-147.55</v>
       </c>
       <c r="L41" t="n">
-        <v>686.9400000000001</v>
+        <v>165.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:44:59</t>
+          <t>07:51:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="F42" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="G42" t="n">
-        <v>96.8</v>
+        <v>101</v>
       </c>
       <c r="H42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-168.12</v>
+        <v>-185.59</v>
       </c>
       <c r="K42" t="n">
-        <v>506.71</v>
+        <v>217.8</v>
       </c>
       <c r="L42" t="n">
-        <v>533.87</v>
+        <v>286.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:46:52</t>
+          <t>07:53:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="F43" t="n">
-        <v>5.21</v>
+        <v>5.95</v>
       </c>
       <c r="G43" t="n">
-        <v>99.3</v>
+        <v>98.7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>14.95</v>
+        <v>-52.3</v>
       </c>
       <c r="K43" t="n">
-        <v>-90</v>
+        <v>155.67</v>
       </c>
       <c r="L43" t="n">
-        <v>91.23</v>
+        <v>164.22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:59:01</t>
+          <t>08:05:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="F44" t="n">
-        <v>5.29</v>
+        <v>6.49</v>
       </c>
       <c r="G44" t="n">
-        <v>88.40000000000001</v>
+        <v>102.7</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.43</v>
+        <v>167.17</v>
       </c>
       <c r="K44" t="n">
-        <v>-35.61</v>
+        <v>27.85</v>
       </c>
       <c r="L44" t="n">
-        <v>45.57</v>
+        <v>169.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:00:01</t>
+          <t>08:07:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="F45" t="n">
-        <v>5.07</v>
+        <v>5.22</v>
       </c>
       <c r="G45" t="n">
-        <v>112.7</v>
+        <v>92.7</v>
       </c>
       <c r="H45" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>33.93</v>
+        <v>0.12</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.25</v>
+        <v>25.3</v>
       </c>
       <c r="L45" t="n">
-        <v>40.03</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:01:14</t>
+          <t>08:09:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="F46" t="n">
-        <v>5.65</v>
+        <v>5.1</v>
       </c>
       <c r="G46" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>16.32</v>
+        <v>-92.84</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.78</v>
+        <v>-151.83</v>
       </c>
       <c r="L46" t="n">
-        <v>18.08</v>
+        <v>177.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:06:24</t>
+          <t>08:15:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="F47" t="n">
-        <v>6.12</v>
+        <v>5.49</v>
       </c>
       <c r="G47" t="n">
-        <v>99.2</v>
+        <v>112.6</v>
       </c>
       <c r="H47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-20.81</v>
+        <v>173.43</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.79000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="L47" t="n">
-        <v>77.63</v>
+        <v>190.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:07:53</t>
+          <t>08:17:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="F48" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="G48" t="n">
-        <v>99.7</v>
+        <v>102.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-47.36</v>
+        <v>-145</v>
       </c>
       <c r="K48" t="n">
-        <v>-107.31</v>
+        <v>62.99</v>
       </c>
       <c r="L48" t="n">
-        <v>117.3</v>
+        <v>158.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:08:52</t>
+          <t>08:20:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="F49" t="n">
-        <v>5.84</v>
+        <v>5.18</v>
       </c>
       <c r="G49" t="n">
-        <v>97.2</v>
+        <v>91</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>2.62</v>
+        <v>-67.33</v>
       </c>
       <c r="K49" t="n">
-        <v>42.29</v>
+        <v>-22.03</v>
       </c>
       <c r="L49" t="n">
-        <v>42.37</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:12:54</t>
+          <t>08:24:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="F50" t="n">
-        <v>5.66</v>
+        <v>5.1</v>
       </c>
       <c r="G50" t="n">
-        <v>88.09999999999999</v>
+        <v>112.9</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-71.7</v>
+        <v>-190.87</v>
       </c>
       <c r="K50" t="n">
-        <v>127.65</v>
+        <v>148.62</v>
       </c>
       <c r="L50" t="n">
-        <v>146.41</v>
+        <v>241.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:14:47</t>
+          <t>08:26:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2182,31 +2182,31 @@
         <v>1.59</v>
       </c>
       <c r="F51" t="n">
-        <v>5.51</v>
+        <v>4.97</v>
       </c>
       <c r="G51" t="n">
-        <v>110.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>157.14</v>
+        <v>-11.39</v>
       </c>
       <c r="K51" t="n">
-        <v>-120.3</v>
+        <v>308</v>
       </c>
       <c r="L51" t="n">
-        <v>197.9</v>
+        <v>308.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:17:26</t>
+          <t>08:28:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="F52" t="n">
-        <v>5.73</v>
+        <v>5.03</v>
       </c>
       <c r="G52" t="n">
-        <v>104.1</v>
+        <v>102.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>11.07</v>
+        <v>95.08</v>
       </c>
       <c r="K52" t="n">
-        <v>-29.42</v>
+        <v>199.1</v>
       </c>
       <c r="L52" t="n">
-        <v>31.43</v>
+        <v>220.64</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:20:35</t>
+          <t>08:33:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="F53" t="n">
-        <v>5.85</v>
+        <v>5.32</v>
       </c>
       <c r="G53" t="n">
-        <v>96.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>72.62</v>
+        <v>-27.38</v>
       </c>
       <c r="K53" t="n">
-        <v>110.26</v>
+        <v>220.52</v>
       </c>
       <c r="L53" t="n">
-        <v>132.03</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:21:50</t>
+          <t>08:34:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="F54" t="n">
-        <v>5.85</v>
+        <v>5.38</v>
       </c>
       <c r="G54" t="n">
-        <v>95.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="H54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>151.55</v>
+        <v>-54.99</v>
       </c>
       <c r="K54" t="n">
-        <v>68.5</v>
+        <v>-177.52</v>
       </c>
       <c r="L54" t="n">
-        <v>166.31</v>
+        <v>185.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:24:30</t>
+          <t>08:36:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="F55" t="n">
-        <v>4.93</v>
+        <v>4.79</v>
       </c>
       <c r="G55" t="n">
-        <v>90.2</v>
+        <v>101.7</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>247.56</v>
+        <v>-181.35</v>
       </c>
       <c r="K55" t="n">
-        <v>104.43</v>
+        <v>-22.25</v>
       </c>
       <c r="L55" t="n">
-        <v>268.69</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:29:11</t>
+          <t>08:40:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="F56" t="n">
-        <v>5.08</v>
+        <v>5.4</v>
       </c>
       <c r="G56" t="n">
-        <v>88.90000000000001</v>
+        <v>107.3</v>
       </c>
       <c r="H56" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-439.92</v>
+        <v>243.72</v>
       </c>
       <c r="K56" t="n">
-        <v>-54.12</v>
+        <v>225.48</v>
       </c>
       <c r="L56" t="n">
-        <v>443.24</v>
+        <v>332.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:30:40</t>
+          <t>08:43:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
         <v>4.78</v>
       </c>
       <c r="G57" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-314.61</v>
+        <v>-312.44</v>
       </c>
       <c r="K57" t="n">
-        <v>-201.29</v>
+        <v>-156.65</v>
       </c>
       <c r="L57" t="n">
-        <v>373.49</v>
+        <v>349.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:33:12</t>
+          <t>08:45:22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="F58" t="n">
-        <v>5.52</v>
+        <v>5.45</v>
       </c>
       <c r="G58" t="n">
-        <v>100.4</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>354.05</v>
+        <v>205.71</v>
       </c>
       <c r="K58" t="n">
-        <v>79.39</v>
+        <v>-240.1</v>
       </c>
       <c r="L58" t="n">
-        <v>362.84</v>
+        <v>316.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:42:25</t>
+          <t>08:54:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2518,31 +2518,31 @@
         <v>1.64</v>
       </c>
       <c r="F59" t="n">
-        <v>5.57</v>
+        <v>4.96</v>
       </c>
       <c r="G59" t="n">
-        <v>102</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.44</v>
+        <v>-22.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-34.56</v>
+        <v>43.53</v>
       </c>
       <c r="L59" t="n">
-        <v>54.73</v>
+        <v>48.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:43:26</t>
+          <t>08:55:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="F60" t="n">
-        <v>5.68</v>
+        <v>4.99</v>
       </c>
       <c r="G60" t="n">
-        <v>120.4</v>
+        <v>87.3</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>2.78</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>40.2</v>
+        <v>-63.41</v>
       </c>
       <c r="L60" t="n">
-        <v>40.3</v>
+        <v>118.25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:44:44</t>
+          <t>08:57:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="F61" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="G61" t="n">
-        <v>119.5</v>
+        <v>94</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.3</v>
+        <v>107.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.88</v>
+        <v>30.12</v>
       </c>
       <c r="L61" t="n">
-        <v>12.95</v>
+        <v>112.09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:49:22</t>
+          <t>09:02:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="F62" t="n">
-        <v>5.86</v>
+        <v>5.34</v>
       </c>
       <c r="G62" t="n">
-        <v>89.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>61.17</v>
+        <v>48.07</v>
       </c>
       <c r="K62" t="n">
-        <v>-75.23</v>
+        <v>-113.28</v>
       </c>
       <c r="L62" t="n">
-        <v>96.95999999999999</v>
+        <v>123.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:50:50</t>
+          <t>09:03:09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="F63" t="n">
-        <v>5.59</v>
+        <v>5.15</v>
       </c>
       <c r="G63" t="n">
-        <v>89.40000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="H63" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>192.1</v>
+        <v>33.16</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.77</v>
+        <v>-170.71</v>
       </c>
       <c r="L63" t="n">
-        <v>192.11</v>
+        <v>173.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:52:51</t>
+          <t>09:03:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="F64" t="n">
-        <v>5.19</v>
+        <v>6.03</v>
       </c>
       <c r="G64" t="n">
-        <v>104.9</v>
+        <v>114.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>56.85</v>
+        <v>-67.02</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.12</v>
+        <v>141.24</v>
       </c>
       <c r="L64" t="n">
-        <v>57</v>
+        <v>156.34</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:58:42</t>
+          <t>09:08:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="F65" t="n">
-        <v>5.74</v>
+        <v>5.36</v>
       </c>
       <c r="G65" t="n">
-        <v>85.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.76</v>
+        <v>-142.39</v>
       </c>
       <c r="K65" t="n">
-        <v>51.2</v>
+        <v>-36.58</v>
       </c>
       <c r="L65" t="n">
-        <v>54.88</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:00:58</t>
+          <t>09:11:40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="F66" t="n">
-        <v>4.92</v>
+        <v>4.74</v>
       </c>
       <c r="G66" t="n">
-        <v>103</v>
+        <v>99.5</v>
       </c>
       <c r="H66" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>49.06</v>
+        <v>-136.05</v>
       </c>
       <c r="K66" t="n">
-        <v>-57.94</v>
+        <v>-35.06</v>
       </c>
       <c r="L66" t="n">
-        <v>75.92</v>
+        <v>140.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:02:56</t>
+          <t>09:12:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="F67" t="n">
-        <v>4.51</v>
+        <v>5.51</v>
       </c>
       <c r="G67" t="n">
-        <v>84.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-55.4</v>
+        <v>-5.44</v>
       </c>
       <c r="K67" t="n">
-        <v>49.55</v>
+        <v>-101.47</v>
       </c>
       <c r="L67" t="n">
-        <v>74.33</v>
+        <v>101.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:07:25</t>
+          <t>09:18:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="F68" t="n">
-        <v>4.81</v>
+        <v>5.2</v>
       </c>
       <c r="G68" t="n">
-        <v>93.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-94.13</v>
+        <v>-263.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-129.92</v>
+        <v>-106.07</v>
       </c>
       <c r="L68" t="n">
-        <v>160.44</v>
+        <v>283.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:08:47</t>
+          <t>09:19:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="F69" t="n">
-        <v>5.32</v>
+        <v>5.6</v>
       </c>
       <c r="G69" t="n">
-        <v>85.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-182.94</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>147.77</v>
+        <v>-95.33</v>
       </c>
       <c r="L69" t="n">
-        <v>235.16</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:10:08</t>
+          <t>09:20:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="F70" t="n">
-        <v>4.97</v>
+        <v>5.71</v>
       </c>
       <c r="G70" t="n">
-        <v>88.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>-92.70999999999999</v>
+        <v>23.84</v>
       </c>
       <c r="K70" t="n">
-        <v>128.71</v>
+        <v>-291.79</v>
       </c>
       <c r="L70" t="n">
-        <v>158.62</v>
+        <v>292.76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:14:14</t>
+          <t>09:25:21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="F71" t="n">
-        <v>5.53</v>
+        <v>4.63</v>
       </c>
       <c r="G71" t="n">
-        <v>95.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H71" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-48.87</v>
+        <v>221.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-29.84</v>
+        <v>213.56</v>
       </c>
       <c r="L71" t="n">
-        <v>57.25</v>
+        <v>307.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:15:56</t>
+          <t>09:26:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="F72" t="n">
-        <v>4.59</v>
+        <v>5.6</v>
       </c>
       <c r="G72" t="n">
-        <v>110.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-90.39</v>
+        <v>-130.38</v>
       </c>
       <c r="K72" t="n">
-        <v>142.87</v>
+        <v>29.18</v>
       </c>
       <c r="L72" t="n">
-        <v>169.07</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:17:26</t>
+          <t>09:27:44</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="F73" t="n">
-        <v>5.4</v>
+        <v>5.16</v>
       </c>
       <c r="G73" t="n">
-        <v>89.2</v>
+        <v>93.5</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-196.72</v>
+        <v>77.64</v>
       </c>
       <c r="K73" t="n">
-        <v>-120.1</v>
+        <v>315.21</v>
       </c>
       <c r="L73" t="n">
-        <v>230.48</v>
+        <v>324.63</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:24:42</t>
+          <t>09:38:12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="F74" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="G74" t="n">
-        <v>97</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.26</v>
+        <v>-48.97</v>
       </c>
       <c r="K74" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="L74" t="n">
-        <v>23.27</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:26:37</t>
+          <t>09:40:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="F75" t="n">
-        <v>5.02</v>
+        <v>5.51</v>
       </c>
       <c r="G75" t="n">
-        <v>83.09999999999999</v>
+        <v>106</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-57.7</v>
+        <v>-66.78</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.37</v>
+        <v>68.33</v>
       </c>
       <c r="L75" t="n">
-        <v>71</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:28:02</t>
+          <t>09:41:08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="F76" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>103.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>47.88</v>
+        <v>144.51</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.27</v>
+        <v>-134.42</v>
       </c>
       <c r="L76" t="n">
-        <v>57.18</v>
+        <v>197.36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:32:50</t>
+          <t>09:46:17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="F77" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="G77" t="n">
-        <v>97.09999999999999</v>
+        <v>104.8</v>
       </c>
       <c r="H77" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-50.11</v>
+        <v>-23.47</v>
       </c>
       <c r="K77" t="n">
-        <v>16.68</v>
+        <v>111.35</v>
       </c>
       <c r="L77" t="n">
-        <v>52.81</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:33:54</t>
+          <t>09:48:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="F78" t="n">
-        <v>4.89</v>
+        <v>5.73</v>
       </c>
       <c r="G78" t="n">
-        <v>94.2</v>
+        <v>101.8</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>89.26000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K78" t="n">
-        <v>37.37</v>
+        <v>120.06</v>
       </c>
       <c r="L78" t="n">
-        <v>96.77</v>
+        <v>136.91</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:35:47</t>
+          <t>09:50:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="F79" t="n">
-        <v>4.57</v>
+        <v>5.42</v>
       </c>
       <c r="G79" t="n">
-        <v>84.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-30.87</v>
+        <v>-1.34</v>
       </c>
       <c r="K79" t="n">
-        <v>14.45</v>
+        <v>147.08</v>
       </c>
       <c r="L79" t="n">
-        <v>34.08</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:41:12</t>
+          <t>09:53:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="F80" t="n">
-        <v>5.35</v>
+        <v>4.87</v>
       </c>
       <c r="G80" t="n">
-        <v>119.3</v>
+        <v>90.3</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>21.2</v>
+        <v>72.7</v>
       </c>
       <c r="K80" t="n">
-        <v>44.25</v>
+        <v>-8.81</v>
       </c>
       <c r="L80" t="n">
-        <v>49.07</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:42:46</t>
+          <t>09:55:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="F81" t="n">
-        <v>5.63</v>
+        <v>4.91</v>
       </c>
       <c r="G81" t="n">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-128.66</v>
+        <v>62.77</v>
       </c>
       <c r="K81" t="n">
-        <v>51.64</v>
+        <v>-40.9</v>
       </c>
       <c r="L81" t="n">
-        <v>138.63</v>
+        <v>74.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:44:30</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="F82" t="n">
-        <v>5.46</v>
+        <v>5.17</v>
       </c>
       <c r="G82" t="n">
-        <v>109.4</v>
+        <v>97.7</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>210.62</v>
+        <v>-124.36</v>
       </c>
       <c r="K82" t="n">
-        <v>-89.14</v>
+        <v>-240.24</v>
       </c>
       <c r="L82" t="n">
-        <v>228.71</v>
+        <v>270.52</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:49:46</t>
+          <t>10:02:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>1.88</v>
       </c>
       <c r="F83" t="n">
-        <v>4.79</v>
+        <v>5.01</v>
       </c>
       <c r="G83" t="n">
-        <v>102.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-312.67</v>
+        <v>-68.06</v>
       </c>
       <c r="K83" t="n">
-        <v>-20.6</v>
+        <v>419.2</v>
       </c>
       <c r="L83" t="n">
-        <v>313.35</v>
+        <v>424.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:51:39</t>
+          <t>10:04:36</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="F84" t="n">
-        <v>4.99</v>
+        <v>4.75</v>
       </c>
       <c r="G84" t="n">
-        <v>100.9</v>
+        <v>107.1</v>
       </c>
       <c r="H84" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-74.55</v>
+        <v>8.92</v>
       </c>
       <c r="K84" t="n">
-        <v>-329.63</v>
+        <v>106.98</v>
       </c>
       <c r="L84" t="n">
-        <v>337.95</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:52:42</t>
+          <t>10:06:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.24</v>
+        <v>1.65</v>
       </c>
       <c r="F85" t="n">
-        <v>5.62</v>
+        <v>5.13</v>
       </c>
       <c r="G85" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>41.9</v>
+        <v>-164.11</v>
       </c>
       <c r="K85" t="n">
-        <v>-90.55</v>
+        <v>54.5</v>
       </c>
       <c r="L85" t="n">
-        <v>99.78</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:56:02</t>
+          <t>10:10:16</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="F86" t="n">
-        <v>5.76</v>
+        <v>5.27</v>
       </c>
       <c r="G86" t="n">
-        <v>79.3</v>
+        <v>108</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-90.38</v>
+        <v>-110.96</v>
       </c>
       <c r="K86" t="n">
-        <v>-295.72</v>
+        <v>179.73</v>
       </c>
       <c r="L86" t="n">
-        <v>309.22</v>
+        <v>211.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:57:10</t>
+          <t>10:11:01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="F87" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
       <c r="G87" t="n">
-        <v>103.1</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-80.81</v>
+        <v>164.43</v>
       </c>
       <c r="K87" t="n">
-        <v>163.84</v>
+        <v>-95.94</v>
       </c>
       <c r="L87" t="n">
-        <v>182.69</v>
+        <v>190.37</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:58:56</t>
+          <t>10:12:31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="F88" t="n">
-        <v>5.33</v>
+        <v>4.76</v>
       </c>
       <c r="G88" t="n">
-        <v>75.3</v>
+        <v>102</v>
       </c>
       <c r="H88" t="n">
-        <v>2.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-11.93</v>
+        <v>310.95</v>
       </c>
       <c r="K88" t="n">
-        <v>47.51</v>
+        <v>93.91</v>
       </c>
       <c r="L88" t="n">
-        <v>48.98</v>
+        <v>324.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>50.07</v>
+        <v>49.96</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.01</v>
+        <v>-15.98</v>
       </c>
       <c r="L14" t="n">
-        <v>52.57</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.42</v>
+        <v>-38.96</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.96</v>
+        <v>-42.75</v>
       </c>
       <c r="L15" t="n">
-        <v>54.06</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>90.11</v>
+        <v>78.41</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.84</v>
+        <v>-41.63</v>
       </c>
       <c r="L16" t="n">
-        <v>102.02</v>
+        <v>88.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-54.18</v>
+        <v>-56.4</v>
       </c>
       <c r="K17" t="n">
-        <v>52.33</v>
+        <v>54.49</v>
       </c>
       <c r="L17" t="n">
-        <v>75.33</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-28.48</v>
+        <v>-29.5</v>
       </c>
       <c r="K18" t="n">
-        <v>44.49</v>
+        <v>46.1</v>
       </c>
       <c r="L18" t="n">
-        <v>52.83</v>
+        <v>54.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-62.61</v>
+        <v>-53.38</v>
       </c>
       <c r="K19" t="n">
-        <v>120.15</v>
+        <v>102.43</v>
       </c>
       <c r="L19" t="n">
-        <v>135.48</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>167.56</v>
+        <v>160.61</v>
       </c>
       <c r="K20" t="n">
-        <v>117.12</v>
+        <v>112.26</v>
       </c>
       <c r="L20" t="n">
-        <v>204.44</v>
+        <v>195.96</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>29.89</v>
+        <v>40.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-70.73</v>
+        <v>-95.40000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>76.79000000000001</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>207.67</v>
+        <v>178.43</v>
       </c>
       <c r="K22" t="n">
-        <v>-108.6</v>
+        <v>-93.31</v>
       </c>
       <c r="L22" t="n">
-        <v>234.35</v>
+        <v>201.36</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-59.81</v>
+        <v>-115.91</v>
       </c>
       <c r="K23" t="n">
-        <v>24.68</v>
+        <v>47.82</v>
       </c>
       <c r="L23" t="n">
-        <v>64.7</v>
+        <v>125.38</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>140.95</v>
+        <v>169.99</v>
       </c>
       <c r="K24" t="n">
-        <v>-97.59999999999999</v>
+        <v>-117.71</v>
       </c>
       <c r="L24" t="n">
-        <v>171.44</v>
+        <v>206.76</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>399.65</v>
+        <v>349.77</v>
       </c>
       <c r="K25" t="n">
-        <v>356.98</v>
+        <v>312.42</v>
       </c>
       <c r="L25" t="n">
-        <v>535.87</v>
+        <v>468.99</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-319.65</v>
+        <v>-338.67</v>
       </c>
       <c r="K26" t="n">
-        <v>56.75</v>
+        <v>60.13</v>
       </c>
       <c r="L26" t="n">
-        <v>324.65</v>
+        <v>343.97</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-23.8</v>
+        <v>-35.02</v>
       </c>
       <c r="K27" t="n">
-        <v>205.72</v>
+        <v>302.7</v>
       </c>
       <c r="L27" t="n">
-        <v>207.09</v>
+        <v>304.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>105.57</v>
+        <v>157.89</v>
       </c>
       <c r="K28" t="n">
-        <v>86.61</v>
+        <v>129.53</v>
       </c>
       <c r="L28" t="n">
-        <v>136.55</v>
+        <v>204.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.79</v>
+        <v>-34.85</v>
       </c>
       <c r="K29" t="n">
-        <v>31.08</v>
+        <v>40.43</v>
       </c>
       <c r="L29" t="n">
-        <v>41.03</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-83.73</v>
+        <v>-62.11</v>
       </c>
       <c r="K30" t="n">
-        <v>-26.59</v>
+        <v>-19.73</v>
       </c>
       <c r="L30" t="n">
-        <v>87.84999999999999</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>81.06</v>
+        <v>63.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.69</v>
+        <v>-2.1</v>
       </c>
       <c r="L31" t="n">
-        <v>81.09999999999999</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>43.58</v>
+        <v>35.87</v>
       </c>
       <c r="K32" t="n">
-        <v>92.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>102.47</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.21</v>
       </c>
       <c r="K33" t="n">
-        <v>-86.64</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>87.06</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>63.58</v>
+        <v>57.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-89.14</v>
+        <v>-80.63</v>
       </c>
       <c r="L34" t="n">
-        <v>109.49</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>47.08</v>
+        <v>46.56</v>
       </c>
       <c r="K35" t="n">
-        <v>-89.52</v>
+        <v>-88.53</v>
       </c>
       <c r="L35" t="n">
-        <v>101.14</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-172.53</v>
+        <v>-173.99</v>
       </c>
       <c r="K36" t="n">
-        <v>-50.12</v>
+        <v>-50.54</v>
       </c>
       <c r="L36" t="n">
-        <v>179.66</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>208.76</v>
+        <v>209.69</v>
       </c>
       <c r="K37" t="n">
-        <v>144.68</v>
+        <v>145.33</v>
       </c>
       <c r="L37" t="n">
-        <v>254</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>19.39</v>
+        <v>35.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-54.69</v>
+        <v>-99.54000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>58.03</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-35.9</v>
+        <v>-87.88</v>
       </c>
       <c r="K39" t="n">
-        <v>27.7</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>45.35</v>
+        <v>110.99</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>169.02</v>
+        <v>168.63</v>
       </c>
       <c r="K40" t="n">
-        <v>-209.5</v>
+        <v>-209.02</v>
       </c>
       <c r="L40" t="n">
-        <v>269.18</v>
+        <v>268.57</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>74.87</v>
+        <v>125.45</v>
       </c>
       <c r="K41" t="n">
-        <v>-147.55</v>
+        <v>-247.24</v>
       </c>
       <c r="L41" t="n">
-        <v>165.46</v>
+        <v>277.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-185.59</v>
+        <v>-195.8</v>
       </c>
       <c r="K42" t="n">
-        <v>217.8</v>
+        <v>229.79</v>
       </c>
       <c r="L42" t="n">
-        <v>286.15</v>
+        <v>301.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-52.3</v>
+        <v>-82.77</v>
       </c>
       <c r="K43" t="n">
-        <v>155.67</v>
+        <v>246.36</v>
       </c>
       <c r="L43" t="n">
-        <v>164.22</v>
+        <v>259.89</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>167.17</v>
+        <v>132.34</v>
       </c>
       <c r="K44" t="n">
-        <v>27.85</v>
+        <v>22.04</v>
       </c>
       <c r="L44" t="n">
-        <v>169.48</v>
+        <v>134.16</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="K45" t="n">
-        <v>25.3</v>
+        <v>36.43</v>
       </c>
       <c r="L45" t="n">
-        <v>25.3</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-92.84</v>
+        <v>-60.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-151.83</v>
+        <v>-98.88</v>
       </c>
       <c r="L46" t="n">
-        <v>177.96</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>173.43</v>
+        <v>128.37</v>
       </c>
       <c r="K47" t="n">
-        <v>79.5</v>
+        <v>58.85</v>
       </c>
       <c r="L47" t="n">
-        <v>190.78</v>
+        <v>141.22</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-145</v>
+        <v>-114.9</v>
       </c>
       <c r="K48" t="n">
-        <v>62.99</v>
+        <v>49.92</v>
       </c>
       <c r="L48" t="n">
-        <v>158.09</v>
+        <v>125.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-67.33</v>
+        <v>-66.61</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.03</v>
+        <v>-21.8</v>
       </c>
       <c r="L49" t="n">
-        <v>70.84</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-190.87</v>
+        <v>-162.71</v>
       </c>
       <c r="K50" t="n">
-        <v>148.62</v>
+        <v>126.7</v>
       </c>
       <c r="L50" t="n">
-        <v>241.91</v>
+        <v>206.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.39</v>
+        <v>-9.94</v>
       </c>
       <c r="K51" t="n">
-        <v>308</v>
+        <v>268.87</v>
       </c>
       <c r="L51" t="n">
-        <v>308.21</v>
+        <v>269.06</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>95.08</v>
+        <v>91.12</v>
       </c>
       <c r="K52" t="n">
-        <v>199.1</v>
+        <v>190.82</v>
       </c>
       <c r="L52" t="n">
-        <v>220.64</v>
+        <v>211.46</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-27.38</v>
+        <v>-25.83</v>
       </c>
       <c r="K53" t="n">
-        <v>220.52</v>
+        <v>208.06</v>
       </c>
       <c r="L53" t="n">
-        <v>222.21</v>
+        <v>209.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-54.99</v>
+        <v>-56.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-177.52</v>
+        <v>-181.44</v>
       </c>
       <c r="L54" t="n">
-        <v>185.84</v>
+        <v>189.94</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-181.35</v>
+        <v>-188.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-22.25</v>
+        <v>-23.1</v>
       </c>
       <c r="L55" t="n">
-        <v>182.71</v>
+        <v>189.66</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>243.72</v>
+        <v>283.14</v>
       </c>
       <c r="K56" t="n">
-        <v>225.48</v>
+        <v>261.94</v>
       </c>
       <c r="L56" t="n">
-        <v>332.03</v>
+        <v>385.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-312.44</v>
+        <v>-311.73</v>
       </c>
       <c r="K57" t="n">
-        <v>-156.65</v>
+        <v>-156.29</v>
       </c>
       <c r="L57" t="n">
-        <v>349.51</v>
+        <v>348.71</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>205.71</v>
+        <v>237.92</v>
       </c>
       <c r="K58" t="n">
-        <v>-240.1</v>
+        <v>-277.69</v>
       </c>
       <c r="L58" t="n">
-        <v>316.17</v>
+        <v>365.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-22.47</v>
+        <v>-25.8</v>
       </c>
       <c r="K59" t="n">
-        <v>43.53</v>
+        <v>49.97</v>
       </c>
       <c r="L59" t="n">
-        <v>48.99</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>99.81999999999999</v>
+        <v>81.94</v>
       </c>
       <c r="K60" t="n">
-        <v>-63.41</v>
+        <v>-52.05</v>
       </c>
       <c r="L60" t="n">
-        <v>118.25</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>107.96</v>
+        <v>88.59</v>
       </c>
       <c r="K61" t="n">
-        <v>30.12</v>
+        <v>24.72</v>
       </c>
       <c r="L61" t="n">
-        <v>112.09</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>48.07</v>
+        <v>38.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-113.28</v>
+        <v>-90.54000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>123.05</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>33.16</v>
+        <v>22.44</v>
       </c>
       <c r="K63" t="n">
-        <v>-170.71</v>
+        <v>-115.51</v>
       </c>
       <c r="L63" t="n">
-        <v>173.9</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-67.02</v>
+        <v>-50.28</v>
       </c>
       <c r="K64" t="n">
-        <v>141.24</v>
+        <v>105.97</v>
       </c>
       <c r="L64" t="n">
-        <v>156.34</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-142.39</v>
+        <v>-152.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-36.58</v>
+        <v>-39.18</v>
       </c>
       <c r="L65" t="n">
-        <v>147.02</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-136.05</v>
+        <v>-145.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-35.06</v>
+        <v>-37.37</v>
       </c>
       <c r="L66" t="n">
-        <v>140.49</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.44</v>
+        <v>-6.6</v>
       </c>
       <c r="K67" t="n">
-        <v>-101.47</v>
+        <v>-123.17</v>
       </c>
       <c r="L67" t="n">
-        <v>101.62</v>
+        <v>123.34</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-263.25</v>
+        <v>-219.22</v>
       </c>
       <c r="K68" t="n">
-        <v>-106.07</v>
+        <v>-88.33</v>
       </c>
       <c r="L68" t="n">
-        <v>283.81</v>
+        <v>236.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-75.48999999999999</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-95.33</v>
+        <v>-125.72</v>
       </c>
       <c r="L69" t="n">
-        <v>121.6</v>
+        <v>160.37</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>23.84</v>
+        <v>21.31</v>
       </c>
       <c r="K70" t="n">
-        <v>-291.79</v>
+        <v>-260.86</v>
       </c>
       <c r="L70" t="n">
-        <v>292.76</v>
+        <v>261.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>221.73</v>
+        <v>252.08</v>
       </c>
       <c r="K71" t="n">
-        <v>213.56</v>
+        <v>242.79</v>
       </c>
       <c r="L71" t="n">
-        <v>307.86</v>
+        <v>349.98</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-130.38</v>
+        <v>-216.28</v>
       </c>
       <c r="K72" t="n">
-        <v>29.18</v>
+        <v>48.4</v>
       </c>
       <c r="L72" t="n">
-        <v>133.6</v>
+        <v>221.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>77.64</v>
+        <v>85.27</v>
       </c>
       <c r="K73" t="n">
-        <v>315.21</v>
+        <v>346.21</v>
       </c>
       <c r="L73" t="n">
-        <v>324.63</v>
+        <v>356.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.97</v>
+        <v>-55.8</v>
       </c>
       <c r="K74" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>48.97</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.78</v>
+        <v>-48.7</v>
       </c>
       <c r="K75" t="n">
-        <v>68.33</v>
+        <v>49.83</v>
       </c>
       <c r="L75" t="n">
-        <v>95.54000000000001</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>144.51</v>
+        <v>108.19</v>
       </c>
       <c r="K76" t="n">
-        <v>-134.42</v>
+        <v>-100.64</v>
       </c>
       <c r="L76" t="n">
-        <v>197.36</v>
+        <v>147.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-23.47</v>
+        <v>-20.02</v>
       </c>
       <c r="K77" t="n">
-        <v>111.35</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>113.79</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>65.8</v>
+        <v>46.67</v>
       </c>
       <c r="K78" t="n">
-        <v>120.06</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>136.91</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.34</v>
+        <v>-1.08</v>
       </c>
       <c r="K79" t="n">
-        <v>147.08</v>
+        <v>118.76</v>
       </c>
       <c r="L79" t="n">
-        <v>147.09</v>
+        <v>118.76</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>72.7</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-8.81</v>
+        <v>-11.81</v>
       </c>
       <c r="L80" t="n">
-        <v>73.23</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>62.77</v>
+        <v>72.84</v>
       </c>
       <c r="K81" t="n">
-        <v>-40.9</v>
+        <v>-47.46</v>
       </c>
       <c r="L81" t="n">
-        <v>74.92</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-124.36</v>
+        <v>-99.37</v>
       </c>
       <c r="K82" t="n">
-        <v>-240.24</v>
+        <v>-191.97</v>
       </c>
       <c r="L82" t="n">
-        <v>270.52</v>
+        <v>216.17</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-68.06</v>
+        <v>-59.91</v>
       </c>
       <c r="K83" t="n">
-        <v>419.2</v>
+        <v>369.01</v>
       </c>
       <c r="L83" t="n">
-        <v>424.69</v>
+        <v>373.84</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>8.92</v>
+        <v>10.99</v>
       </c>
       <c r="K84" t="n">
-        <v>106.98</v>
+        <v>131.75</v>
       </c>
       <c r="L84" t="n">
-        <v>107.35</v>
+        <v>132.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-164.11</v>
+        <v>-198.28</v>
       </c>
       <c r="K85" t="n">
-        <v>54.5</v>
+        <v>65.84</v>
       </c>
       <c r="L85" t="n">
-        <v>172.93</v>
+        <v>208.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-110.96</v>
+        <v>-164.96</v>
       </c>
       <c r="K86" t="n">
-        <v>179.73</v>
+        <v>267.18</v>
       </c>
       <c r="L86" t="n">
-        <v>211.22</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>164.43</v>
+        <v>242.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-95.94</v>
+        <v>-141.21</v>
       </c>
       <c r="L87" t="n">
-        <v>190.37</v>
+        <v>280.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>310.95</v>
+        <v>332.58</v>
       </c>
       <c r="K88" t="n">
-        <v>93.91</v>
+        <v>100.45</v>
       </c>
       <c r="L88" t="n">
-        <v>324.82</v>
+        <v>347.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>49.96</v>
+        <v>44.61</v>
       </c>
       <c r="K14" t="n">
-        <v>-15.98</v>
+        <v>-14.26</v>
       </c>
       <c r="L14" t="n">
-        <v>52.45</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.96</v>
+        <v>-31.51</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.75</v>
+        <v>-34.57</v>
       </c>
       <c r="L15" t="n">
-        <v>57.84</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>78.41</v>
+        <v>62.99</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.63</v>
+        <v>-33.45</v>
       </c>
       <c r="L16" t="n">
-        <v>88.77</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.4</v>
+        <v>-45.42</v>
       </c>
       <c r="K17" t="n">
-        <v>54.49</v>
+        <v>43.87</v>
       </c>
       <c r="L17" t="n">
-        <v>78.42</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-29.5</v>
+        <v>-27.52</v>
       </c>
       <c r="K18" t="n">
-        <v>46.1</v>
+        <v>43.01</v>
       </c>
       <c r="L18" t="n">
-        <v>54.73</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-53.38</v>
+        <v>-41.65</v>
       </c>
       <c r="K19" t="n">
-        <v>102.43</v>
+        <v>79.92</v>
       </c>
       <c r="L19" t="n">
-        <v>115.5</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>160.61</v>
+        <v>106.01</v>
       </c>
       <c r="K20" t="n">
-        <v>112.26</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>195.96</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>40.32</v>
+        <v>28.24</v>
       </c>
       <c r="K21" t="n">
-        <v>-95.40000000000001</v>
+        <v>-66.81999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>103.57</v>
+        <v>72.54000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>178.43</v>
+        <v>129.31</v>
       </c>
       <c r="K22" t="n">
-        <v>-93.31</v>
+        <v>-67.63</v>
       </c>
       <c r="L22" t="n">
-        <v>201.36</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-115.91</v>
+        <v>-71</v>
       </c>
       <c r="K23" t="n">
-        <v>47.82</v>
+        <v>29.29</v>
       </c>
       <c r="L23" t="n">
-        <v>125.38</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>169.99</v>
+        <v>100.25</v>
       </c>
       <c r="K24" t="n">
-        <v>-117.71</v>
+        <v>-69.42</v>
       </c>
       <c r="L24" t="n">
-        <v>206.76</v>
+        <v>121.94</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>349.77</v>
+        <v>206.26</v>
       </c>
       <c r="K25" t="n">
-        <v>312.42</v>
+        <v>184.24</v>
       </c>
       <c r="L25" t="n">
-        <v>468.99</v>
+        <v>276.56</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-338.67</v>
+        <v>-208.22</v>
       </c>
       <c r="K26" t="n">
-        <v>60.13</v>
+        <v>36.97</v>
       </c>
       <c r="L26" t="n">
-        <v>343.97</v>
+        <v>211.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-35.02</v>
+        <v>-20.83</v>
       </c>
       <c r="K27" t="n">
-        <v>302.7</v>
+        <v>180.07</v>
       </c>
       <c r="L27" t="n">
-        <v>304.72</v>
+        <v>181.27</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>157.89</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>129.53</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>204.22</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.85</v>
+        <v>-27.03</v>
       </c>
       <c r="K29" t="n">
-        <v>40.43</v>
+        <v>31.36</v>
       </c>
       <c r="L29" t="n">
-        <v>53.38</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.11</v>
+        <v>-57.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-19.73</v>
+        <v>-18.24</v>
       </c>
       <c r="L30" t="n">
-        <v>65.16</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>63.3</v>
+        <v>61.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.1</v>
+        <v>-2.05</v>
       </c>
       <c r="L31" t="n">
-        <v>63.34</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>35.87</v>
+        <v>32.84</v>
       </c>
       <c r="K32" t="n">
-        <v>76.31999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="L32" t="n">
-        <v>84.33</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.21</v>
+        <v>-6.73</v>
       </c>
       <c r="K33" t="n">
-        <v>-72.51000000000001</v>
+        <v>-67.73</v>
       </c>
       <c r="L33" t="n">
-        <v>72.87</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>57.51</v>
+        <v>45.95</v>
       </c>
       <c r="K34" t="n">
-        <v>-80.63</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>99.03</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>46.56</v>
+        <v>38.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-88.53</v>
+        <v>-73.36</v>
       </c>
       <c r="L35" t="n">
-        <v>100.03</v>
+        <v>82.89</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-173.99</v>
+        <v>-113.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-50.54</v>
+        <v>-32.83</v>
       </c>
       <c r="L36" t="n">
-        <v>181.18</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>209.69</v>
+        <v>138.35</v>
       </c>
       <c r="K37" t="n">
-        <v>145.33</v>
+        <v>95.88</v>
       </c>
       <c r="L37" t="n">
-        <v>255.13</v>
+        <v>168.32</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>35.29</v>
+        <v>24.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-99.54000000000001</v>
+        <v>-69.06</v>
       </c>
       <c r="L38" t="n">
-        <v>105.61</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-87.88</v>
+        <v>-53.72</v>
       </c>
       <c r="K39" t="n">
-        <v>67.79000000000001</v>
+        <v>41.44</v>
       </c>
       <c r="L39" t="n">
-        <v>110.99</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>168.63</v>
+        <v>107.41</v>
       </c>
       <c r="K40" t="n">
-        <v>-209.02</v>
+        <v>-133.14</v>
       </c>
       <c r="L40" t="n">
-        <v>268.57</v>
+        <v>171.07</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>125.45</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-247.24</v>
+        <v>-126.99</v>
       </c>
       <c r="L41" t="n">
-        <v>277.25</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-195.8</v>
+        <v>-126.13</v>
       </c>
       <c r="K42" t="n">
-        <v>229.79</v>
+        <v>148.03</v>
       </c>
       <c r="L42" t="n">
-        <v>301.89</v>
+        <v>194.48</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-82.77</v>
+        <v>-45.14</v>
       </c>
       <c r="K43" t="n">
-        <v>246.36</v>
+        <v>134.35</v>
       </c>
       <c r="L43" t="n">
-        <v>259.89</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>132.34</v>
+        <v>103.04</v>
       </c>
       <c r="K44" t="n">
-        <v>22.04</v>
+        <v>17.16</v>
       </c>
       <c r="L44" t="n">
-        <v>134.16</v>
+        <v>104.46</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="K45" t="n">
-        <v>36.43</v>
+        <v>32.6</v>
       </c>
       <c r="L45" t="n">
-        <v>36.43</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-60.46</v>
+        <v>-51.54</v>
       </c>
       <c r="K46" t="n">
-        <v>-98.88</v>
+        <v>-84.28</v>
       </c>
       <c r="L46" t="n">
-        <v>115.9</v>
+        <v>98.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>128.37</v>
+        <v>108.36</v>
       </c>
       <c r="K47" t="n">
-        <v>58.85</v>
+        <v>49.68</v>
       </c>
       <c r="L47" t="n">
-        <v>141.22</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-114.9</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>49.92</v>
+        <v>40.12</v>
       </c>
       <c r="L48" t="n">
-        <v>125.27</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-66.61</v>
+        <v>-58.05</v>
       </c>
       <c r="K49" t="n">
-        <v>-21.8</v>
+        <v>-19</v>
       </c>
       <c r="L49" t="n">
-        <v>70.09</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-162.71</v>
+        <v>-117.92</v>
       </c>
       <c r="K50" t="n">
-        <v>126.7</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>206.22</v>
+        <v>149.45</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.94</v>
+        <v>-6.48</v>
       </c>
       <c r="K51" t="n">
-        <v>268.87</v>
+        <v>175.19</v>
       </c>
       <c r="L51" t="n">
-        <v>269.06</v>
+        <v>175.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>91.12</v>
+        <v>59.56</v>
       </c>
       <c r="K52" t="n">
-        <v>190.82</v>
+        <v>124.73</v>
       </c>
       <c r="L52" t="n">
-        <v>211.46</v>
+        <v>138.22</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-25.83</v>
+        <v>-17.9</v>
       </c>
       <c r="K53" t="n">
-        <v>208.06</v>
+        <v>144.19</v>
       </c>
       <c r="L53" t="n">
-        <v>209.65</v>
+        <v>145.29</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-56.2</v>
+        <v>-38.97</v>
       </c>
       <c r="K54" t="n">
-        <v>-181.44</v>
+        <v>-125.82</v>
       </c>
       <c r="L54" t="n">
-        <v>189.94</v>
+        <v>131.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-188.25</v>
+        <v>-130.58</v>
       </c>
       <c r="K55" t="n">
-        <v>-23.1</v>
+        <v>-16.02</v>
       </c>
       <c r="L55" t="n">
-        <v>189.66</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>283.14</v>
+        <v>154.27</v>
       </c>
       <c r="K56" t="n">
-        <v>261.94</v>
+        <v>142.72</v>
       </c>
       <c r="L56" t="n">
-        <v>385.72</v>
+        <v>210.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-311.73</v>
+        <v>-200.15</v>
       </c>
       <c r="K57" t="n">
-        <v>-156.29</v>
+        <v>-100.35</v>
       </c>
       <c r="L57" t="n">
-        <v>348.71</v>
+        <v>223.9</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>237.92</v>
+        <v>134.76</v>
       </c>
       <c r="K58" t="n">
-        <v>-277.69</v>
+        <v>-157.29</v>
       </c>
       <c r="L58" t="n">
-        <v>365.68</v>
+        <v>207.12</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.8</v>
+        <v>-19.95</v>
       </c>
       <c r="K59" t="n">
-        <v>49.97</v>
+        <v>38.64</v>
       </c>
       <c r="L59" t="n">
-        <v>56.24</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>81.94</v>
+        <v>63.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-52.05</v>
+        <v>-40.21</v>
       </c>
       <c r="L60" t="n">
-        <v>97.08</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>88.59</v>
+        <v>70.73</v>
       </c>
       <c r="K61" t="n">
-        <v>24.72</v>
+        <v>19.73</v>
       </c>
       <c r="L61" t="n">
-        <v>91.97</v>
+        <v>73.43000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>38.42</v>
+        <v>33.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-90.54000000000001</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>98.34999999999999</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>22.44</v>
+        <v>21.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-115.51</v>
+        <v>-110.5</v>
       </c>
       <c r="L63" t="n">
-        <v>117.67</v>
+        <v>112.57</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-50.28</v>
+        <v>-44.16</v>
       </c>
       <c r="K64" t="n">
-        <v>105.97</v>
+        <v>93.08</v>
       </c>
       <c r="L64" t="n">
-        <v>117.29</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-152.49</v>
+        <v>-98.81999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-39.18</v>
+        <v>-25.39</v>
       </c>
       <c r="L65" t="n">
-        <v>157.45</v>
+        <v>102.03</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-145.02</v>
+        <v>-98.09999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-37.37</v>
+        <v>-25.28</v>
       </c>
       <c r="L66" t="n">
-        <v>149.76</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.6</v>
+        <v>-4.43</v>
       </c>
       <c r="K67" t="n">
-        <v>-123.17</v>
+        <v>-82.62</v>
       </c>
       <c r="L67" t="n">
-        <v>123.34</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-219.22</v>
+        <v>-156.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-88.33</v>
+        <v>-63.17</v>
       </c>
       <c r="L68" t="n">
-        <v>236.35</v>
+        <v>169.03</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-99.56999999999999</v>
+        <v>-63.36</v>
       </c>
       <c r="K69" t="n">
-        <v>-125.72</v>
+        <v>-80.01000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>160.37</v>
+        <v>102.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>21.31</v>
+        <v>14.78</v>
       </c>
       <c r="K70" t="n">
-        <v>-260.86</v>
+        <v>-180.9</v>
       </c>
       <c r="L70" t="n">
-        <v>261.73</v>
+        <v>181.51</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>252.08</v>
+        <v>142.17</v>
       </c>
       <c r="K71" t="n">
-        <v>242.79</v>
+        <v>136.93</v>
       </c>
       <c r="L71" t="n">
-        <v>349.98</v>
+        <v>197.39</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-216.28</v>
+        <v>-124.79</v>
       </c>
       <c r="K72" t="n">
-        <v>48.4</v>
+        <v>27.92</v>
       </c>
       <c r="L72" t="n">
-        <v>221.63</v>
+        <v>127.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>85.27</v>
+        <v>50.28</v>
       </c>
       <c r="K73" t="n">
-        <v>346.21</v>
+        <v>204.12</v>
       </c>
       <c r="L73" t="n">
-        <v>356.55</v>
+        <v>210.22</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-55.8</v>
+        <v>-43.04</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="L74" t="n">
-        <v>55.8</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-48.7</v>
+        <v>-45.08</v>
       </c>
       <c r="K75" t="n">
-        <v>49.83</v>
+        <v>46.13</v>
       </c>
       <c r="L75" t="n">
-        <v>69.68000000000001</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>108.19</v>
+        <v>90.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-100.64</v>
+        <v>-83.87</v>
       </c>
       <c r="L76" t="n">
-        <v>147.76</v>
+        <v>123.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.02</v>
+        <v>-16.81</v>
       </c>
       <c r="K77" t="n">
-        <v>94.95999999999999</v>
+        <v>79.72</v>
       </c>
       <c r="L77" t="n">
-        <v>97.04000000000001</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>46.67</v>
+        <v>45.91</v>
       </c>
       <c r="K78" t="n">
-        <v>85.15000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>97.11</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="K79" t="n">
-        <v>118.76</v>
+        <v>97.81</v>
       </c>
       <c r="L79" t="n">
-        <v>118.76</v>
+        <v>97.81999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>97.45999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-11.81</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>98.17</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>72.84</v>
+        <v>59.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-47.46</v>
+        <v>-38.89</v>
       </c>
       <c r="L81" t="n">
-        <v>86.94</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-99.37</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-191.97</v>
+        <v>-154.48</v>
       </c>
       <c r="L82" t="n">
-        <v>216.17</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-59.91</v>
+        <v>-35.74</v>
       </c>
       <c r="K83" t="n">
-        <v>369.01</v>
+        <v>220.11</v>
       </c>
       <c r="L83" t="n">
-        <v>373.84</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>10.99</v>
+        <v>7.64</v>
       </c>
       <c r="K84" t="n">
-        <v>131.75</v>
+        <v>91.59</v>
       </c>
       <c r="L84" t="n">
-        <v>132.21</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-198.28</v>
+        <v>-116.96</v>
       </c>
       <c r="K85" t="n">
-        <v>65.84</v>
+        <v>38.84</v>
       </c>
       <c r="L85" t="n">
-        <v>208.92</v>
+        <v>123.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-164.96</v>
+        <v>-84.08</v>
       </c>
       <c r="K86" t="n">
-        <v>267.18</v>
+        <v>136.19</v>
       </c>
       <c r="L86" t="n">
-        <v>314</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>242.02</v>
+        <v>132.27</v>
       </c>
       <c r="K87" t="n">
-        <v>-141.21</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>280.2</v>
+        <v>153.14</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>332.58</v>
+        <v>199.46</v>
       </c>
       <c r="K88" t="n">
-        <v>100.45</v>
+        <v>60.24</v>
       </c>
       <c r="L88" t="n">
-        <v>347.42</v>
+        <v>208.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>44.61</v>
+        <v>39.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-14.26</v>
+        <v>-12.71</v>
       </c>
       <c r="L14" t="n">
-        <v>46.83</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-31.51</v>
+        <v>-28.07</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.57</v>
+        <v>-30.8</v>
       </c>
       <c r="L15" t="n">
-        <v>46.78</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>62.99</v>
+        <v>56.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.45</v>
+        <v>-30.02</v>
       </c>
       <c r="L16" t="n">
-        <v>71.31999999999999</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-45.42</v>
+        <v>-42.94</v>
       </c>
       <c r="K17" t="n">
-        <v>43.87</v>
+        <v>41.48</v>
       </c>
       <c r="L17" t="n">
-        <v>63.15</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-27.52</v>
+        <v>-25.14</v>
       </c>
       <c r="K18" t="n">
-        <v>43.01</v>
+        <v>39.29</v>
       </c>
       <c r="L18" t="n">
-        <v>51.06</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.65</v>
+        <v>-39.18</v>
       </c>
       <c r="K19" t="n">
-        <v>79.92</v>
+        <v>75.19</v>
       </c>
       <c r="L19" t="n">
-        <v>90.12</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>106.01</v>
+        <v>105.62</v>
       </c>
       <c r="K20" t="n">
-        <v>74.09999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="L20" t="n">
-        <v>129.34</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>28.24</v>
+        <v>27.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.81999999999999</v>
+        <v>-65.93000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>72.54000000000001</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>129.31</v>
+        <v>128.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-67.63</v>
+        <v>-67.45</v>
       </c>
       <c r="L22" t="n">
-        <v>145.93</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-71</v>
+        <v>-72.7</v>
       </c>
       <c r="K23" t="n">
-        <v>29.29</v>
+        <v>30</v>
       </c>
       <c r="L23" t="n">
-        <v>76.8</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>100.25</v>
+        <v>102.81</v>
       </c>
       <c r="K24" t="n">
-        <v>-69.42</v>
+        <v>-71.19</v>
       </c>
       <c r="L24" t="n">
-        <v>121.94</v>
+        <v>125.05</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>206.26</v>
+        <v>212.85</v>
       </c>
       <c r="K25" t="n">
-        <v>184.24</v>
+        <v>190.12</v>
       </c>
       <c r="L25" t="n">
-        <v>276.56</v>
+        <v>285.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-208.22</v>
+        <v>-212.33</v>
       </c>
       <c r="K26" t="n">
-        <v>36.97</v>
+        <v>37.7</v>
       </c>
       <c r="L26" t="n">
-        <v>211.48</v>
+        <v>215.65</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-20.83</v>
+        <v>-21.21</v>
       </c>
       <c r="K27" t="n">
-        <v>180.07</v>
+        <v>183.29</v>
       </c>
       <c r="L27" t="n">
-        <v>181.27</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>97.56999999999999</v>
+        <v>99.89</v>
       </c>
       <c r="K28" t="n">
-        <v>80.04000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="L28" t="n">
-        <v>126.2</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.03</v>
+        <v>-24.58</v>
       </c>
       <c r="K29" t="n">
-        <v>31.36</v>
+        <v>28.51</v>
       </c>
       <c r="L29" t="n">
-        <v>41.4</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-57.43</v>
+        <v>-52.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.24</v>
+        <v>-16.55</v>
       </c>
       <c r="L30" t="n">
-        <v>60.26</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>61.76</v>
+        <v>54.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.05</v>
+        <v>-1.8</v>
       </c>
       <c r="L31" t="n">
-        <v>61.79</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>32.84</v>
+        <v>30.12</v>
       </c>
       <c r="K32" t="n">
-        <v>69.88</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.20999999999999</v>
+        <v>70.81999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.73</v>
+        <v>-6.15</v>
       </c>
       <c r="K33" t="n">
-        <v>-67.73</v>
+        <v>-61.86</v>
       </c>
       <c r="L33" t="n">
-        <v>68.06999999999999</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>45.95</v>
+        <v>42.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-64.43000000000001</v>
+        <v>-60.15</v>
       </c>
       <c r="L34" t="n">
-        <v>79.14</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>38.58</v>
+        <v>37.52</v>
       </c>
       <c r="K35" t="n">
-        <v>-73.36</v>
+        <v>-71.34</v>
       </c>
       <c r="L35" t="n">
-        <v>82.89</v>
+        <v>80.61</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-113.01</v>
+        <v>-112.59</v>
       </c>
       <c r="K36" t="n">
-        <v>-32.83</v>
+        <v>-32.71</v>
       </c>
       <c r="L36" t="n">
-        <v>117.68</v>
+        <v>117.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>138.35</v>
+        <v>137.84</v>
       </c>
       <c r="K37" t="n">
-        <v>95.88</v>
+        <v>95.53</v>
       </c>
       <c r="L37" t="n">
-        <v>168.32</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>24.48</v>
+        <v>24.54</v>
       </c>
       <c r="K38" t="n">
-        <v>-69.06</v>
+        <v>-69.2</v>
       </c>
       <c r="L38" t="n">
-        <v>73.27</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-53.72</v>
+        <v>-54.71</v>
       </c>
       <c r="K39" t="n">
-        <v>41.44</v>
+        <v>42.21</v>
       </c>
       <c r="L39" t="n">
-        <v>67.84999999999999</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>107.41</v>
+        <v>109.04</v>
       </c>
       <c r="K40" t="n">
-        <v>-133.14</v>
+        <v>-135.16</v>
       </c>
       <c r="L40" t="n">
-        <v>171.07</v>
+        <v>173.66</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>64.43000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="K41" t="n">
-        <v>-126.99</v>
+        <v>-132.98</v>
       </c>
       <c r="L41" t="n">
-        <v>142.4</v>
+        <v>149.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-126.13</v>
+        <v>-128</v>
       </c>
       <c r="K42" t="n">
-        <v>148.03</v>
+        <v>150.22</v>
       </c>
       <c r="L42" t="n">
-        <v>194.48</v>
+        <v>197.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-45.14</v>
+        <v>-46.69</v>
       </c>
       <c r="K43" t="n">
-        <v>134.35</v>
+        <v>138.98</v>
       </c>
       <c r="L43" t="n">
-        <v>141.74</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>103.04</v>
+        <v>92.81</v>
       </c>
       <c r="K44" t="n">
-        <v>17.16</v>
+        <v>15.46</v>
       </c>
       <c r="L44" t="n">
-        <v>104.46</v>
+        <v>94.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="K45" t="n">
-        <v>32.6</v>
+        <v>28.98</v>
       </c>
       <c r="L45" t="n">
-        <v>32.6</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.54</v>
+        <v>-47.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-84.28</v>
+        <v>-77.13</v>
       </c>
       <c r="L46" t="n">
-        <v>98.79000000000001</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>108.36</v>
+        <v>100.49</v>
       </c>
       <c r="K47" t="n">
-        <v>49.68</v>
+        <v>46.07</v>
       </c>
       <c r="L47" t="n">
-        <v>119.2</v>
+        <v>110.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-92.34999999999999</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>40.12</v>
+        <v>37.5</v>
       </c>
       <c r="L48" t="n">
-        <v>100.69</v>
+        <v>94.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-58.05</v>
+        <v>-53.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-19</v>
+        <v>-17.61</v>
       </c>
       <c r="L49" t="n">
-        <v>61.08</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-117.92</v>
+        <v>-115.76</v>
       </c>
       <c r="K50" t="n">
-        <v>91.81999999999999</v>
+        <v>90.14</v>
       </c>
       <c r="L50" t="n">
-        <v>149.45</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.48</v>
+        <v>-6.49</v>
       </c>
       <c r="K51" t="n">
-        <v>175.19</v>
+        <v>175.46</v>
       </c>
       <c r="L51" t="n">
-        <v>175.31</v>
+        <v>175.58</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>59.56</v>
+        <v>59.98</v>
       </c>
       <c r="K52" t="n">
-        <v>124.73</v>
+        <v>125.61</v>
       </c>
       <c r="L52" t="n">
-        <v>138.22</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-17.9</v>
+        <v>-18.02</v>
       </c>
       <c r="K53" t="n">
-        <v>144.19</v>
+        <v>145.18</v>
       </c>
       <c r="L53" t="n">
-        <v>145.29</v>
+        <v>146.29</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-38.97</v>
+        <v>-39.05</v>
       </c>
       <c r="K54" t="n">
-        <v>-125.82</v>
+        <v>-126.07</v>
       </c>
       <c r="L54" t="n">
-        <v>131.72</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-130.58</v>
+        <v>-131.65</v>
       </c>
       <c r="K55" t="n">
-        <v>-16.02</v>
+        <v>-16.15</v>
       </c>
       <c r="L55" t="n">
-        <v>131.56</v>
+        <v>132.64</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>154.27</v>
+        <v>159.97</v>
       </c>
       <c r="K56" t="n">
-        <v>142.72</v>
+        <v>147.99</v>
       </c>
       <c r="L56" t="n">
-        <v>210.17</v>
+        <v>217.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-200.15</v>
+        <v>-202.82</v>
       </c>
       <c r="K57" t="n">
-        <v>-100.35</v>
+        <v>-101.69</v>
       </c>
       <c r="L57" t="n">
-        <v>223.9</v>
+        <v>226.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>134.76</v>
+        <v>138.79</v>
       </c>
       <c r="K58" t="n">
-        <v>-157.29</v>
+        <v>-162</v>
       </c>
       <c r="L58" t="n">
-        <v>207.12</v>
+        <v>213.32</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-19.95</v>
+        <v>-18.28</v>
       </c>
       <c r="K59" t="n">
-        <v>38.64</v>
+        <v>35.41</v>
       </c>
       <c r="L59" t="n">
-        <v>43.48</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>63.3</v>
+        <v>58.43</v>
       </c>
       <c r="K60" t="n">
-        <v>-40.21</v>
+        <v>-37.12</v>
       </c>
       <c r="L60" t="n">
-        <v>74.98999999999999</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>70.73</v>
+        <v>64.87</v>
       </c>
       <c r="K61" t="n">
-        <v>19.73</v>
+        <v>18.1</v>
       </c>
       <c r="L61" t="n">
-        <v>73.43000000000001</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>33.61</v>
+        <v>31.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-79.20999999999999</v>
+        <v>-73.11</v>
       </c>
       <c r="L62" t="n">
-        <v>86.04000000000001</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>21.46</v>
+        <v>19.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-110.5</v>
+        <v>-101.18</v>
       </c>
       <c r="L63" t="n">
-        <v>112.57</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-44.16</v>
+        <v>-40.73</v>
       </c>
       <c r="K64" t="n">
-        <v>93.08</v>
+        <v>85.84</v>
       </c>
       <c r="L64" t="n">
-        <v>103.02</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-98.81999999999999</v>
+        <v>-99.01000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-25.39</v>
+        <v>-25.44</v>
       </c>
       <c r="L65" t="n">
-        <v>102.03</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-98.09999999999999</v>
+        <v>-97.28</v>
       </c>
       <c r="K66" t="n">
-        <v>-25.28</v>
+        <v>-25.07</v>
       </c>
       <c r="L66" t="n">
-        <v>101.31</v>
+        <v>100.46</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.43</v>
+        <v>-4.39</v>
       </c>
       <c r="K67" t="n">
-        <v>-82.62</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>82.73999999999999</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-156.78</v>
+        <v>-156.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.17</v>
+        <v>-63.18</v>
       </c>
       <c r="L68" t="n">
-        <v>169.03</v>
+        <v>169.06</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-63.36</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-80.01000000000001</v>
+        <v>-81.08</v>
       </c>
       <c r="L69" t="n">
-        <v>102.06</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>14.78</v>
+        <v>14.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-180.9</v>
+        <v>-181.27</v>
       </c>
       <c r="L70" t="n">
-        <v>181.51</v>
+        <v>181.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>142.17</v>
+        <v>146.28</v>
       </c>
       <c r="K71" t="n">
-        <v>136.93</v>
+        <v>140.89</v>
       </c>
       <c r="L71" t="n">
-        <v>197.39</v>
+        <v>203.1</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-124.79</v>
+        <v>-129.09</v>
       </c>
       <c r="K72" t="n">
-        <v>27.92</v>
+        <v>28.89</v>
       </c>
       <c r="L72" t="n">
-        <v>127.88</v>
+        <v>132.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>50.28</v>
+        <v>51.54</v>
       </c>
       <c r="K73" t="n">
-        <v>204.12</v>
+        <v>209.26</v>
       </c>
       <c r="L73" t="n">
-        <v>210.22</v>
+        <v>215.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-43.04</v>
+        <v>-39.63</v>
       </c>
       <c r="K74" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="L74" t="n">
-        <v>43.04</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-45.08</v>
+        <v>-40.45</v>
       </c>
       <c r="K75" t="n">
-        <v>46.13</v>
+        <v>41.39</v>
       </c>
       <c r="L75" t="n">
-        <v>64.5</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>90.16</v>
+        <v>83.45</v>
       </c>
       <c r="K76" t="n">
-        <v>-83.87</v>
+        <v>-77.63</v>
       </c>
       <c r="L76" t="n">
-        <v>123.14</v>
+        <v>113.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-16.81</v>
+        <v>-15.65</v>
       </c>
       <c r="K77" t="n">
-        <v>79.72</v>
+        <v>74.22</v>
       </c>
       <c r="L77" t="n">
-        <v>81.48</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>45.91</v>
+        <v>42.19</v>
       </c>
       <c r="K78" t="n">
-        <v>83.76000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="L78" t="n">
-        <v>95.51000000000001</v>
+        <v>87.79000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.89</v>
+        <v>-0.84</v>
       </c>
       <c r="K79" t="n">
-        <v>97.81</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>97.81999999999999</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>70.43000000000001</v>
+        <v>69.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>70.94</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>59.67</v>
+        <v>57.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-38.89</v>
+        <v>-37.55</v>
       </c>
       <c r="L81" t="n">
-        <v>71.22</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.95999999999999</v>
+        <v>-77.69</v>
       </c>
       <c r="K82" t="n">
-        <v>-154.48</v>
+        <v>-150.08</v>
       </c>
       <c r="L82" t="n">
-        <v>173.95</v>
+        <v>168.99</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-35.74</v>
+        <v>-36.62</v>
       </c>
       <c r="K83" t="n">
-        <v>220.11</v>
+        <v>225.56</v>
       </c>
       <c r="L83" t="n">
-        <v>223</v>
+        <v>228.51</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>7.64</v>
+        <v>7.71</v>
       </c>
       <c r="K84" t="n">
-        <v>91.59</v>
+        <v>92.48</v>
       </c>
       <c r="L84" t="n">
-        <v>91.91</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-116.96</v>
+        <v>-120.48</v>
       </c>
       <c r="K85" t="n">
-        <v>38.84</v>
+        <v>40.01</v>
       </c>
       <c r="L85" t="n">
-        <v>123.24</v>
+        <v>126.95</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-84.08</v>
+        <v>-88.34</v>
       </c>
       <c r="K86" t="n">
-        <v>136.19</v>
+        <v>143.08</v>
       </c>
       <c r="L86" t="n">
-        <v>160.05</v>
+        <v>168.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>132.27</v>
+        <v>136.96</v>
       </c>
       <c r="K87" t="n">
-        <v>-77.18000000000001</v>
+        <v>-79.91</v>
       </c>
       <c r="L87" t="n">
-        <v>153.14</v>
+        <v>158.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>199.46</v>
+        <v>206.56</v>
       </c>
       <c r="K88" t="n">
-        <v>60.24</v>
+        <v>62.39</v>
       </c>
       <c r="L88" t="n">
-        <v>208.36</v>
+        <v>215.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>39.73</v>
+        <v>29.8</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.71</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>41.71</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-28.07</v>
+        <v>-21.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.8</v>
+        <v>-23.1</v>
       </c>
       <c r="L15" t="n">
-        <v>41.68</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>56.53</v>
+        <v>42.4</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.02</v>
+        <v>-22.51</v>
       </c>
       <c r="L16" t="n">
-        <v>64.01000000000001</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.94</v>
+        <v>-32.21</v>
       </c>
       <c r="K17" t="n">
-        <v>41.48</v>
+        <v>31.11</v>
       </c>
       <c r="L17" t="n">
-        <v>59.7</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-25.14</v>
+        <v>-18.86</v>
       </c>
       <c r="K18" t="n">
-        <v>39.29</v>
+        <v>29.47</v>
       </c>
       <c r="L18" t="n">
-        <v>46.65</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.18</v>
+        <v>-29.39</v>
       </c>
       <c r="K19" t="n">
-        <v>75.19</v>
+        <v>56.39</v>
       </c>
       <c r="L19" t="n">
-        <v>84.79000000000001</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>105.62</v>
+        <v>79.22</v>
       </c>
       <c r="K20" t="n">
-        <v>73.83</v>
+        <v>55.37</v>
       </c>
       <c r="L20" t="n">
-        <v>128.87</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>27.87</v>
+        <v>20.9</v>
       </c>
       <c r="K21" t="n">
-        <v>-65.93000000000001</v>
+        <v>-49.45</v>
       </c>
       <c r="L21" t="n">
-        <v>71.58</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>128.98</v>
+        <v>96.73</v>
       </c>
       <c r="K22" t="n">
-        <v>-67.45</v>
+        <v>-50.59</v>
       </c>
       <c r="L22" t="n">
-        <v>145.55</v>
+        <v>109.16</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-72.7</v>
+        <v>-54.53</v>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="L23" t="n">
-        <v>78.65000000000001</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>102.81</v>
+        <v>77.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-71.19</v>
+        <v>-53.39</v>
       </c>
       <c r="L24" t="n">
-        <v>125.05</v>
+        <v>93.79000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>212.85</v>
+        <v>159.64</v>
       </c>
       <c r="K25" t="n">
-        <v>190.12</v>
+        <v>142.59</v>
       </c>
       <c r="L25" t="n">
-        <v>285.39</v>
+        <v>214.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-212.33</v>
+        <v>-159.25</v>
       </c>
       <c r="K26" t="n">
-        <v>37.7</v>
+        <v>28.27</v>
       </c>
       <c r="L26" t="n">
-        <v>215.65</v>
+        <v>161.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-21.21</v>
+        <v>-13.29</v>
       </c>
       <c r="K27" t="n">
-        <v>183.29</v>
+        <v>114.9</v>
       </c>
       <c r="L27" t="n">
-        <v>184.51</v>
+        <v>115.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>99.89</v>
+        <v>74.92</v>
       </c>
       <c r="K28" t="n">
-        <v>81.95</v>
+        <v>61.46</v>
       </c>
       <c r="L28" t="n">
-        <v>129.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.58</v>
+        <v>-18.43</v>
       </c>
       <c r="K29" t="n">
-        <v>28.51</v>
+        <v>21.38</v>
       </c>
       <c r="L29" t="n">
-        <v>37.64</v>
+        <v>28.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-52.1</v>
+        <v>-39.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.55</v>
+        <v>-12.41</v>
       </c>
       <c r="L30" t="n">
-        <v>54.66</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>54.35</v>
+        <v>40.77</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.8</v>
+        <v>-1.35</v>
       </c>
       <c r="L31" t="n">
-        <v>54.38</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>30.12</v>
+        <v>22.59</v>
       </c>
       <c r="K32" t="n">
-        <v>64.09999999999999</v>
+        <v>48.07</v>
       </c>
       <c r="L32" t="n">
-        <v>70.81999999999999</v>
+        <v>53.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.15</v>
+        <v>-4.61</v>
       </c>
       <c r="K33" t="n">
-        <v>-61.86</v>
+        <v>-46.4</v>
       </c>
       <c r="L33" t="n">
-        <v>62.17</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>42.9</v>
+        <v>32.18</v>
       </c>
       <c r="K34" t="n">
-        <v>-60.15</v>
+        <v>-45.11</v>
       </c>
       <c r="L34" t="n">
-        <v>73.89</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>37.52</v>
+        <v>28.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-71.34</v>
+        <v>-53.51</v>
       </c>
       <c r="L35" t="n">
-        <v>80.61</v>
+        <v>60.46</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-112.59</v>
+        <v>-84.45</v>
       </c>
       <c r="K36" t="n">
-        <v>-32.71</v>
+        <v>-24.53</v>
       </c>
       <c r="L36" t="n">
-        <v>117.25</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>137.84</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>95.53</v>
+        <v>57.9</v>
       </c>
       <c r="L37" t="n">
-        <v>167.7</v>
+        <v>101.64</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>24.54</v>
+        <v>18.4</v>
       </c>
       <c r="K38" t="n">
-        <v>-69.2</v>
+        <v>-51.9</v>
       </c>
       <c r="L38" t="n">
-        <v>73.42</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-54.71</v>
+        <v>-18.42</v>
       </c>
       <c r="K39" t="n">
-        <v>42.21</v>
+        <v>14.21</v>
       </c>
       <c r="L39" t="n">
-        <v>69.09999999999999</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>109.04</v>
+        <v>81.78</v>
       </c>
       <c r="K40" t="n">
-        <v>-135.16</v>
+        <v>-101.37</v>
       </c>
       <c r="L40" t="n">
-        <v>173.66</v>
+        <v>130.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>67.47</v>
+        <v>50.6</v>
       </c>
       <c r="K41" t="n">
-        <v>-132.98</v>
+        <v>-99.73</v>
       </c>
       <c r="L41" t="n">
-        <v>149.12</v>
+        <v>111.84</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-128</v>
+        <v>-96</v>
       </c>
       <c r="K42" t="n">
-        <v>150.22</v>
+        <v>112.67</v>
       </c>
       <c r="L42" t="n">
-        <v>197.36</v>
+        <v>148.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-46.69</v>
+        <v>-35.02</v>
       </c>
       <c r="K43" t="n">
-        <v>138.98</v>
+        <v>104.23</v>
       </c>
       <c r="L43" t="n">
-        <v>146.61</v>
+        <v>109.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>92.81</v>
+        <v>69.61</v>
       </c>
       <c r="K44" t="n">
-        <v>15.46</v>
+        <v>11.59</v>
       </c>
       <c r="L44" t="n">
-        <v>94.09</v>
+        <v>70.56999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="K45" t="n">
-        <v>28.98</v>
+        <v>21.73</v>
       </c>
       <c r="L45" t="n">
-        <v>28.98</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-47.16</v>
+        <v>-35.37</v>
       </c>
       <c r="K46" t="n">
-        <v>-77.13</v>
+        <v>-57.84</v>
       </c>
       <c r="L46" t="n">
-        <v>90.40000000000001</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>100.49</v>
+        <v>75.37</v>
       </c>
       <c r="K47" t="n">
-        <v>46.07</v>
+        <v>34.55</v>
       </c>
       <c r="L47" t="n">
-        <v>110.54</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-86.31999999999999</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>37.5</v>
+        <v>28.13</v>
       </c>
       <c r="L48" t="n">
-        <v>94.11</v>
+        <v>70.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-53.8</v>
+        <v>-40.35</v>
       </c>
       <c r="K49" t="n">
-        <v>-17.61</v>
+        <v>-13.2</v>
       </c>
       <c r="L49" t="n">
-        <v>56.61</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-115.76</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>90.14</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>146.72</v>
+        <v>110.04</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.49</v>
+        <v>-4.87</v>
       </c>
       <c r="K51" t="n">
-        <v>175.46</v>
+        <v>131.59</v>
       </c>
       <c r="L51" t="n">
-        <v>175.58</v>
+        <v>131.68</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>59.98</v>
+        <v>44.99</v>
       </c>
       <c r="K52" t="n">
-        <v>125.61</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>139.2</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-18.02</v>
+        <v>-13.52</v>
       </c>
       <c r="K53" t="n">
-        <v>145.18</v>
+        <v>108.88</v>
       </c>
       <c r="L53" t="n">
-        <v>146.29</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-39.05</v>
+        <v>-29.29</v>
       </c>
       <c r="K54" t="n">
-        <v>-126.07</v>
+        <v>-94.56</v>
       </c>
       <c r="L54" t="n">
-        <v>131.98</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-131.65</v>
+        <v>-98.73999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-16.15</v>
+        <v>-12.12</v>
       </c>
       <c r="L55" t="n">
-        <v>132.64</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>159.97</v>
+        <v>119.98</v>
       </c>
       <c r="K56" t="n">
-        <v>147.99</v>
+        <v>110.99</v>
       </c>
       <c r="L56" t="n">
-        <v>217.93</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-202.82</v>
+        <v>-152.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-101.69</v>
+        <v>-76.27</v>
       </c>
       <c r="L57" t="n">
-        <v>226.88</v>
+        <v>170.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>138.79</v>
+        <v>104.1</v>
       </c>
       <c r="K58" t="n">
-        <v>-162</v>
+        <v>-121.5</v>
       </c>
       <c r="L58" t="n">
-        <v>213.32</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-18.28</v>
+        <v>-13.71</v>
       </c>
       <c r="K59" t="n">
-        <v>35.41</v>
+        <v>26.56</v>
       </c>
       <c r="L59" t="n">
-        <v>39.85</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>58.43</v>
+        <v>43.83</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.12</v>
+        <v>-27.84</v>
       </c>
       <c r="L60" t="n">
-        <v>69.23</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>64.87</v>
+        <v>48.65</v>
       </c>
       <c r="K61" t="n">
-        <v>18.1</v>
+        <v>13.57</v>
       </c>
       <c r="L61" t="n">
-        <v>67.34999999999999</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>31.03</v>
+        <v>23.27</v>
       </c>
       <c r="K62" t="n">
-        <v>-73.11</v>
+        <v>-54.84</v>
       </c>
       <c r="L62" t="n">
-        <v>79.43000000000001</v>
+        <v>59.57</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>19.65</v>
+        <v>14.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-101.18</v>
+        <v>-75.89</v>
       </c>
       <c r="L63" t="n">
-        <v>103.07</v>
+        <v>77.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-40.73</v>
+        <v>-30.55</v>
       </c>
       <c r="K64" t="n">
-        <v>85.84</v>
+        <v>64.38</v>
       </c>
       <c r="L64" t="n">
-        <v>95.02</v>
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-99.01000000000001</v>
+        <v>-74.26000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-25.44</v>
+        <v>-19.08</v>
       </c>
       <c r="L65" t="n">
-        <v>102.23</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-97.28</v>
+        <v>-72.95999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-25.07</v>
+        <v>-18.8</v>
       </c>
       <c r="L66" t="n">
-        <v>100.46</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.39</v>
+        <v>-3.29</v>
       </c>
       <c r="K67" t="n">
-        <v>-81.93000000000001</v>
+        <v>-61.44</v>
       </c>
       <c r="L67" t="n">
-        <v>82.04000000000001</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-156.81</v>
+        <v>-115.24</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.18</v>
+        <v>-46.44</v>
       </c>
       <c r="L68" t="n">
-        <v>169.06</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-64.20999999999999</v>
+        <v>-48.16</v>
       </c>
       <c r="K69" t="n">
-        <v>-81.08</v>
+        <v>-60.81</v>
       </c>
       <c r="L69" t="n">
-        <v>103.42</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>14.81</v>
+        <v>11.11</v>
       </c>
       <c r="K70" t="n">
-        <v>-181.27</v>
+        <v>-135.96</v>
       </c>
       <c r="L70" t="n">
-        <v>181.88</v>
+        <v>136.41</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>146.28</v>
+        <v>109.71</v>
       </c>
       <c r="K71" t="n">
-        <v>140.89</v>
+        <v>105.67</v>
       </c>
       <c r="L71" t="n">
-        <v>203.1</v>
+        <v>152.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-129.09</v>
+        <v>-94.5</v>
       </c>
       <c r="K72" t="n">
-        <v>28.89</v>
+        <v>21.15</v>
       </c>
       <c r="L72" t="n">
-        <v>132.28</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>51.54</v>
+        <v>38.66</v>
       </c>
       <c r="K73" t="n">
-        <v>209.26</v>
+        <v>156.94</v>
       </c>
       <c r="L73" t="n">
-        <v>215.51</v>
+        <v>161.64</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-39.63</v>
+        <v>-29.72</v>
       </c>
       <c r="K74" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="L74" t="n">
-        <v>39.63</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.45</v>
+        <v>-30.33</v>
       </c>
       <c r="K75" t="n">
-        <v>41.39</v>
+        <v>31.04</v>
       </c>
       <c r="L75" t="n">
-        <v>57.87</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>83.45</v>
+        <v>52.71</v>
       </c>
       <c r="K76" t="n">
-        <v>-77.63</v>
+        <v>-49.03</v>
       </c>
       <c r="L76" t="n">
-        <v>113.97</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-15.65</v>
+        <v>-11.73</v>
       </c>
       <c r="K77" t="n">
-        <v>74.22</v>
+        <v>55.66</v>
       </c>
       <c r="L77" t="n">
-        <v>75.84999999999999</v>
+        <v>56.89</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>42.19</v>
+        <v>29.99</v>
       </c>
       <c r="K78" t="n">
-        <v>76.98</v>
+        <v>54.71</v>
       </c>
       <c r="L78" t="n">
-        <v>87.79000000000001</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.84</v>
+        <v>-0.61</v>
       </c>
       <c r="K79" t="n">
-        <v>91.68000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="L79" t="n">
-        <v>91.69</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>69.27</v>
+        <v>51.96</v>
       </c>
       <c r="K80" t="n">
-        <v>-8.390000000000001</v>
+        <v>-6.29</v>
       </c>
       <c r="L80" t="n">
-        <v>69.78</v>
+        <v>52.34</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>57.63</v>
+        <v>43.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.55</v>
+        <v>-28.16</v>
       </c>
       <c r="L81" t="n">
-        <v>68.78</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-77.69</v>
+        <v>-48.77</v>
       </c>
       <c r="K82" t="n">
-        <v>-150.08</v>
+        <v>-94.22</v>
       </c>
       <c r="L82" t="n">
-        <v>168.99</v>
+        <v>106.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-36.62</v>
+        <v>-27.26</v>
       </c>
       <c r="K83" t="n">
-        <v>225.56</v>
+        <v>167.87</v>
       </c>
       <c r="L83" t="n">
-        <v>228.51</v>
+        <v>170.07</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>7.71</v>
+        <v>5.77</v>
       </c>
       <c r="K84" t="n">
-        <v>92.48</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>92.8</v>
+        <v>69.42</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-120.48</v>
+        <v>-90.36</v>
       </c>
       <c r="K85" t="n">
-        <v>40.01</v>
+        <v>30.01</v>
       </c>
       <c r="L85" t="n">
-        <v>126.95</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-88.34</v>
+        <v>-66.25</v>
       </c>
       <c r="K86" t="n">
-        <v>143.08</v>
+        <v>107.31</v>
       </c>
       <c r="L86" t="n">
-        <v>168.16</v>
+        <v>126.12</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>136.96</v>
+        <v>102.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-79.91</v>
+        <v>-59.93</v>
       </c>
       <c r="L87" t="n">
-        <v>158.56</v>
+        <v>118.92</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>206.56</v>
+        <v>151.22</v>
       </c>
       <c r="K88" t="n">
-        <v>62.39</v>
+        <v>45.67</v>
       </c>
       <c r="L88" t="n">
-        <v>215.78</v>
+        <v>157.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>29.8</v>
+        <v>30.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.76</v>
       </c>
       <c r="L14" t="n">
-        <v>31.28</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.06</v>
+        <v>-21.59</v>
       </c>
       <c r="K15" t="n">
-        <v>-23.1</v>
+        <v>-23.69</v>
       </c>
       <c r="L15" t="n">
-        <v>31.26</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>42.4</v>
+        <v>41.41</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.51</v>
+        <v>-21.99</v>
       </c>
       <c r="L16" t="n">
-        <v>48.01</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-32.21</v>
+        <v>-33.35</v>
       </c>
       <c r="K17" t="n">
-        <v>31.11</v>
+        <v>32.22</v>
       </c>
       <c r="L17" t="n">
-        <v>44.78</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-18.86</v>
+        <v>-19.75</v>
       </c>
       <c r="K18" t="n">
-        <v>29.47</v>
+        <v>30.87</v>
       </c>
       <c r="L18" t="n">
-        <v>34.99</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-29.39</v>
+        <v>-28.81</v>
       </c>
       <c r="K19" t="n">
-        <v>56.39</v>
+        <v>55.28</v>
       </c>
       <c r="L19" t="n">
-        <v>63.59</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>79.22</v>
+        <v>77.52</v>
       </c>
       <c r="K20" t="n">
-        <v>55.37</v>
+        <v>54.18</v>
       </c>
       <c r="L20" t="n">
-        <v>96.65000000000001</v>
+        <v>94.56999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>20.9</v>
+        <v>22.07</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.45</v>
+        <v>-52.23</v>
       </c>
       <c r="L21" t="n">
-        <v>53.68</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>96.73</v>
+        <v>93.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-50.59</v>
+        <v>-48.84</v>
       </c>
       <c r="L22" t="n">
-        <v>109.16</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-54.53</v>
+        <v>-59.51</v>
       </c>
       <c r="K23" t="n">
-        <v>22.5</v>
+        <v>24.55</v>
       </c>
       <c r="L23" t="n">
-        <v>58.99</v>
+        <v>64.37</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>77.11</v>
+        <v>78.34</v>
       </c>
       <c r="K24" t="n">
-        <v>-53.39</v>
+        <v>-54.25</v>
       </c>
       <c r="L24" t="n">
-        <v>93.79000000000001</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>159.64</v>
+        <v>149.81</v>
       </c>
       <c r="K25" t="n">
-        <v>142.59</v>
+        <v>133.81</v>
       </c>
       <c r="L25" t="n">
-        <v>214.05</v>
+        <v>200.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-159.25</v>
+        <v>-157.46</v>
       </c>
       <c r="K26" t="n">
-        <v>28.27</v>
+        <v>27.96</v>
       </c>
       <c r="L26" t="n">
-        <v>161.74</v>
+        <v>159.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.29</v>
+        <v>-13.99</v>
       </c>
       <c r="K27" t="n">
-        <v>114.9</v>
+        <v>120.94</v>
       </c>
       <c r="L27" t="n">
-        <v>115.66</v>
+        <v>121.74</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>74.92</v>
+        <v>79.37</v>
       </c>
       <c r="K28" t="n">
-        <v>61.46</v>
+        <v>65.11</v>
       </c>
       <c r="L28" t="n">
-        <v>96.90000000000001</v>
+        <v>102.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-18.43</v>
+        <v>-19.46</v>
       </c>
       <c r="K29" t="n">
-        <v>21.38</v>
+        <v>22.58</v>
       </c>
       <c r="L29" t="n">
-        <v>28.23</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.07</v>
+        <v>-38.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-12.41</v>
+        <v>-12.33</v>
       </c>
       <c r="L30" t="n">
-        <v>41</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>40.77</v>
+        <v>40.17</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.35</v>
+        <v>-1.33</v>
       </c>
       <c r="L31" t="n">
-        <v>40.79</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>22.59</v>
+        <v>22.55</v>
       </c>
       <c r="K32" t="n">
-        <v>48.07</v>
+        <v>47.97</v>
       </c>
       <c r="L32" t="n">
-        <v>53.12</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.61</v>
+        <v>-4.64</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.4</v>
+        <v>-46.69</v>
       </c>
       <c r="L33" t="n">
-        <v>46.63</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>32.18</v>
+        <v>32.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-45.11</v>
+        <v>-44.99</v>
       </c>
       <c r="L34" t="n">
-        <v>55.41</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>28.14</v>
+        <v>28.8</v>
       </c>
       <c r="K35" t="n">
-        <v>-53.51</v>
+        <v>-54.76</v>
       </c>
       <c r="L35" t="n">
-        <v>60.46</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-84.45</v>
+        <v>-84.11</v>
       </c>
       <c r="K36" t="n">
-        <v>-24.53</v>
+        <v>-24.43</v>
       </c>
       <c r="L36" t="n">
-        <v>87.94</v>
+        <v>87.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>83.54000000000001</v>
+        <v>82.75</v>
       </c>
       <c r="K37" t="n">
-        <v>57.9</v>
+        <v>57.35</v>
       </c>
       <c r="L37" t="n">
-        <v>101.64</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>18.4</v>
+        <v>20.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-51.9</v>
+        <v>-56.86</v>
       </c>
       <c r="L38" t="n">
-        <v>55.07</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-18.42</v>
+        <v>-18.05</v>
       </c>
       <c r="K39" t="n">
-        <v>14.21</v>
+        <v>13.93</v>
       </c>
       <c r="L39" t="n">
-        <v>23.27</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>81.78</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-101.37</v>
+        <v>-98.63</v>
       </c>
       <c r="L40" t="n">
-        <v>130.25</v>
+        <v>126.72</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>50.6</v>
+        <v>53.45</v>
       </c>
       <c r="K41" t="n">
-        <v>-99.73</v>
+        <v>-105.34</v>
       </c>
       <c r="L41" t="n">
-        <v>111.84</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-96</v>
+        <v>-95.73</v>
       </c>
       <c r="K42" t="n">
-        <v>112.67</v>
+        <v>112.35</v>
       </c>
       <c r="L42" t="n">
-        <v>148.02</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-35.02</v>
+        <v>-37.02</v>
       </c>
       <c r="K43" t="n">
-        <v>104.23</v>
+        <v>110.19</v>
       </c>
       <c r="L43" t="n">
-        <v>109.96</v>
+        <v>116.24</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>69.61</v>
+        <v>65.86</v>
       </c>
       <c r="K44" t="n">
-        <v>11.59</v>
+        <v>10.97</v>
       </c>
       <c r="L44" t="n">
-        <v>70.56999999999999</v>
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1945,10 +1945,10 @@
         <v>0.11</v>
       </c>
       <c r="K45" t="n">
-        <v>21.73</v>
+        <v>23.61</v>
       </c>
       <c r="L45" t="n">
-        <v>21.73</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-35.37</v>
+        <v>-33.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-57.84</v>
+        <v>-54.94</v>
       </c>
       <c r="L46" t="n">
-        <v>67.8</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>75.37</v>
+        <v>72.13</v>
       </c>
       <c r="K47" t="n">
-        <v>34.55</v>
+        <v>33.07</v>
       </c>
       <c r="L47" t="n">
-        <v>82.91</v>
+        <v>79.34999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-64.73999999999999</v>
+        <v>-63.26</v>
       </c>
       <c r="K48" t="n">
-        <v>28.13</v>
+        <v>27.49</v>
       </c>
       <c r="L48" t="n">
-        <v>70.58</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.35</v>
+        <v>-41.72</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.2</v>
+        <v>-13.65</v>
       </c>
       <c r="L49" t="n">
-        <v>42.46</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-86.81999999999999</v>
+        <v>-83.65000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>67.59999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="L50" t="n">
-        <v>110.04</v>
+        <v>106.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.87</v>
+        <v>-4.65</v>
       </c>
       <c r="K51" t="n">
-        <v>131.59</v>
+        <v>125.69</v>
       </c>
       <c r="L51" t="n">
-        <v>131.68</v>
+        <v>125.78</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>44.99</v>
+        <v>43.87</v>
       </c>
       <c r="K52" t="n">
-        <v>94.20999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="L52" t="n">
-        <v>104.4</v>
+        <v>101.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-13.52</v>
+        <v>-13.34</v>
       </c>
       <c r="K53" t="n">
-        <v>108.88</v>
+        <v>107.44</v>
       </c>
       <c r="L53" t="n">
-        <v>109.72</v>
+        <v>108.26</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.29</v>
+        <v>-29.21</v>
       </c>
       <c r="K54" t="n">
-        <v>-94.56</v>
+        <v>-94.31999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>98.98999999999999</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-98.73999999999999</v>
+        <v>-98.48</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.12</v>
+        <v>-12.08</v>
       </c>
       <c r="L55" t="n">
-        <v>99.48</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>119.98</v>
+        <v>119.68</v>
       </c>
       <c r="K56" t="n">
-        <v>110.99</v>
+        <v>110.72</v>
       </c>
       <c r="L56" t="n">
-        <v>163.45</v>
+        <v>163.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-152.12</v>
+        <v>-149.34</v>
       </c>
       <c r="K57" t="n">
-        <v>-76.27</v>
+        <v>-74.88</v>
       </c>
       <c r="L57" t="n">
-        <v>170.16</v>
+        <v>167.06</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>104.1</v>
+        <v>103.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-121.5</v>
+        <v>-121</v>
       </c>
       <c r="L58" t="n">
-        <v>159.99</v>
+        <v>159.33</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.71</v>
+        <v>-14.29</v>
       </c>
       <c r="K59" t="n">
-        <v>26.56</v>
+        <v>27.67</v>
       </c>
       <c r="L59" t="n">
-        <v>29.89</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>43.83</v>
+        <v>42.65</v>
       </c>
       <c r="K60" t="n">
-        <v>-27.84</v>
+        <v>-27.09</v>
       </c>
       <c r="L60" t="n">
-        <v>51.92</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>48.65</v>
+        <v>47.35</v>
       </c>
       <c r="K61" t="n">
-        <v>13.57</v>
+        <v>13.21</v>
       </c>
       <c r="L61" t="n">
-        <v>50.51</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>23.27</v>
+        <v>22.9</v>
       </c>
       <c r="K62" t="n">
-        <v>-54.84</v>
+        <v>-53.96</v>
       </c>
       <c r="L62" t="n">
-        <v>59.57</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>14.74</v>
+        <v>14.09</v>
       </c>
       <c r="K63" t="n">
-        <v>-75.89</v>
+        <v>-72.52</v>
       </c>
       <c r="L63" t="n">
-        <v>77.31</v>
+        <v>73.87</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.55</v>
+        <v>-29.49</v>
       </c>
       <c r="K64" t="n">
-        <v>64.38</v>
+        <v>62.15</v>
       </c>
       <c r="L64" t="n">
-        <v>71.26000000000001</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.26000000000001</v>
+        <v>-74.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-19.08</v>
+        <v>-19.26</v>
       </c>
       <c r="L65" t="n">
-        <v>76.67</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-72.95999999999999</v>
+        <v>-73.25</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.8</v>
+        <v>-18.87</v>
       </c>
       <c r="L66" t="n">
-        <v>75.34</v>
+        <v>75.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.29</v>
+        <v>-3.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-61.44</v>
+        <v>-63.7</v>
       </c>
       <c r="L67" t="n">
-        <v>61.53</v>
+        <v>63.79</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-115.24</v>
+        <v>-112.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-46.44</v>
+        <v>-45.17</v>
       </c>
       <c r="L68" t="n">
-        <v>124.25</v>
+        <v>120.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-48.16</v>
+        <v>-49.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-60.81</v>
+        <v>-62.76</v>
       </c>
       <c r="L69" t="n">
-        <v>77.56999999999999</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>11.11</v>
+        <v>10.69</v>
       </c>
       <c r="K70" t="n">
-        <v>-135.96</v>
+        <v>-130.78</v>
       </c>
       <c r="L70" t="n">
-        <v>136.41</v>
+        <v>131.22</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>109.71</v>
+        <v>109.8</v>
       </c>
       <c r="K71" t="n">
-        <v>105.67</v>
+        <v>105.76</v>
       </c>
       <c r="L71" t="n">
-        <v>152.32</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-94.5</v>
+        <v>-101.61</v>
       </c>
       <c r="K72" t="n">
-        <v>21.15</v>
+        <v>22.74</v>
       </c>
       <c r="L72" t="n">
-        <v>96.84</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>38.66</v>
+        <v>38.2</v>
       </c>
       <c r="K73" t="n">
-        <v>156.94</v>
+        <v>155.1</v>
       </c>
       <c r="L73" t="n">
-        <v>161.64</v>
+        <v>159.73</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-29.72</v>
+        <v>-31.21</v>
       </c>
       <c r="K74" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="L74" t="n">
-        <v>29.72</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.33</v>
+        <v>-29.85</v>
       </c>
       <c r="K75" t="n">
-        <v>31.04</v>
+        <v>30.55</v>
       </c>
       <c r="L75" t="n">
-        <v>43.4</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>52.71</v>
+        <v>50.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-49.03</v>
+        <v>-47.21</v>
       </c>
       <c r="L76" t="n">
-        <v>71.98999999999999</v>
+        <v>69.31999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.73</v>
+        <v>-11.69</v>
       </c>
       <c r="K77" t="n">
-        <v>55.66</v>
+        <v>55.45</v>
       </c>
       <c r="L77" t="n">
-        <v>56.89</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>29.99</v>
+        <v>29.5</v>
       </c>
       <c r="K78" t="n">
-        <v>54.71</v>
+        <v>53.83</v>
       </c>
       <c r="L78" t="n">
-        <v>62.39</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.61</v>
+        <v>-0.6</v>
       </c>
       <c r="K79" t="n">
-        <v>66.58</v>
+        <v>65.56</v>
       </c>
       <c r="L79" t="n">
-        <v>66.58</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>51.96</v>
+        <v>55.1</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.29</v>
+        <v>-6.67</v>
       </c>
       <c r="L80" t="n">
-        <v>52.34</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>43.22</v>
+        <v>45.43</v>
       </c>
       <c r="K81" t="n">
-        <v>-28.16</v>
+        <v>-29.61</v>
       </c>
       <c r="L81" t="n">
-        <v>51.59</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-48.77</v>
+        <v>-47.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-94.22</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>106.09</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-27.26</v>
+        <v>-26.02</v>
       </c>
       <c r="K83" t="n">
-        <v>167.87</v>
+        <v>160.29</v>
       </c>
       <c r="L83" t="n">
-        <v>170.07</v>
+        <v>162.39</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>5.77</v>
+        <v>6.07</v>
       </c>
       <c r="K84" t="n">
-        <v>69.18000000000001</v>
+        <v>72.83</v>
       </c>
       <c r="L84" t="n">
-        <v>69.42</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.36</v>
+        <v>-91.67</v>
       </c>
       <c r="K85" t="n">
-        <v>30.01</v>
+        <v>30.44</v>
       </c>
       <c r="L85" t="n">
-        <v>95.20999999999999</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-66.25</v>
+        <v>-68.95</v>
       </c>
       <c r="K86" t="n">
-        <v>107.31</v>
+        <v>111.68</v>
       </c>
       <c r="L86" t="n">
-        <v>126.12</v>
+        <v>131.26</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>102.72</v>
+        <v>106.8</v>
       </c>
       <c r="K87" t="n">
-        <v>-59.93</v>
+        <v>-62.32</v>
       </c>
       <c r="L87" t="n">
-        <v>118.92</v>
+        <v>123.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>151.22</v>
+        <v>151.28</v>
       </c>
       <c r="K88" t="n">
-        <v>45.67</v>
+        <v>45.69</v>
       </c>
       <c r="L88" t="n">
-        <v>157.96</v>
+        <v>158.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>30.51</v>
+        <v>31.31</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.76</v>
+        <v>-10.01</v>
       </c>
       <c r="L14" t="n">
-        <v>32.03</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.59</v>
+        <v>-22.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-23.69</v>
+        <v>-24.37</v>
       </c>
       <c r="L15" t="n">
-        <v>32.06</v>
+        <v>32.97</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>41.41</v>
+        <v>40.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.99</v>
+        <v>-21.39</v>
       </c>
       <c r="L16" t="n">
-        <v>46.89</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.35</v>
+        <v>-34.66</v>
       </c>
       <c r="K17" t="n">
-        <v>32.22</v>
+        <v>33.49</v>
       </c>
       <c r="L17" t="n">
-        <v>46.37</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-19.75</v>
+        <v>-20.78</v>
       </c>
       <c r="K18" t="n">
-        <v>30.87</v>
+        <v>32.47</v>
       </c>
       <c r="L18" t="n">
-        <v>36.65</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.81</v>
+        <v>-28.14</v>
       </c>
       <c r="K19" t="n">
-        <v>55.28</v>
+        <v>54</v>
       </c>
       <c r="L19" t="n">
-        <v>62.33</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>77.52</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>54.18</v>
+        <v>52.82</v>
       </c>
       <c r="L20" t="n">
-        <v>94.56999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>22.07</v>
+        <v>23.41</v>
       </c>
       <c r="K21" t="n">
-        <v>-52.23</v>
+        <v>-55.4</v>
       </c>
       <c r="L21" t="n">
-        <v>56.7</v>
+        <v>60.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>93.39</v>
+        <v>89.56</v>
       </c>
       <c r="K22" t="n">
-        <v>-48.84</v>
+        <v>-46.84</v>
       </c>
       <c r="L22" t="n">
-        <v>105.39</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-59.51</v>
+        <v>-65.2</v>
       </c>
       <c r="K23" t="n">
-        <v>24.55</v>
+        <v>26.9</v>
       </c>
       <c r="L23" t="n">
-        <v>64.37</v>
+        <v>70.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>78.34</v>
+        <v>79.75</v>
       </c>
       <c r="K24" t="n">
-        <v>-54.25</v>
+        <v>-55.23</v>
       </c>
       <c r="L24" t="n">
-        <v>95.29000000000001</v>
+        <v>97.01000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>149.81</v>
+        <v>138.58</v>
       </c>
       <c r="K25" t="n">
-        <v>133.81</v>
+        <v>123.79</v>
       </c>
       <c r="L25" t="n">
-        <v>200.87</v>
+        <v>185.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-157.46</v>
+        <v>-155.42</v>
       </c>
       <c r="K26" t="n">
-        <v>27.96</v>
+        <v>27.59</v>
       </c>
       <c r="L26" t="n">
-        <v>159.92</v>
+        <v>157.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.99</v>
+        <v>-14.79</v>
       </c>
       <c r="K27" t="n">
-        <v>120.94</v>
+        <v>127.84</v>
       </c>
       <c r="L27" t="n">
-        <v>121.74</v>
+        <v>128.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>79.37</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>65.11</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>102.66</v>
+        <v>109.24</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-19.46</v>
+        <v>-20.64</v>
       </c>
       <c r="K29" t="n">
-        <v>22.58</v>
+        <v>23.94</v>
       </c>
       <c r="L29" t="n">
-        <v>29.81</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.82</v>
+        <v>-38.54</v>
       </c>
       <c r="K30" t="n">
-        <v>-12.33</v>
+        <v>-12.24</v>
       </c>
       <c r="L30" t="n">
-        <v>40.73</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>40.17</v>
+        <v>39.49</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.33</v>
+        <v>-1.31</v>
       </c>
       <c r="L31" t="n">
-        <v>40.19</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>22.55</v>
+        <v>22.49</v>
       </c>
       <c r="K32" t="n">
-        <v>47.97</v>
+        <v>47.86</v>
       </c>
       <c r="L32" t="n">
-        <v>53.01</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.64</v>
+        <v>-4.67</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.69</v>
+        <v>-47.02</v>
       </c>
       <c r="L33" t="n">
-        <v>46.92</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>32.09</v>
+        <v>31.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-44.99</v>
+        <v>-44.84</v>
       </c>
       <c r="L34" t="n">
-        <v>55.26</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>28.8</v>
+        <v>29.55</v>
       </c>
       <c r="K35" t="n">
-        <v>-54.76</v>
+        <v>-56.18</v>
       </c>
       <c r="L35" t="n">
-        <v>61.87</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-84.11</v>
+        <v>-83.73</v>
       </c>
       <c r="K36" t="n">
-        <v>-24.43</v>
+        <v>-24.32</v>
       </c>
       <c r="L36" t="n">
-        <v>87.59</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>82.75</v>
+        <v>81.84</v>
       </c>
       <c r="K37" t="n">
-        <v>57.35</v>
+        <v>56.72</v>
       </c>
       <c r="L37" t="n">
-        <v>100.68</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>20.16</v>
+        <v>22.17</v>
       </c>
       <c r="K38" t="n">
-        <v>-56.86</v>
+        <v>-62.52</v>
       </c>
       <c r="L38" t="n">
-        <v>60.33</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-18.05</v>
+        <v>-19.5</v>
       </c>
       <c r="K39" t="n">
-        <v>13.93</v>
+        <v>15.04</v>
       </c>
       <c r="L39" t="n">
-        <v>22.8</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>79.56999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-98.63</v>
+        <v>-95.48999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>126.72</v>
+        <v>122.69</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>53.45</v>
+        <v>56.71</v>
       </c>
       <c r="K41" t="n">
-        <v>-105.34</v>
+        <v>-111.76</v>
       </c>
       <c r="L41" t="n">
-        <v>118.13</v>
+        <v>125.32</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-95.73</v>
+        <v>-95.42</v>
       </c>
       <c r="K42" t="n">
-        <v>112.35</v>
+        <v>111.98</v>
       </c>
       <c r="L42" t="n">
-        <v>147.6</v>
+        <v>147.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-37.02</v>
+        <v>-39.31</v>
       </c>
       <c r="K43" t="n">
-        <v>110.19</v>
+        <v>116.99</v>
       </c>
       <c r="L43" t="n">
-        <v>116.24</v>
+        <v>123.42</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>65.86</v>
+        <v>61.57</v>
       </c>
       <c r="K44" t="n">
-        <v>10.97</v>
+        <v>10.26</v>
       </c>
       <c r="L44" t="n">
-        <v>66.76000000000001</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="K45" t="n">
-        <v>23.61</v>
+        <v>25.76</v>
       </c>
       <c r="L45" t="n">
-        <v>23.61</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-33.59</v>
+        <v>-31.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.94</v>
+        <v>-51.62</v>
       </c>
       <c r="L46" t="n">
-        <v>64.40000000000001</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>72.13</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>33.07</v>
+        <v>31.37</v>
       </c>
       <c r="L47" t="n">
-        <v>79.34999999999999</v>
+        <v>75.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-63.26</v>
+        <v>-61.58</v>
       </c>
       <c r="K48" t="n">
-        <v>27.49</v>
+        <v>26.75</v>
       </c>
       <c r="L48" t="n">
-        <v>68.98</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.72</v>
+        <v>-43.29</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.65</v>
+        <v>-14.17</v>
       </c>
       <c r="L49" t="n">
-        <v>43.9</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-83.65000000000001</v>
+        <v>-80.01000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>65.13</v>
+        <v>62.3</v>
       </c>
       <c r="L50" t="n">
-        <v>106.01</v>
+        <v>101.41</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.65</v>
+        <v>-4.4</v>
       </c>
       <c r="K51" t="n">
-        <v>125.69</v>
+        <v>118.95</v>
       </c>
       <c r="L51" t="n">
-        <v>125.78</v>
+        <v>119.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>43.87</v>
+        <v>42.58</v>
       </c>
       <c r="K52" t="n">
-        <v>91.86</v>
+        <v>89.17</v>
       </c>
       <c r="L52" t="n">
-        <v>101.79</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-13.34</v>
+        <v>-13.13</v>
       </c>
       <c r="K53" t="n">
-        <v>107.44</v>
+        <v>105.79</v>
       </c>
       <c r="L53" t="n">
-        <v>108.26</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.21</v>
+        <v>-29.13</v>
       </c>
       <c r="K54" t="n">
-        <v>-94.31999999999999</v>
+        <v>-94.04000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>98.73999999999999</v>
+        <v>98.45</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-98.48</v>
+        <v>-98.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.08</v>
+        <v>-12.05</v>
       </c>
       <c r="L55" t="n">
-        <v>99.20999999999999</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>119.68</v>
+        <v>119.34</v>
       </c>
       <c r="K56" t="n">
-        <v>110.72</v>
+        <v>110.41</v>
       </c>
       <c r="L56" t="n">
-        <v>163.04</v>
+        <v>162.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-149.34</v>
+        <v>-146.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-74.88</v>
+        <v>-73.29000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>167.06</v>
+        <v>163.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>103.66</v>
+        <v>103.17</v>
       </c>
       <c r="K58" t="n">
-        <v>-121</v>
+        <v>-120.42</v>
       </c>
       <c r="L58" t="n">
-        <v>159.33</v>
+        <v>158.57</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.29</v>
+        <v>-14.94</v>
       </c>
       <c r="K59" t="n">
-        <v>27.67</v>
+        <v>28.95</v>
       </c>
       <c r="L59" t="n">
-        <v>31.14</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>42.65</v>
+        <v>41.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-27.09</v>
+        <v>-26.23</v>
       </c>
       <c r="L60" t="n">
-        <v>50.52</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>47.35</v>
+        <v>45.87</v>
       </c>
       <c r="K61" t="n">
-        <v>13.21</v>
+        <v>12.8</v>
       </c>
       <c r="L61" t="n">
-        <v>49.16</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>22.9</v>
+        <v>22.47</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.96</v>
+        <v>-52.96</v>
       </c>
       <c r="L62" t="n">
-        <v>58.62</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>14.09</v>
+        <v>13.34</v>
       </c>
       <c r="K63" t="n">
-        <v>-72.52</v>
+        <v>-68.67</v>
       </c>
       <c r="L63" t="n">
-        <v>73.87</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.49</v>
+        <v>-28.28</v>
       </c>
       <c r="K64" t="n">
-        <v>62.15</v>
+        <v>59.6</v>
       </c>
       <c r="L64" t="n">
-        <v>68.79000000000001</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.98</v>
+        <v>-75.8</v>
       </c>
       <c r="K65" t="n">
-        <v>-19.26</v>
+        <v>-19.47</v>
       </c>
       <c r="L65" t="n">
-        <v>77.41</v>
+        <v>78.26000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-73.25</v>
+        <v>-73.58</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.87</v>
+        <v>-18.96</v>
       </c>
       <c r="L66" t="n">
-        <v>75.64</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.41</v>
+        <v>-3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-63.7</v>
+        <v>-66.28</v>
       </c>
       <c r="L67" t="n">
-        <v>63.79</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-112.12</v>
+        <v>-108.54</v>
       </c>
       <c r="K68" t="n">
-        <v>-45.17</v>
+        <v>-43.73</v>
       </c>
       <c r="L68" t="n">
-        <v>120.88</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.71</v>
+        <v>-51.47</v>
       </c>
       <c r="K69" t="n">
-        <v>-62.76</v>
+        <v>-65</v>
       </c>
       <c r="L69" t="n">
-        <v>80.06</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>10.69</v>
+        <v>10.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-130.78</v>
+        <v>-124.86</v>
       </c>
       <c r="L70" t="n">
-        <v>131.22</v>
+        <v>125.28</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>109.8</v>
+        <v>109.91</v>
       </c>
       <c r="K71" t="n">
-        <v>105.76</v>
+        <v>105.86</v>
       </c>
       <c r="L71" t="n">
-        <v>152.45</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-101.61</v>
+        <v>-109.73</v>
       </c>
       <c r="K72" t="n">
-        <v>22.74</v>
+        <v>24.56</v>
       </c>
       <c r="L72" t="n">
-        <v>104.12</v>
+        <v>112.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>38.2</v>
+        <v>37.68</v>
       </c>
       <c r="K73" t="n">
-        <v>155.1</v>
+        <v>152.99</v>
       </c>
       <c r="L73" t="n">
-        <v>159.73</v>
+        <v>157.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-31.21</v>
+        <v>-32.92</v>
       </c>
       <c r="K74" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="L74" t="n">
-        <v>31.21</v>
+        <v>32.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-29.85</v>
+        <v>-29.3</v>
       </c>
       <c r="K75" t="n">
-        <v>30.55</v>
+        <v>29.98</v>
       </c>
       <c r="L75" t="n">
-        <v>42.71</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>50.76</v>
+        <v>48.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.21</v>
+        <v>-45.14</v>
       </c>
       <c r="L76" t="n">
-        <v>69.31999999999999</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.69</v>
+        <v>-11.64</v>
       </c>
       <c r="K77" t="n">
-        <v>55.45</v>
+        <v>55.2</v>
       </c>
       <c r="L77" t="n">
-        <v>56.66</v>
+        <v>56.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>29.5</v>
+        <v>28.95</v>
       </c>
       <c r="K78" t="n">
-        <v>53.83</v>
+        <v>52.82</v>
       </c>
       <c r="L78" t="n">
-        <v>61.38</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="K79" t="n">
-        <v>65.56</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>65.56999999999999</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>55.1</v>
+        <v>58.69</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.67</v>
+        <v>-7.11</v>
       </c>
       <c r="L80" t="n">
-        <v>55.5</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>45.43</v>
+        <v>47.96</v>
       </c>
       <c r="K81" t="n">
-        <v>-29.61</v>
+        <v>-31.26</v>
       </c>
       <c r="L81" t="n">
-        <v>54.23</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-47.44</v>
+        <v>-45.92</v>
       </c>
       <c r="K82" t="n">
-        <v>-91.65000000000001</v>
+        <v>-88.70999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-26.02</v>
+        <v>-24.62</v>
       </c>
       <c r="K83" t="n">
-        <v>160.29</v>
+        <v>151.62</v>
       </c>
       <c r="L83" t="n">
-        <v>162.39</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>6.07</v>
+        <v>6.42</v>
       </c>
       <c r="K84" t="n">
-        <v>72.83</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>73.08</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-91.67</v>
+        <v>-93.17</v>
       </c>
       <c r="K85" t="n">
-        <v>30.44</v>
+        <v>30.94</v>
       </c>
       <c r="L85" t="n">
-        <v>96.59999999999999</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-68.95</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>111.68</v>
+        <v>116.68</v>
       </c>
       <c r="L86" t="n">
-        <v>131.26</v>
+        <v>137.13</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>106.8</v>
+        <v>111.47</v>
       </c>
       <c r="K87" t="n">
-        <v>-62.32</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>123.65</v>
+        <v>129.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>151.28</v>
+        <v>151.35</v>
       </c>
       <c r="K88" t="n">
-        <v>45.69</v>
+        <v>45.71</v>
       </c>
       <c r="L88" t="n">
-        <v>158.03</v>
+        <v>158.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="F14" t="n">
-        <v>5.56</v>
+        <v>6.09</v>
       </c>
       <c r="G14" t="n">
-        <v>85.5</v>
+        <v>96.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>31.31</v>
+        <v>-32.94</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.01</v>
+        <v>-36.88</v>
       </c>
       <c r="L14" t="n">
-        <v>32.88</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:31:12</t>
+          <t>06:31:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="F15" t="n">
-        <v>5.28</v>
+        <v>3.92</v>
       </c>
       <c r="G15" t="n">
-        <v>97.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-22.21</v>
+        <v>-19.61</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.37</v>
+        <v>60.41</v>
       </c>
       <c r="L15" t="n">
-        <v>32.97</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:32:43</t>
+          <t>06:32:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="n">
-        <v>5.72</v>
+        <v>6.09</v>
       </c>
       <c r="G16" t="n">
-        <v>112.7</v>
+        <v>108.9</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>40.29</v>
+        <v>-34.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.39</v>
+        <v>32.61</v>
       </c>
       <c r="L16" t="n">
-        <v>45.61</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:36:58</t>
+          <t>06:37:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="F17" t="n">
-        <v>5.89</v>
+        <v>1.97</v>
       </c>
       <c r="G17" t="n">
-        <v>83.2</v>
+        <v>100.3</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-34.66</v>
+        <v>21.68</v>
       </c>
       <c r="K17" t="n">
-        <v>33.49</v>
+        <v>-53.59</v>
       </c>
       <c r="L17" t="n">
-        <v>48.2</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:37:52</t>
+          <t>06:39:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="F18" t="n">
-        <v>5.83</v>
+        <v>5.7</v>
       </c>
       <c r="G18" t="n">
-        <v>98.59999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.78</v>
+        <v>-39.53</v>
       </c>
       <c r="K18" t="n">
-        <v>32.47</v>
+        <v>77.33</v>
       </c>
       <c r="L18" t="n">
-        <v>38.55</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:39:38</t>
+          <t>06:41:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="F19" t="n">
-        <v>5.51</v>
+        <v>3.9</v>
       </c>
       <c r="G19" t="n">
-        <v>100.4</v>
+        <v>105.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.14</v>
+        <v>63.55</v>
       </c>
       <c r="K19" t="n">
-        <v>54</v>
+        <v>9.27</v>
       </c>
       <c r="L19" t="n">
-        <v>60.9</v>
+        <v>64.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:44:24</t>
+          <t>06:46:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="F20" t="n">
-        <v>5.06</v>
+        <v>2.29</v>
       </c>
       <c r="G20" t="n">
-        <v>101.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>75.56999999999999</v>
+        <v>29.88</v>
       </c>
       <c r="K20" t="n">
-        <v>52.82</v>
+        <v>-58.94</v>
       </c>
       <c r="L20" t="n">
-        <v>92.2</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:46:05</t>
+          <t>06:47:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="F21" t="n">
-        <v>5.43</v>
+        <v>6.09</v>
       </c>
       <c r="G21" t="n">
-        <v>104.2</v>
+        <v>101.8</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>23.41</v>
+        <v>32.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-55.4</v>
+        <v>130.28</v>
       </c>
       <c r="L21" t="n">
-        <v>60.14</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:48:16</t>
+          <t>06:49:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="F22" t="n">
-        <v>5.51</v>
+        <v>6.09</v>
       </c>
       <c r="G22" t="n">
-        <v>105.8</v>
+        <v>89.2</v>
       </c>
       <c r="H22" t="n">
-        <v>10.7</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>89.56</v>
+        <v>-72.63</v>
       </c>
       <c r="K22" t="n">
-        <v>-46.84</v>
+        <v>-40.72</v>
       </c>
       <c r="L22" t="n">
-        <v>101.07</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:52:44</t>
+          <t>06:54:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="F23" t="n">
-        <v>5.87</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
-        <v>89.2</v>
+        <v>101.7</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-65.2</v>
+        <v>100.62</v>
       </c>
       <c r="K23" t="n">
-        <v>26.9</v>
+        <v>-64.86</v>
       </c>
       <c r="L23" t="n">
-        <v>70.53</v>
+        <v>119.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:54:10</t>
+          <t>06:55:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="F24" t="n">
-        <v>5.53</v>
+        <v>5.09</v>
       </c>
       <c r="G24" t="n">
-        <v>103.4</v>
+        <v>92.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>79.75</v>
+        <v>-36.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-55.23</v>
+        <v>169.33</v>
       </c>
       <c r="L24" t="n">
-        <v>97.01000000000001</v>
+        <v>173.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:55:13</t>
+          <t>06:57:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="F25" t="n">
-        <v>5.43</v>
+        <v>6.09</v>
       </c>
       <c r="G25" t="n">
-        <v>92.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>138.58</v>
+        <v>114.94</v>
       </c>
       <c r="K25" t="n">
-        <v>123.79</v>
+        <v>-16.25</v>
       </c>
       <c r="L25" t="n">
-        <v>185.82</v>
+        <v>116.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:00:29</t>
+          <t>07:02:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="F26" t="n">
-        <v>5.35</v>
+        <v>4.15</v>
       </c>
       <c r="G26" t="n">
-        <v>94.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-155.42</v>
+        <v>146.58</v>
       </c>
       <c r="K26" t="n">
-        <v>27.59</v>
+        <v>-49.71</v>
       </c>
       <c r="L26" t="n">
-        <v>157.85</v>
+        <v>154.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:02:21</t>
+          <t>07:04:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="F27" t="n">
-        <v>5.86</v>
+        <v>6.09</v>
       </c>
       <c r="G27" t="n">
-        <v>101.5</v>
+        <v>90.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.79</v>
+        <v>159.47</v>
       </c>
       <c r="K27" t="n">
-        <v>127.84</v>
+        <v>96.27</v>
       </c>
       <c r="L27" t="n">
-        <v>128.69</v>
+        <v>186.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:03:45</t>
+          <t>07:06:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="F28" t="n">
-        <v>4.95</v>
+        <v>3.64</v>
       </c>
       <c r="G28" t="n">
-        <v>114.7</v>
+        <v>99.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>84.45999999999999</v>
+        <v>-166.49</v>
       </c>
       <c r="K28" t="n">
-        <v>69.29000000000001</v>
+        <v>-60.27</v>
       </c>
       <c r="L28" t="n">
-        <v>109.24</v>
+        <v>177.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:16:27</t>
+          <t>07:15:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="F29" t="n">
-        <v>4.79</v>
+        <v>6.09</v>
       </c>
       <c r="G29" t="n">
-        <v>99.5</v>
+        <v>100.1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-20.64</v>
+        <v>-53.67</v>
       </c>
       <c r="K29" t="n">
-        <v>23.94</v>
+        <v>-17.15</v>
       </c>
       <c r="L29" t="n">
-        <v>31.61</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:17:55</t>
+          <t>07:17:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5.45</v>
+        <v>2.66</v>
       </c>
       <c r="G30" t="n">
-        <v>102.4</v>
+        <v>101.8</v>
       </c>
       <c r="H30" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.54</v>
+        <v>23.93</v>
       </c>
       <c r="K30" t="n">
-        <v>-12.24</v>
+        <v>33.54</v>
       </c>
       <c r="L30" t="n">
-        <v>40.43</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:20:21</t>
+          <t>07:18:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="F31" t="n">
-        <v>5.63</v>
+        <v>5.23</v>
       </c>
       <c r="G31" t="n">
-        <v>101.8</v>
+        <v>89.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>39.49</v>
+        <v>-36</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.31</v>
+        <v>29.17</v>
       </c>
       <c r="L31" t="n">
-        <v>39.51</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:25:09</t>
+          <t>07:22:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="F32" t="n">
-        <v>4.98</v>
+        <v>1.85</v>
       </c>
       <c r="G32" t="n">
-        <v>111.3</v>
+        <v>96.7</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>22.49</v>
+        <v>-10.76</v>
       </c>
       <c r="K32" t="n">
-        <v>47.86</v>
+        <v>52.33</v>
       </c>
       <c r="L32" t="n">
-        <v>52.88</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:26:13</t>
+          <t>07:24:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.19</v>
+        <v>1.59</v>
       </c>
       <c r="F33" t="n">
-        <v>5.71</v>
+        <v>2.99</v>
       </c>
       <c r="G33" t="n">
-        <v>95.2</v>
+        <v>87</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.67</v>
+        <v>92.69</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.02</v>
+        <v>15.73</v>
       </c>
       <c r="L33" t="n">
-        <v>47.25</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:28:36</t>
+          <t>07:26:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="F34" t="n">
-        <v>6.37</v>
+        <v>2.81</v>
       </c>
       <c r="G34" t="n">
-        <v>96.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>31.98</v>
+        <v>5.56</v>
       </c>
       <c r="K34" t="n">
-        <v>-44.84</v>
+        <v>108.05</v>
       </c>
       <c r="L34" t="n">
-        <v>55.08</v>
+        <v>108.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:32:54</t>
+          <t>07:31:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="F35" t="n">
-        <v>6.72</v>
+        <v>3.09</v>
       </c>
       <c r="G35" t="n">
-        <v>98.3</v>
+        <v>90.3</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>29.55</v>
+        <v>84.02</v>
       </c>
       <c r="K35" t="n">
-        <v>-56.18</v>
+        <v>72.87</v>
       </c>
       <c r="L35" t="n">
-        <v>63.48</v>
+        <v>111.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:34:49</t>
+          <t>07:32:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="F36" t="n">
-        <v>5.89</v>
+        <v>6.09</v>
       </c>
       <c r="G36" t="n">
-        <v>95.5</v>
+        <v>99.5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-83.73</v>
+        <v>-87.51000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-24.32</v>
+        <v>-64.55</v>
       </c>
       <c r="L36" t="n">
-        <v>87.19</v>
+        <v>108.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:36:17</t>
+          <t>07:34:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.53</v>
+        <v>1.44</v>
       </c>
       <c r="F37" t="n">
-        <v>5.21</v>
+        <v>6.09</v>
       </c>
       <c r="G37" t="n">
-        <v>90.5</v>
+        <v>107</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>81.84</v>
+        <v>62.84</v>
       </c>
       <c r="K37" t="n">
-        <v>56.72</v>
+        <v>81.25</v>
       </c>
       <c r="L37" t="n">
-        <v>99.56999999999999</v>
+        <v>102.71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:41:42</t>
+          <t>07:38:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="F38" t="n">
-        <v>5.7</v>
+        <v>5.54</v>
       </c>
       <c r="G38" t="n">
-        <v>102.6</v>
+        <v>109</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>22.17</v>
+        <v>-78.83</v>
       </c>
       <c r="K38" t="n">
-        <v>-62.52</v>
+        <v>119.71</v>
       </c>
       <c r="L38" t="n">
-        <v>66.34</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:43:28</t>
+          <t>07:40:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="F39" t="n">
-        <v>4.68</v>
+        <v>3.84</v>
       </c>
       <c r="G39" t="n">
-        <v>107.8</v>
+        <v>99</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-19.5</v>
+        <v>-26.56</v>
       </c>
       <c r="K39" t="n">
-        <v>15.04</v>
+        <v>151.16</v>
       </c>
       <c r="L39" t="n">
-        <v>24.63</v>
+        <v>153.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:44:39</t>
+          <t>07:42:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="F40" t="n">
-        <v>6.11</v>
+        <v>2.33</v>
       </c>
       <c r="G40" t="n">
-        <v>93.40000000000001</v>
+        <v>100.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>77.04000000000001</v>
+        <v>-98.86</v>
       </c>
       <c r="K40" t="n">
-        <v>-95.48999999999999</v>
+        <v>13.09</v>
       </c>
       <c r="L40" t="n">
-        <v>122.69</v>
+        <v>99.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:49:57</t>
+          <t>07:46:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="F41" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="G41" t="n">
-        <v>98.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>56.71</v>
+        <v>137.81</v>
       </c>
       <c r="K41" t="n">
-        <v>-111.76</v>
+        <v>124.98</v>
       </c>
       <c r="L41" t="n">
-        <v>125.32</v>
+        <v>186.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:51:19</t>
+          <t>07:49:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="F42" t="n">
-        <v>5.54</v>
+        <v>6.09</v>
       </c>
       <c r="G42" t="n">
-        <v>101</v>
+        <v>97.3</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-95.42</v>
+        <v>-139.77</v>
       </c>
       <c r="K42" t="n">
-        <v>111.98</v>
+        <v>55.33</v>
       </c>
       <c r="L42" t="n">
-        <v>147.12</v>
+        <v>150.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:53:27</t>
+          <t>07:50:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="F43" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="G43" t="n">
-        <v>98.7</v>
+        <v>103</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-39.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>116.99</v>
+        <v>297.42</v>
       </c>
       <c r="L43" t="n">
-        <v>123.42</v>
+        <v>312.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:20</t>
+          <t>08:02:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>6.49</v>
+        <v>5.97</v>
       </c>
       <c r="G44" t="n">
-        <v>102.7</v>
+        <v>90.8</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>61.57</v>
+        <v>31.41</v>
       </c>
       <c r="K44" t="n">
-        <v>10.26</v>
+        <v>-34.79</v>
       </c>
       <c r="L44" t="n">
-        <v>62.42</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:07:34</t>
+          <t>08:05:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="F45" t="n">
-        <v>5.22</v>
+        <v>5.18</v>
       </c>
       <c r="G45" t="n">
-        <v>92.7</v>
+        <v>88.2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.13</v>
+        <v>-3.99</v>
       </c>
       <c r="K45" t="n">
-        <v>25.76</v>
+        <v>-37.08</v>
       </c>
       <c r="L45" t="n">
-        <v>25.76</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:09:06</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="F46" t="n">
-        <v>5.1</v>
+        <v>2.01</v>
       </c>
       <c r="G46" t="n">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-31.56</v>
+        <v>-37.34</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.62</v>
+        <v>42.64</v>
       </c>
       <c r="L46" t="n">
-        <v>60.5</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:15:10</t>
+          <t>08:11:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F47" t="n">
-        <v>5.49</v>
+        <v>6.09</v>
       </c>
       <c r="G47" t="n">
-        <v>112.6</v>
+        <v>87.8</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>68.43000000000001</v>
+        <v>51.85</v>
       </c>
       <c r="K47" t="n">
-        <v>31.37</v>
+        <v>32.81</v>
       </c>
       <c r="L47" t="n">
-        <v>75.28</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:17:48</t>
+          <t>08:13:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="F48" t="n">
-        <v>5.47</v>
+        <v>6.09</v>
       </c>
       <c r="G48" t="n">
-        <v>102.1</v>
+        <v>104.7</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-61.58</v>
+        <v>39.91</v>
       </c>
       <c r="K48" t="n">
-        <v>26.75</v>
+        <v>-55.95</v>
       </c>
       <c r="L48" t="n">
-        <v>67.14</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:20:07</t>
+          <t>08:15:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="F49" t="n">
-        <v>5.18</v>
+        <v>3.66</v>
       </c>
       <c r="G49" t="n">
-        <v>91</v>
+        <v>93.3</v>
       </c>
       <c r="H49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.29</v>
+        <v>-47.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.17</v>
+        <v>73.81</v>
       </c>
       <c r="L49" t="n">
-        <v>45.55</v>
+        <v>87.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:24:18</t>
+          <t>08:19:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="F50" t="n">
-        <v>5.1</v>
+        <v>1.77</v>
       </c>
       <c r="G50" t="n">
-        <v>112.9</v>
+        <v>98.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-80.01000000000001</v>
+        <v>-30.62</v>
       </c>
       <c r="K50" t="n">
-        <v>62.3</v>
+        <v>75.83</v>
       </c>
       <c r="L50" t="n">
-        <v>101.41</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:26:49</t>
+          <t>08:21:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="F51" t="n">
-        <v>4.97</v>
+        <v>3.43</v>
       </c>
       <c r="G51" t="n">
-        <v>73.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="H51" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.4</v>
+        <v>106</v>
       </c>
       <c r="K51" t="n">
-        <v>118.95</v>
+        <v>37.6</v>
       </c>
       <c r="L51" t="n">
-        <v>119.03</v>
+        <v>112.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:28:59</t>
+          <t>08:22:23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="F52" t="n">
-        <v>5.03</v>
+        <v>6.09</v>
       </c>
       <c r="G52" t="n">
-        <v>102.6</v>
+        <v>101.6</v>
       </c>
       <c r="H52" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>42.58</v>
+        <v>151.76</v>
       </c>
       <c r="K52" t="n">
-        <v>89.17</v>
+        <v>46.43</v>
       </c>
       <c r="L52" t="n">
-        <v>98.81999999999999</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:33:33</t>
+          <t>08:28:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="F53" t="n">
-        <v>5.32</v>
+        <v>6.09</v>
       </c>
       <c r="G53" t="n">
-        <v>88.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="H53" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-13.13</v>
+        <v>-78.31999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>105.79</v>
+        <v>53.79</v>
       </c>
       <c r="L53" t="n">
-        <v>106.6</v>
+        <v>95.01000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:34:47</t>
+          <t>08:29:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="F54" t="n">
-        <v>5.38</v>
+        <v>4.72</v>
       </c>
       <c r="G54" t="n">
-        <v>98.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.13</v>
+        <v>113.95</v>
       </c>
       <c r="K54" t="n">
-        <v>-94.04000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="L54" t="n">
-        <v>98.45</v>
+        <v>150.22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:36:35</t>
+          <t>08:30:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="F55" t="n">
-        <v>4.79</v>
+        <v>5.64</v>
       </c>
       <c r="G55" t="n">
-        <v>101.7</v>
+        <v>102.4</v>
       </c>
       <c r="H55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-98.17</v>
+        <v>61.95</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.05</v>
+        <v>117.87</v>
       </c>
       <c r="L55" t="n">
-        <v>98.91</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:40:59</t>
+          <t>08:35:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="F56" t="n">
-        <v>5.4</v>
+        <v>6.09</v>
       </c>
       <c r="G56" t="n">
-        <v>107.3</v>
+        <v>93</v>
       </c>
       <c r="H56" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="I56" t="n">
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>119.34</v>
+        <v>-5.96</v>
       </c>
       <c r="K56" t="n">
-        <v>110.41</v>
+        <v>-244.92</v>
       </c>
       <c r="L56" t="n">
-        <v>162.58</v>
+        <v>244.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:43:41</t>
+          <t>08:37:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="F57" t="n">
-        <v>4.78</v>
+        <v>6.09</v>
       </c>
       <c r="G57" t="n">
-        <v>100.7</v>
+        <v>93.7</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-146.18</v>
+        <v>-48.97</v>
       </c>
       <c r="K57" t="n">
-        <v>-73.29000000000001</v>
+        <v>-188.11</v>
       </c>
       <c r="L57" t="n">
-        <v>163.52</v>
+        <v>194.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:45:22</t>
+          <t>08:38:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="F58" t="n">
-        <v>5.45</v>
+        <v>6.09</v>
       </c>
       <c r="G58" t="n">
-        <v>88.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>103.17</v>
+        <v>2.6</v>
       </c>
       <c r="K58" t="n">
-        <v>-120.42</v>
+        <v>61.94</v>
       </c>
       <c r="L58" t="n">
-        <v>158.57</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:54:54</t>
+          <t>08:48:18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="F59" t="n">
-        <v>4.96</v>
+        <v>5.62</v>
       </c>
       <c r="G59" t="n">
-        <v>83.90000000000001</v>
+        <v>100.6</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.94</v>
+        <v>37.02</v>
       </c>
       <c r="K59" t="n">
-        <v>28.95</v>
+        <v>-44.7</v>
       </c>
       <c r="L59" t="n">
-        <v>32.58</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:55:34</t>
+          <t>08:49:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="F60" t="n">
-        <v>4.99</v>
+        <v>6.09</v>
       </c>
       <c r="G60" t="n">
-        <v>87.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>41.3</v>
+        <v>26.54</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.23</v>
+        <v>46.37</v>
       </c>
       <c r="L60" t="n">
-        <v>48.92</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:57:14</t>
+          <t>08:51:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="F61" t="n">
-        <v>5.7</v>
+        <v>6.09</v>
       </c>
       <c r="G61" t="n">
-        <v>94</v>
+        <v>98.5</v>
       </c>
       <c r="H61" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>45.87</v>
+        <v>-52.91</v>
       </c>
       <c r="K61" t="n">
-        <v>12.8</v>
+        <v>-10.32</v>
       </c>
       <c r="L61" t="n">
-        <v>47.62</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:02:10</t>
+          <t>08:56:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="F62" t="n">
-        <v>5.34</v>
+        <v>6.09</v>
       </c>
       <c r="G62" t="n">
-        <v>95</v>
+        <v>95.7</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>22.47</v>
+        <v>57.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-52.96</v>
+        <v>33.93</v>
       </c>
       <c r="L62" t="n">
-        <v>57.53</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:03:09</t>
+          <t>08:57:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="F63" t="n">
-        <v>5.15</v>
+        <v>2.33</v>
       </c>
       <c r="G63" t="n">
-        <v>100.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>13.34</v>
+        <v>-14.17</v>
       </c>
       <c r="K63" t="n">
-        <v>-68.67</v>
+        <v>75.72</v>
       </c>
       <c r="L63" t="n">
-        <v>69.95</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:03:58</t>
+          <t>08:59:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="F64" t="n">
-        <v>6.03</v>
+        <v>4.96</v>
       </c>
       <c r="G64" t="n">
-        <v>114.6</v>
+        <v>102.2</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.28</v>
+        <v>5.54</v>
       </c>
       <c r="K64" t="n">
-        <v>59.6</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>65.97</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:08:59</t>
+          <t>09:04:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="F65" t="n">
-        <v>5.36</v>
+        <v>6.08</v>
       </c>
       <c r="G65" t="n">
-        <v>92.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="H65" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-75.8</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-19.47</v>
+        <v>29.64</v>
       </c>
       <c r="L65" t="n">
-        <v>78.26000000000001</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:11:40</t>
+          <t>09:05:08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="F66" t="n">
-        <v>4.74</v>
+        <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>99.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-73.58</v>
+        <v>-95.33</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.96</v>
+        <v>-10.24</v>
       </c>
       <c r="L66" t="n">
-        <v>75.98999999999999</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:12:25</t>
+          <t>09:07:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,13 +2851,13 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="F67" t="n">
-        <v>5.51</v>
+        <v>4.81</v>
       </c>
       <c r="G67" t="n">
-        <v>91.2</v>
+        <v>111</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2866,19 +2866,19 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.55</v>
+        <v>-66.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-66.28</v>
+        <v>15.8</v>
       </c>
       <c r="L67" t="n">
-        <v>66.38</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:18:24</t>
+          <t>09:10:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F68" t="n">
         <v>1.93</v>
       </c>
-      <c r="F68" t="n">
-        <v>5.2</v>
-      </c>
       <c r="G68" t="n">
-        <v>98.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.54</v>
+        <v>144.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-43.73</v>
+        <v>-2.93</v>
       </c>
       <c r="L68" t="n">
-        <v>117.02</v>
+        <v>144.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:19:16</t>
+          <t>09:11:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="F69" t="n">
-        <v>5.6</v>
+        <v>2.98</v>
       </c>
       <c r="G69" t="n">
-        <v>86</v>
+        <v>93.2</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-51.47</v>
+        <v>-105.87</v>
       </c>
       <c r="K69" t="n">
-        <v>-65</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>82.91</v>
+        <v>123.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:20:01</t>
+          <t>09:12:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="F70" t="n">
-        <v>5.71</v>
+        <v>6.09</v>
       </c>
       <c r="G70" t="n">
-        <v>91.59999999999999</v>
+        <v>104.8</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>10.2</v>
+        <v>132.93</v>
       </c>
       <c r="K70" t="n">
-        <v>-124.86</v>
+        <v>10.83</v>
       </c>
       <c r="L70" t="n">
-        <v>125.28</v>
+        <v>133.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:25:21</t>
+          <t>09:17:05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="F71" t="n">
-        <v>4.63</v>
+        <v>6.09</v>
       </c>
       <c r="G71" t="n">
-        <v>92.7</v>
+        <v>111.8</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>109.91</v>
+        <v>212.36</v>
       </c>
       <c r="K71" t="n">
-        <v>105.86</v>
+        <v>-76.5</v>
       </c>
       <c r="L71" t="n">
-        <v>152.6</v>
+        <v>225.72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:26:55</t>
+          <t>09:18:50</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="F72" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="G72" t="n">
-        <v>93.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-109.73</v>
+        <v>-5.17</v>
       </c>
       <c r="K72" t="n">
-        <v>24.56</v>
+        <v>-223.82</v>
       </c>
       <c r="L72" t="n">
-        <v>112.45</v>
+        <v>223.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:27:44</t>
+          <t>09:20:52</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="F73" t="n">
-        <v>5.16</v>
+        <v>6.09</v>
       </c>
       <c r="G73" t="n">
-        <v>93.5</v>
+        <v>101.4</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>37.68</v>
+        <v>62.49</v>
       </c>
       <c r="K73" t="n">
-        <v>152.99</v>
+        <v>-142.29</v>
       </c>
       <c r="L73" t="n">
-        <v>157.56</v>
+        <v>155.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:38:12</t>
+          <t>09:33:45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,13 +3145,13 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="F74" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>94.40000000000001</v>
+        <v>100.9</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3160,19 +3160,19 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-32.92</v>
+        <v>10.68</v>
       </c>
       <c r="K74" t="n">
-        <v>0.41</v>
+        <v>-49.88</v>
       </c>
       <c r="L74" t="n">
-        <v>32.92</v>
+        <v>51.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:40:14</t>
+          <t>09:36:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="F75" t="n">
-        <v>5.51</v>
+        <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>106</v>
+        <v>104.7</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-29.3</v>
+        <v>-14</v>
       </c>
       <c r="K75" t="n">
-        <v>29.98</v>
+        <v>-43.2</v>
       </c>
       <c r="L75" t="n">
-        <v>41.92</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:41:08</t>
+          <t>09:37:16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="G76" t="n">
-        <v>86.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>48.52</v>
+        <v>27.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.14</v>
+        <v>21.66</v>
       </c>
       <c r="L76" t="n">
-        <v>66.27</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:46:17</t>
+          <t>09:40:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="F77" t="n">
-        <v>5.12</v>
+        <v>6.09</v>
       </c>
       <c r="G77" t="n">
-        <v>104.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.64</v>
+        <v>48.43</v>
       </c>
       <c r="K77" t="n">
-        <v>55.2</v>
+        <v>75.36</v>
       </c>
       <c r="L77" t="n">
-        <v>56.41</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:48:14</t>
+          <t>09:43:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="F78" t="n">
-        <v>5.73</v>
+        <v>6.09</v>
       </c>
       <c r="G78" t="n">
-        <v>101.8</v>
+        <v>112.9</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>28.95</v>
+        <v>60.07</v>
       </c>
       <c r="K78" t="n">
-        <v>52.82</v>
+        <v>69.16</v>
       </c>
       <c r="L78" t="n">
-        <v>60.23</v>
+        <v>91.61</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:50:33</t>
+          <t>09:44:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="F79" t="n">
-        <v>5.42</v>
+        <v>4.34</v>
       </c>
       <c r="G79" t="n">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I79" t="n">
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.59</v>
+        <v>63.4</v>
       </c>
       <c r="K79" t="n">
-        <v>64.40000000000001</v>
+        <v>-29.93</v>
       </c>
       <c r="L79" t="n">
-        <v>64.41</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:53:54</t>
+          <t>09:49:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="F80" t="n">
         <v>4.87</v>
       </c>
       <c r="G80" t="n">
-        <v>90.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>58.69</v>
+        <v>4.7</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.11</v>
+        <v>-80.54000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>59.12</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:55:16</t>
+          <t>09:51:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="F81" t="n">
-        <v>4.91</v>
+        <v>4.6</v>
       </c>
       <c r="G81" t="n">
-        <v>91.5</v>
+        <v>95.3</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>47.96</v>
+        <v>-20.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-31.26</v>
+        <v>-97.05</v>
       </c>
       <c r="L81" t="n">
-        <v>57.25</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:58:00</t>
+          <t>09:52:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="F82" t="n">
-        <v>5.17</v>
+        <v>6.09</v>
       </c>
       <c r="G82" t="n">
-        <v>97.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.92</v>
+        <v>-53.45</v>
       </c>
       <c r="K82" t="n">
-        <v>-88.70999999999999</v>
+        <v>-108.72</v>
       </c>
       <c r="L82" t="n">
-        <v>99.90000000000001</v>
+        <v>121.14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:02:49</t>
+          <t>09:57:08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>1.88</v>
       </c>
       <c r="F83" t="n">
-        <v>5.01</v>
+        <v>6.09</v>
       </c>
       <c r="G83" t="n">
-        <v>99.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H83" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-24.62</v>
+        <v>-20.02</v>
       </c>
       <c r="K83" t="n">
-        <v>151.62</v>
+        <v>180.36</v>
       </c>
       <c r="L83" t="n">
-        <v>153.61</v>
+        <v>181.47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:04:36</t>
+          <t>09:58:38</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="F84" t="n">
-        <v>4.75</v>
+        <v>6.09</v>
       </c>
       <c r="G84" t="n">
-        <v>107.1</v>
+        <v>86.2</v>
       </c>
       <c r="H84" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>6.42</v>
+        <v>27.93</v>
       </c>
       <c r="K84" t="n">
-        <v>76.98999999999999</v>
+        <v>99</v>
       </c>
       <c r="L84" t="n">
-        <v>77.26000000000001</v>
+        <v>102.87</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:06:26</t>
+          <t>10:00:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="F85" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="G85" t="n">
-        <v>85.7</v>
+        <v>93.8</v>
       </c>
       <c r="H85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-93.17</v>
+        <v>-108.68</v>
       </c>
       <c r="K85" t="n">
-        <v>30.94</v>
+        <v>38.69</v>
       </c>
       <c r="L85" t="n">
-        <v>98.18000000000001</v>
+        <v>115.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:10:16</t>
+          <t>10:05:28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="F86" t="n">
-        <v>5.27</v>
+        <v>6.09</v>
       </c>
       <c r="G86" t="n">
-        <v>108</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-72.04000000000001</v>
+        <v>-52.16</v>
       </c>
       <c r="K86" t="n">
-        <v>116.68</v>
+        <v>163.22</v>
       </c>
       <c r="L86" t="n">
-        <v>137.13</v>
+        <v>171.35</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:11:01</t>
+          <t>10:06:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="F87" t="n">
-        <v>5.47</v>
+        <v>6.09</v>
       </c>
       <c r="G87" t="n">
-        <v>90.90000000000001</v>
+        <v>100.6</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>111.47</v>
+        <v>168.69</v>
       </c>
       <c r="K87" t="n">
-        <v>-65.04000000000001</v>
+        <v>-88.34</v>
       </c>
       <c r="L87" t="n">
-        <v>129.06</v>
+        <v>190.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:12:31</t>
+          <t>10:08:36</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,25 +3736,25 @@
         <v>1.95</v>
       </c>
       <c r="F88" t="n">
-        <v>4.76</v>
+        <v>6.09</v>
       </c>
       <c r="G88" t="n">
-        <v>102</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>9.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>151.35</v>
+        <v>194.4</v>
       </c>
       <c r="K88" t="n">
-        <v>45.71</v>
+        <v>55.62</v>
       </c>
       <c r="L88" t="n">
-        <v>158.11</v>
+        <v>202.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-32.94</v>
+        <v>-36.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-36.88</v>
+        <v>-40.83</v>
       </c>
       <c r="L14" t="n">
-        <v>49.45</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.61</v>
+        <v>-20</v>
       </c>
       <c r="K15" t="n">
-        <v>60.41</v>
+        <v>61.59</v>
       </c>
       <c r="L15" t="n">
-        <v>63.51</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.68</v>
+        <v>-37.84</v>
       </c>
       <c r="K16" t="n">
-        <v>32.61</v>
+        <v>35.58</v>
       </c>
       <c r="L16" t="n">
-        <v>47.61</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="17">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-39.53</v>
+        <v>-43.77</v>
       </c>
       <c r="K18" t="n">
-        <v>77.33</v>
+        <v>85.62</v>
       </c>
       <c r="L18" t="n">
-        <v>86.84999999999999</v>
+        <v>96.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>63.55</v>
+        <v>70.36</v>
       </c>
       <c r="K19" t="n">
-        <v>9.27</v>
+        <v>10.27</v>
       </c>
       <c r="L19" t="n">
-        <v>64.23</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>29.88</v>
+        <v>30.47</v>
       </c>
       <c r="K20" t="n">
-        <v>-58.94</v>
+        <v>-60.1</v>
       </c>
       <c r="L20" t="n">
-        <v>66.08</v>
+        <v>67.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>32.87</v>
+        <v>36.39</v>
       </c>
       <c r="K21" t="n">
-        <v>130.28</v>
+        <v>144.24</v>
       </c>
       <c r="L21" t="n">
-        <v>134.37</v>
+        <v>148.76</v>
       </c>
     </row>
     <row r="22">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>100.62</v>
+        <v>111.4</v>
       </c>
       <c r="K23" t="n">
-        <v>-64.86</v>
+        <v>-71.81</v>
       </c>
       <c r="L23" t="n">
-        <v>119.72</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="24">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>114.94</v>
+        <v>127.26</v>
       </c>
       <c r="K25" t="n">
-        <v>-16.25</v>
+        <v>-17.99</v>
       </c>
       <c r="L25" t="n">
-        <v>116.09</v>
+        <v>128.52</v>
       </c>
     </row>
     <row r="26">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>159.47</v>
+        <v>173.97</v>
       </c>
       <c r="K27" t="n">
-        <v>96.27</v>
+        <v>105.02</v>
       </c>
       <c r="L27" t="n">
-        <v>186.28</v>
+        <v>203.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-166.49</v>
+        <v>-169.75</v>
       </c>
       <c r="K28" t="n">
-        <v>-60.27</v>
+        <v>-61.46</v>
       </c>
       <c r="L28" t="n">
-        <v>177.06</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-53.67</v>
+        <v>-58.55</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.15</v>
+        <v>-18.71</v>
       </c>
       <c r="L29" t="n">
-        <v>56.34</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>23.93</v>
+        <v>26.1</v>
       </c>
       <c r="K30" t="n">
-        <v>33.54</v>
+        <v>36.59</v>
       </c>
       <c r="L30" t="n">
-        <v>41.2</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-36</v>
+        <v>-38.03</v>
       </c>
       <c r="K31" t="n">
-        <v>29.17</v>
+        <v>30.82</v>
       </c>
       <c r="L31" t="n">
-        <v>46.33</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.76</v>
+        <v>-10.98</v>
       </c>
       <c r="K32" t="n">
-        <v>52.33</v>
+        <v>53.36</v>
       </c>
       <c r="L32" t="n">
-        <v>53.43</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>92.69</v>
+        <v>102.63</v>
       </c>
       <c r="K33" t="n">
-        <v>15.73</v>
+        <v>17.41</v>
       </c>
       <c r="L33" t="n">
-        <v>94.02</v>
+        <v>104.09</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>5.56</v>
+        <v>6.15</v>
       </c>
       <c r="K34" t="n">
-        <v>108.05</v>
+        <v>119.63</v>
       </c>
       <c r="L34" t="n">
-        <v>108.19</v>
+        <v>119.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>84.02</v>
+        <v>88.78</v>
       </c>
       <c r="K35" t="n">
-        <v>72.87</v>
+        <v>77</v>
       </c>
       <c r="L35" t="n">
-        <v>111.22</v>
+        <v>117.52</v>
       </c>
     </row>
     <row r="36">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>62.84</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>81.25</v>
+        <v>82.84</v>
       </c>
       <c r="L37" t="n">
-        <v>102.71</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-78.83</v>
+        <v>-83.29000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>119.71</v>
+        <v>126.48</v>
       </c>
       <c r="L38" t="n">
-        <v>143.33</v>
+        <v>151.45</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-26.56</v>
+        <v>-27.08</v>
       </c>
       <c r="K39" t="n">
-        <v>151.16</v>
+        <v>154.12</v>
       </c>
       <c r="L39" t="n">
-        <v>153.48</v>
+        <v>156.48</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-98.86</v>
+        <v>-104.46</v>
       </c>
       <c r="K40" t="n">
-        <v>13.09</v>
+        <v>13.83</v>
       </c>
       <c r="L40" t="n">
-        <v>99.73</v>
+        <v>105.37</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>137.81</v>
+        <v>148.02</v>
       </c>
       <c r="K41" t="n">
-        <v>124.98</v>
+        <v>134.24</v>
       </c>
       <c r="L41" t="n">
-        <v>186.04</v>
+        <v>199.82</v>
       </c>
     </row>
     <row r="42">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>97.45999999999999</v>
+        <v>104.68</v>
       </c>
       <c r="K43" t="n">
-        <v>297.42</v>
+        <v>319.45</v>
       </c>
       <c r="L43" t="n">
-        <v>312.98</v>
+        <v>336.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>31.41</v>
+        <v>34.26</v>
       </c>
       <c r="K44" t="n">
-        <v>-34.79</v>
+        <v>-37.95</v>
       </c>
       <c r="L44" t="n">
-        <v>46.87</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="45">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>51.85</v>
+        <v>52.87</v>
       </c>
       <c r="K47" t="n">
-        <v>32.81</v>
+        <v>33.45</v>
       </c>
       <c r="L47" t="n">
-        <v>61.36</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>39.91</v>
+        <v>42.86</v>
       </c>
       <c r="K48" t="n">
-        <v>-55.95</v>
+        <v>-60.1</v>
       </c>
       <c r="L48" t="n">
-        <v>68.73</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-47.56</v>
+        <v>-51.88</v>
       </c>
       <c r="K49" t="n">
-        <v>73.81</v>
+        <v>80.52</v>
       </c>
       <c r="L49" t="n">
-        <v>87.81</v>
+        <v>95.79000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-30.62</v>
+        <v>-33.9</v>
       </c>
       <c r="K50" t="n">
-        <v>75.83</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>81.78</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>106</v>
+        <v>108.07</v>
       </c>
       <c r="K51" t="n">
-        <v>37.6</v>
+        <v>38.34</v>
       </c>
       <c r="L51" t="n">
-        <v>112.47</v>
+        <v>114.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>151.76</v>
+        <v>160.35</v>
       </c>
       <c r="K52" t="n">
-        <v>46.43</v>
+        <v>49.06</v>
       </c>
       <c r="L52" t="n">
-        <v>158.71</v>
+        <v>167.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-78.31999999999999</v>
+        <v>-85.44</v>
       </c>
       <c r="K53" t="n">
-        <v>53.79</v>
+        <v>58.68</v>
       </c>
       <c r="L53" t="n">
-        <v>95.01000000000001</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>113.95</v>
+        <v>126.16</v>
       </c>
       <c r="K54" t="n">
-        <v>97.88</v>
+        <v>108.37</v>
       </c>
       <c r="L54" t="n">
-        <v>150.22</v>
+        <v>166.31</v>
       </c>
     </row>
     <row r="55">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-48.97</v>
+        <v>-49.93</v>
       </c>
       <c r="K57" t="n">
-        <v>-188.11</v>
+        <v>-191.8</v>
       </c>
       <c r="L57" t="n">
-        <v>194.38</v>
+        <v>198.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="K58" t="n">
-        <v>61.94</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>61.99</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>37.02</v>
+        <v>39.77</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.7</v>
+        <v>-48.01</v>
       </c>
       <c r="L59" t="n">
-        <v>58.04</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>26.54</v>
+        <v>28.04</v>
       </c>
       <c r="K60" t="n">
-        <v>46.37</v>
+        <v>49</v>
       </c>
       <c r="L60" t="n">
-        <v>53.43</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.91</v>
+        <v>-54.95</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.32</v>
+        <v>-10.72</v>
       </c>
       <c r="L61" t="n">
-        <v>53.91</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="62">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.17</v>
+        <v>-15.22</v>
       </c>
       <c r="K63" t="n">
-        <v>75.72</v>
+        <v>81.33</v>
       </c>
       <c r="L63" t="n">
-        <v>77.04000000000001</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>5.54</v>
+        <v>6.13</v>
       </c>
       <c r="K64" t="n">
-        <v>65.98999999999999</v>
+        <v>73.06</v>
       </c>
       <c r="L64" t="n">
-        <v>66.22</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="65">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-95.33</v>
+        <v>-100.73</v>
       </c>
       <c r="K66" t="n">
-        <v>-10.24</v>
+        <v>-10.82</v>
       </c>
       <c r="L66" t="n">
-        <v>95.88</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-66.41</v>
+        <v>-67.72</v>
       </c>
       <c r="K67" t="n">
-        <v>15.8</v>
+        <v>16.11</v>
       </c>
       <c r="L67" t="n">
-        <v>68.27</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>144.44</v>
+        <v>147.27</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.93</v>
+        <v>-2.99</v>
       </c>
       <c r="L68" t="n">
-        <v>144.47</v>
+        <v>147.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-105.87</v>
+        <v>-113.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-64.31999999999999</v>
+        <v>-69.08</v>
       </c>
       <c r="L69" t="n">
-        <v>123.87</v>
+        <v>133.05</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>132.93</v>
+        <v>138.05</v>
       </c>
       <c r="K70" t="n">
-        <v>10.83</v>
+        <v>11.25</v>
       </c>
       <c r="L70" t="n">
-        <v>133.37</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>212.36</v>
+        <v>216.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-76.5</v>
+        <v>-78</v>
       </c>
       <c r="L71" t="n">
-        <v>225.72</v>
+        <v>230.14</v>
       </c>
     </row>
     <row r="72">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>62.49</v>
+        <v>64.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-142.29</v>
+        <v>-147.77</v>
       </c>
       <c r="L73" t="n">
-        <v>155.41</v>
+        <v>161.39</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>10.68</v>
+        <v>11.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.88</v>
+        <v>-51.79</v>
       </c>
       <c r="L74" t="n">
-        <v>51.01</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="75">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>27.4</v>
+        <v>30.33</v>
       </c>
       <c r="K76" t="n">
-        <v>21.66</v>
+        <v>23.99</v>
       </c>
       <c r="L76" t="n">
-        <v>34.93</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="77">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>60.07</v>
+        <v>64.52</v>
       </c>
       <c r="K78" t="n">
-        <v>69.16</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>91.61</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="79">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>4.7</v>
+        <v>4.88</v>
       </c>
       <c r="K80" t="n">
-        <v>-80.54000000000001</v>
+        <v>-83.63</v>
       </c>
       <c r="L80" t="n">
-        <v>80.67</v>
+        <v>83.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.06</v>
+        <v>-22.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.05</v>
+        <v>-107.45</v>
       </c>
       <c r="L81" t="n">
-        <v>99.09999999999999</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-53.45</v>
+        <v>-57.41</v>
       </c>
       <c r="K82" t="n">
-        <v>-108.72</v>
+        <v>-116.77</v>
       </c>
       <c r="L82" t="n">
-        <v>121.14</v>
+        <v>130.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-20.02</v>
+        <v>-21.5</v>
       </c>
       <c r="K83" t="n">
-        <v>180.36</v>
+        <v>193.72</v>
       </c>
       <c r="L83" t="n">
-        <v>181.47</v>
+        <v>194.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>27.93</v>
+        <v>28.47</v>
       </c>
       <c r="K84" t="n">
-        <v>99</v>
+        <v>100.94</v>
       </c>
       <c r="L84" t="n">
-        <v>102.87</v>
+        <v>104.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-108.68</v>
+        <v>-116.74</v>
       </c>
       <c r="K85" t="n">
-        <v>38.69</v>
+        <v>41.56</v>
       </c>
       <c r="L85" t="n">
-        <v>115.37</v>
+        <v>123.91</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-52.16</v>
+        <v>-57.74</v>
       </c>
       <c r="K86" t="n">
-        <v>163.22</v>
+        <v>180.7</v>
       </c>
       <c r="L86" t="n">
-        <v>171.35</v>
+        <v>189.7</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>168.69</v>
+        <v>186.76</v>
       </c>
       <c r="K87" t="n">
-        <v>-88.34</v>
+        <v>-97.81</v>
       </c>
       <c r="L87" t="n">
-        <v>190.42</v>
+        <v>210.82</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>194.4</v>
+        <v>201.87</v>
       </c>
       <c r="K88" t="n">
-        <v>55.62</v>
+        <v>57.76</v>
       </c>
       <c r="L88" t="n">
-        <v>202.2</v>
+        <v>209.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="F14" t="n">
-        <v>6.09</v>
+        <v>3.33</v>
       </c>
       <c r="G14" t="n">
-        <v>96.8</v>
+        <v>79.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>61</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-36.47</v>
+        <v>-2.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.83</v>
+        <v>-26.52</v>
       </c>
       <c r="L14" t="n">
-        <v>54.75</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:31:45</t>
+          <t>06:31:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>99.7</v>
+        <v>103.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>36.4</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-20</v>
+        <v>25.82</v>
       </c>
       <c r="K15" t="n">
-        <v>61.59</v>
+        <v>-8.4</v>
       </c>
       <c r="L15" t="n">
-        <v>64.76000000000001</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:32:53</t>
+          <t>06:34:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="F16" t="n">
-        <v>6.09</v>
+        <v>3.68</v>
       </c>
       <c r="G16" t="n">
-        <v>108.9</v>
+        <v>96</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-37.84</v>
+        <v>7.82</v>
       </c>
       <c r="K16" t="n">
-        <v>35.58</v>
+        <v>29.2</v>
       </c>
       <c r="L16" t="n">
-        <v>51.94</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:37:17</t>
+          <t>06:37:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>100.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>43.7</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>21.68</v>
+        <v>12.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-53.59</v>
+        <v>-36.03</v>
       </c>
       <c r="L17" t="n">
-        <v>57.81</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:39:28</t>
+          <t>06:39:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="F18" t="n">
-        <v>5.7</v>
+        <v>4.72</v>
       </c>
       <c r="G18" t="n">
-        <v>101.5</v>
+        <v>99.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6</v>
+        <v>17.4</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.77</v>
+        <v>-33.21</v>
       </c>
       <c r="K18" t="n">
-        <v>85.62</v>
+        <v>-29.57</v>
       </c>
       <c r="L18" t="n">
-        <v>96.16</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:41:23</t>
+          <t>06:40:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -838,31 +838,31 @@
         <v>1.27</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9</v>
+        <v>5.22</v>
       </c>
       <c r="G19" t="n">
-        <v>105.6</v>
+        <v>92</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>70.36</v>
+        <v>-53.56</v>
       </c>
       <c r="K19" t="n">
-        <v>10.27</v>
+        <v>-2.33</v>
       </c>
       <c r="L19" t="n">
-        <v>71.11</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:46:30</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="F20" t="n">
-        <v>2.29</v>
+        <v>3.91</v>
       </c>
       <c r="G20" t="n">
-        <v>99.90000000000001</v>
+        <v>106.9</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>28.6</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>30.47</v>
+        <v>15.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-60.1</v>
+        <v>67.83</v>
       </c>
       <c r="L20" t="n">
-        <v>67.38</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:47:33</t>
+          <t>06:46:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="F21" t="n">
         <v>6.09</v>
       </c>
       <c r="G21" t="n">
-        <v>101.8</v>
+        <v>88</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1</v>
+        <v>11.8</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>36.39</v>
+        <v>44.91</v>
       </c>
       <c r="K21" t="n">
-        <v>144.24</v>
+        <v>-27</v>
       </c>
       <c r="L21" t="n">
-        <v>148.76</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:49:26</t>
+          <t>06:48:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="F22" t="n">
         <v>6.09</v>
       </c>
       <c r="G22" t="n">
-        <v>89.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>27.9</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-72.63</v>
+        <v>85.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-40.72</v>
+        <v>-5.01</v>
       </c>
       <c r="L22" t="n">
-        <v>83.27</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:54:16</t>
+          <t>06:52:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="F23" t="n">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="G23" t="n">
-        <v>101.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>13.2</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>111.4</v>
+        <v>130.39</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.81</v>
+        <v>-7.55</v>
       </c>
       <c r="L23" t="n">
-        <v>132.54</v>
+        <v>130.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:55:39</t>
+          <t>06:53:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="F24" t="n">
-        <v>5.09</v>
+        <v>4.37</v>
       </c>
       <c r="G24" t="n">
-        <v>92.2</v>
+        <v>105.9</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>29.7</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-36.78</v>
+        <v>-113.94</v>
       </c>
       <c r="K24" t="n">
-        <v>169.33</v>
+        <v>-37.18</v>
       </c>
       <c r="L24" t="n">
-        <v>173.27</v>
+        <v>119.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:57:11</t>
+          <t>06:55:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="F25" t="n">
         <v>6.09</v>
       </c>
       <c r="G25" t="n">
-        <v>96.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5</v>
+        <v>25.5</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>127.26</v>
+        <v>-143.58</v>
       </c>
       <c r="K25" t="n">
-        <v>-17.99</v>
+        <v>115.78</v>
       </c>
       <c r="L25" t="n">
-        <v>128.52</v>
+        <v>184.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:02:49</t>
+          <t>07:00:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="F26" t="n">
-        <v>4.15</v>
+        <v>1.67</v>
       </c>
       <c r="G26" t="n">
-        <v>101.5</v>
+        <v>101.2</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>47.3</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>146.58</v>
+        <v>343.06</v>
       </c>
       <c r="K26" t="n">
-        <v>-49.71</v>
+        <v>-150.67</v>
       </c>
       <c r="L26" t="n">
-        <v>154.78</v>
+        <v>374.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:04:48</t>
+          <t>07:01:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="F27" t="n">
-        <v>6.09</v>
+        <v>2.19</v>
       </c>
       <c r="G27" t="n">
-        <v>90.2</v>
+        <v>102</v>
       </c>
       <c r="H27" t="n">
-        <v>8.699999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>173.97</v>
+        <v>40.48</v>
       </c>
       <c r="K27" t="n">
-        <v>105.02</v>
+        <v>-129.84</v>
       </c>
       <c r="L27" t="n">
-        <v>203.21</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:06:42</t>
+          <t>07:03:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F28" t="n">
-        <v>3.64</v>
+        <v>6.09</v>
       </c>
       <c r="G28" t="n">
-        <v>99.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-169.75</v>
+        <v>188.48</v>
       </c>
       <c r="K28" t="n">
-        <v>-61.46</v>
+        <v>-52.36</v>
       </c>
       <c r="L28" t="n">
-        <v>180.54</v>
+        <v>195.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:15:29</t>
+          <t>07:11:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="F29" t="n">
         <v>6.09</v>
       </c>
       <c r="G29" t="n">
-        <v>100.1</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6</v>
+        <v>28.1</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.55</v>
+        <v>-3.78</v>
       </c>
       <c r="K29" t="n">
-        <v>-18.71</v>
+        <v>38.47</v>
       </c>
       <c r="L29" t="n">
-        <v>61.47</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:17:51</t>
+          <t>07:13:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="F30" t="n">
-        <v>2.66</v>
+        <v>6.09</v>
       </c>
       <c r="G30" t="n">
-        <v>101.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>43.3</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>26.1</v>
+        <v>13.74</v>
       </c>
       <c r="K30" t="n">
-        <v>36.59</v>
+        <v>27.09</v>
       </c>
       <c r="L30" t="n">
-        <v>44.95</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:18:51</t>
+          <t>07:14:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="F31" t="n">
-        <v>5.23</v>
+        <v>6.09</v>
       </c>
       <c r="G31" t="n">
-        <v>89.5</v>
+        <v>101.5</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>33.9</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-38.03</v>
+        <v>10.28</v>
       </c>
       <c r="K31" t="n">
-        <v>30.82</v>
+        <v>34.87</v>
       </c>
       <c r="L31" t="n">
-        <v>48.95</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:22:45</t>
+          <t>07:19:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1.85</v>
+        <v>5.31</v>
       </c>
       <c r="G32" t="n">
-        <v>96.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>52.7</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.98</v>
+        <v>2.26</v>
       </c>
       <c r="K32" t="n">
-        <v>53.36</v>
+        <v>33.43</v>
       </c>
       <c r="L32" t="n">
-        <v>54.47</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:24:13</t>
+          <t>07:20:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="F33" t="n">
-        <v>2.99</v>
+        <v>6.09</v>
       </c>
       <c r="G33" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>13.9</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>102.63</v>
+        <v>-23.99</v>
       </c>
       <c r="K33" t="n">
-        <v>17.41</v>
+        <v>42.87</v>
       </c>
       <c r="L33" t="n">
-        <v>104.09</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:26:21</t>
+          <t>07:21:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="F34" t="n">
-        <v>2.81</v>
+        <v>5.06</v>
       </c>
       <c r="G34" t="n">
-        <v>94.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>24.2</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>6.15</v>
+        <v>-41.72</v>
       </c>
       <c r="K34" t="n">
-        <v>119.63</v>
+        <v>-35.08</v>
       </c>
       <c r="L34" t="n">
-        <v>119.78</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:31:14</t>
+          <t>07:27:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="F35" t="n">
-        <v>3.09</v>
+        <v>6.09</v>
       </c>
       <c r="G35" t="n">
-        <v>90.3</v>
+        <v>110.5</v>
       </c>
       <c r="H35" t="n">
-        <v>2.2</v>
+        <v>47.5</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>88.78</v>
+        <v>-8.77</v>
       </c>
       <c r="K35" t="n">
-        <v>77</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>117.52</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:32:25</t>
+          <t>07:29:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="F36" t="n">
-        <v>6.09</v>
+        <v>5.42</v>
       </c>
       <c r="G36" t="n">
-        <v>99.5</v>
+        <v>88</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>34.3</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>-87.51000000000001</v>
+        <v>-54.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-64.55</v>
+        <v>-20.62</v>
       </c>
       <c r="L36" t="n">
-        <v>108.74</v>
+        <v>57.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:34:29</t>
+          <t>07:30:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="F37" t="n">
-        <v>6.09</v>
+        <v>1.98</v>
       </c>
       <c r="G37" t="n">
-        <v>107</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>34.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>64.06999999999999</v>
+        <v>61.45</v>
       </c>
       <c r="K37" t="n">
-        <v>82.84</v>
+        <v>-18.73</v>
       </c>
       <c r="L37" t="n">
-        <v>104.73</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:38:11</t>
+          <t>07:36:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="F38" t="n">
-        <v>5.54</v>
+        <v>4.33</v>
       </c>
       <c r="G38" t="n">
-        <v>109</v>
+        <v>103.3</v>
       </c>
       <c r="H38" t="n">
-        <v>5.6</v>
+        <v>90.7</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-83.29000000000001</v>
+        <v>103.7</v>
       </c>
       <c r="K38" t="n">
-        <v>126.48</v>
+        <v>-59.28</v>
       </c>
       <c r="L38" t="n">
-        <v>151.45</v>
+        <v>119.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:40:19</t>
+          <t>07:37:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="F39" t="n">
-        <v>3.84</v>
+        <v>6.09</v>
       </c>
       <c r="G39" t="n">
-        <v>99</v>
+        <v>105.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>58.4</v>
       </c>
       <c r="I39" t="n">
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-27.08</v>
+        <v>-30.51</v>
       </c>
       <c r="K39" t="n">
-        <v>154.12</v>
+        <v>-120.63</v>
       </c>
       <c r="L39" t="n">
-        <v>156.48</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:42:38</t>
+          <t>07:38:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="F40" t="n">
-        <v>2.33</v>
+        <v>5.15</v>
       </c>
       <c r="G40" t="n">
-        <v>100.9</v>
+        <v>109.1</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-104.46</v>
+        <v>-26.88</v>
       </c>
       <c r="K40" t="n">
-        <v>13.83</v>
+        <v>-117.59</v>
       </c>
       <c r="L40" t="n">
-        <v>105.37</v>
+        <v>120.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:46:44</t>
+          <t>07:42:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="F41" t="n">
-        <v>4.82</v>
+        <v>6.09</v>
       </c>
       <c r="G41" t="n">
-        <v>86.59999999999999</v>
+        <v>108.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>53.6</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>148.02</v>
+        <v>23.43</v>
       </c>
       <c r="K41" t="n">
-        <v>134.24</v>
+        <v>-138.44</v>
       </c>
       <c r="L41" t="n">
-        <v>199.82</v>
+        <v>140.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:49:07</t>
+          <t>07:42:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="F42" t="n">
-        <v>6.09</v>
+        <v>5.68</v>
       </c>
       <c r="G42" t="n">
-        <v>97.3</v>
+        <v>96.8</v>
       </c>
       <c r="H42" t="n">
-        <v>2.8</v>
+        <v>78.8</v>
       </c>
       <c r="I42" t="n">
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-139.77</v>
+        <v>113.71</v>
       </c>
       <c r="K42" t="n">
-        <v>55.33</v>
+        <v>-123.68</v>
       </c>
       <c r="L42" t="n">
-        <v>150.33</v>
+        <v>168.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:50:07</t>
+          <t>07:44:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="F43" t="n">
-        <v>5.57</v>
+        <v>5.83</v>
       </c>
       <c r="G43" t="n">
-        <v>103</v>
+        <v>114.9</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>104.68</v>
+        <v>80.3</v>
       </c>
       <c r="K43" t="n">
-        <v>319.45</v>
+        <v>164.21</v>
       </c>
       <c r="L43" t="n">
-        <v>336.17</v>
+        <v>182.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:02:51</t>
+          <t>07:53:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="F44" t="n">
-        <v>5.97</v>
+        <v>6.09</v>
       </c>
       <c r="G44" t="n">
-        <v>90.8</v>
+        <v>103</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>34.26</v>
+        <v>28.92</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.95</v>
+        <v>-2.64</v>
       </c>
       <c r="L44" t="n">
-        <v>51.13</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:05:10</t>
+          <t>07:55:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="F45" t="n">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="G45" t="n">
-        <v>88.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.99</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.08</v>
+        <v>22.59</v>
       </c>
       <c r="L45" t="n">
-        <v>37.3</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>07:56:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="F46" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="G46" t="n">
-        <v>96.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-37.34</v>
+        <v>-8.83</v>
       </c>
       <c r="K46" t="n">
-        <v>42.64</v>
+        <v>-32.4</v>
       </c>
       <c r="L46" t="n">
-        <v>56.68</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:11:15</t>
+          <t>08:00:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="F47" t="n">
-        <v>6.09</v>
+        <v>5.69</v>
       </c>
       <c r="G47" t="n">
-        <v>87.8</v>
+        <v>110.4</v>
       </c>
       <c r="H47" t="n">
-        <v>7.1</v>
+        <v>35.9</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>52.87</v>
+        <v>-36.92</v>
       </c>
       <c r="K47" t="n">
-        <v>33.45</v>
+        <v>41.29</v>
       </c>
       <c r="L47" t="n">
-        <v>62.57</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:13:25</t>
+          <t>08:01:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F48" t="n">
         <v>1.76</v>
       </c>
-      <c r="F48" t="n">
-        <v>6.09</v>
-      </c>
       <c r="G48" t="n">
-        <v>104.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>47.1</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>42.86</v>
+        <v>-13.3</v>
       </c>
       <c r="K48" t="n">
-        <v>-60.1</v>
+        <v>-45.29</v>
       </c>
       <c r="L48" t="n">
-        <v>73.81999999999999</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:15:20</t>
+          <t>08:04:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="F49" t="n">
-        <v>3.66</v>
+        <v>5.91</v>
       </c>
       <c r="G49" t="n">
-        <v>93.3</v>
+        <v>81.7</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-51.88</v>
+        <v>19.65</v>
       </c>
       <c r="K49" t="n">
-        <v>80.52</v>
+        <v>41</v>
       </c>
       <c r="L49" t="n">
-        <v>95.79000000000001</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:19:20</t>
+          <t>08:09:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="F50" t="n">
-        <v>1.77</v>
+        <v>4.36</v>
       </c>
       <c r="G50" t="n">
-        <v>98.5</v>
+        <v>102</v>
       </c>
       <c r="H50" t="n">
-        <v>5.4</v>
+        <v>39.8</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>-33.9</v>
+        <v>70.17</v>
       </c>
       <c r="K50" t="n">
-        <v>83.95999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="L50" t="n">
-        <v>90.54000000000001</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:21:08</t>
+          <t>08:10:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="F51" t="n">
-        <v>3.43</v>
+        <v>6.09</v>
       </c>
       <c r="G51" t="n">
-        <v>94.5</v>
+        <v>99.5</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>108.07</v>
+        <v>-85.5</v>
       </c>
       <c r="K51" t="n">
-        <v>38.34</v>
+        <v>31.68</v>
       </c>
       <c r="L51" t="n">
-        <v>114.67</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:22:23</t>
+          <t>08:13:02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="F52" t="n">
-        <v>6.09</v>
+        <v>3.13</v>
       </c>
       <c r="G52" t="n">
-        <v>101.6</v>
+        <v>91.8</v>
       </c>
       <c r="H52" t="n">
-        <v>6.6</v>
+        <v>24.9</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>160.35</v>
+        <v>73.36</v>
       </c>
       <c r="K52" t="n">
-        <v>49.06</v>
+        <v>-73.41</v>
       </c>
       <c r="L52" t="n">
-        <v>167.69</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:28:05</t>
+          <t>08:18:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="F53" t="n">
-        <v>6.09</v>
+        <v>5.21</v>
       </c>
       <c r="G53" t="n">
-        <v>96.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>6</v>
+        <v>49.3</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-85.44</v>
+        <v>24.61</v>
       </c>
       <c r="K53" t="n">
-        <v>58.68</v>
+        <v>93.45</v>
       </c>
       <c r="L53" t="n">
-        <v>103.65</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:29:46</t>
+          <t>08:19:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="F54" t="n">
-        <v>4.72</v>
+        <v>3.2</v>
       </c>
       <c r="G54" t="n">
-        <v>93.90000000000001</v>
+        <v>108.3</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>126.16</v>
+        <v>38.42</v>
       </c>
       <c r="K54" t="n">
-        <v>108.37</v>
+        <v>116.47</v>
       </c>
       <c r="L54" t="n">
-        <v>166.31</v>
+        <v>122.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:30:32</t>
+          <t>08:21:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2350,31 +2350,31 @@
         <v>1.66</v>
       </c>
       <c r="F55" t="n">
-        <v>5.64</v>
+        <v>5.07</v>
       </c>
       <c r="G55" t="n">
-        <v>102.4</v>
+        <v>99.2</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>61.95</v>
+        <v>120.65</v>
       </c>
       <c r="K55" t="n">
-        <v>117.87</v>
+        <v>80.12</v>
       </c>
       <c r="L55" t="n">
-        <v>133.16</v>
+        <v>144.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:35:50</t>
+          <t>08:27:23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="F56" t="n">
         <v>6.09</v>
       </c>
       <c r="G56" t="n">
-        <v>93</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.96</v>
+        <v>-165.29</v>
       </c>
       <c r="K56" t="n">
-        <v>-244.92</v>
+        <v>-84.09</v>
       </c>
       <c r="L56" t="n">
-        <v>244.99</v>
+        <v>185.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:37:15</t>
+          <t>08:28:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.65</v>
+        <v>2.66</v>
       </c>
       <c r="F57" t="n">
         <v>6.09</v>
       </c>
       <c r="G57" t="n">
-        <v>93.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-49.93</v>
+        <v>194.53</v>
       </c>
       <c r="K57" t="n">
-        <v>-191.8</v>
+        <v>-126.46</v>
       </c>
       <c r="L57" t="n">
-        <v>198.19</v>
+        <v>232.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:38:08</t>
+          <t>08:30:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="F58" t="n">
-        <v>6.09</v>
+        <v>2.39</v>
       </c>
       <c r="G58" t="n">
-        <v>98.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>2.88</v>
+        <v>-204.96</v>
       </c>
       <c r="K58" t="n">
-        <v>68.56999999999999</v>
+        <v>-52.94</v>
       </c>
       <c r="L58" t="n">
-        <v>68.63</v>
+        <v>211.68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:48:18</t>
+          <t>08:38:28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="F59" t="n">
-        <v>5.62</v>
+        <v>5.06</v>
       </c>
       <c r="G59" t="n">
-        <v>100.6</v>
+        <v>98.3</v>
       </c>
       <c r="H59" t="n">
-        <v>2.5</v>
+        <v>50.9</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>39.77</v>
+        <v>-23.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-48.01</v>
+        <v>30.18</v>
       </c>
       <c r="L59" t="n">
-        <v>62.34</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:49:07</t>
+          <t>08:39:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="F60" t="n">
         <v>6.09</v>
       </c>
       <c r="G60" t="n">
-        <v>98.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>49.2</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>28.04</v>
+        <v>6.3</v>
       </c>
       <c r="K60" t="n">
-        <v>49</v>
+        <v>28.86</v>
       </c>
       <c r="L60" t="n">
-        <v>56.46</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:51:22</t>
+          <t>08:41:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="F61" t="n">
         <v>6.09</v>
       </c>
       <c r="G61" t="n">
-        <v>98.5</v>
+        <v>109</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>19.8</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.95</v>
+        <v>-3.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.72</v>
+        <v>-30.31</v>
       </c>
       <c r="L61" t="n">
-        <v>55.99</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:56:34</t>
+          <t>08:44:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="F62" t="n">
         <v>6.09</v>
       </c>
       <c r="G62" t="n">
-        <v>95.7</v>
+        <v>101.1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>57.42</v>
+        <v>-57.58</v>
       </c>
       <c r="K62" t="n">
-        <v>33.93</v>
+        <v>-3.44</v>
       </c>
       <c r="L62" t="n">
-        <v>66.7</v>
+        <v>57.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:57:20</t>
+          <t>08:45:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="F63" t="n">
-        <v>2.33</v>
+        <v>6.09</v>
       </c>
       <c r="G63" t="n">
-        <v>94.59999999999999</v>
+        <v>104.6</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>33.2</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-15.22</v>
+        <v>-21.16</v>
       </c>
       <c r="K63" t="n">
-        <v>81.33</v>
+        <v>-54.52</v>
       </c>
       <c r="L63" t="n">
-        <v>82.73999999999999</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:59:47</t>
+          <t>08:47:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="F64" t="n">
-        <v>4.96</v>
+        <v>6.09</v>
       </c>
       <c r="G64" t="n">
-        <v>102.2</v>
+        <v>97.5</v>
       </c>
       <c r="H64" t="n">
-        <v>7.7</v>
+        <v>40.7</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>6.13</v>
+        <v>-43.92</v>
       </c>
       <c r="K64" t="n">
-        <v>73.06</v>
+        <v>-13.67</v>
       </c>
       <c r="L64" t="n">
-        <v>73.31</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:04:23</t>
+          <t>08:52:31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="F65" t="n">
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="G65" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.34999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="K65" t="n">
-        <v>29.64</v>
+        <v>24.59</v>
       </c>
       <c r="L65" t="n">
-        <v>87.52</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:05:08</t>
+          <t>08:54:40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="F66" t="n">
-        <v>2.5</v>
+        <v>6.09</v>
       </c>
       <c r="G66" t="n">
-        <v>98.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-100.73</v>
+        <v>-60.85</v>
       </c>
       <c r="K66" t="n">
-        <v>-10.82</v>
+        <v>-50.63</v>
       </c>
       <c r="L66" t="n">
-        <v>101.31</v>
+        <v>79.15000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:07:24</t>
+          <t>08:55:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="F67" t="n">
-        <v>4.81</v>
+        <v>6.09</v>
       </c>
       <c r="G67" t="n">
-        <v>111</v>
+        <v>91.3</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-67.72</v>
+        <v>-29.27</v>
       </c>
       <c r="K67" t="n">
-        <v>16.11</v>
+        <v>-58.76</v>
       </c>
       <c r="L67" t="n">
-        <v>69.61</v>
+        <v>65.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:10:41</t>
+          <t>09:00:52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="F68" t="n">
-        <v>1.93</v>
+        <v>3.37</v>
       </c>
       <c r="G68" t="n">
-        <v>89.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>147.27</v>
+        <v>46.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.99</v>
+        <v>-113.27</v>
       </c>
       <c r="L68" t="n">
-        <v>147.3</v>
+        <v>122.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:11:30</t>
+          <t>09:01:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="F69" t="n">
-        <v>2.98</v>
+        <v>3.71</v>
       </c>
       <c r="G69" t="n">
-        <v>93.2</v>
+        <v>89</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>49.9</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-113.71</v>
+        <v>20.49</v>
       </c>
       <c r="K69" t="n">
-        <v>-69.08</v>
+        <v>104.77</v>
       </c>
       <c r="L69" t="n">
-        <v>133.05</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:12:32</t>
+          <t>09:02:31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="F70" t="n">
         <v>6.09</v>
       </c>
       <c r="G70" t="n">
-        <v>104.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>138.05</v>
+        <v>-121.42</v>
       </c>
       <c r="K70" t="n">
-        <v>11.25</v>
+        <v>18.81</v>
       </c>
       <c r="L70" t="n">
-        <v>138.5</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:17:05</t>
+          <t>09:06:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="F71" t="n">
         <v>6.09</v>
       </c>
       <c r="G71" t="n">
-        <v>111.8</v>
+        <v>112.4</v>
       </c>
       <c r="H71" t="n">
-        <v>3.5</v>
+        <v>67.2</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>216.52</v>
+        <v>91.75</v>
       </c>
       <c r="K71" t="n">
-        <v>-78</v>
+        <v>151.98</v>
       </c>
       <c r="L71" t="n">
-        <v>230.14</v>
+        <v>177.52</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:18:50</t>
+          <t>09:08:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="F72" t="n">
-        <v>5.33</v>
+        <v>4.63</v>
       </c>
       <c r="G72" t="n">
-        <v>87.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4</v>
+        <v>33.3</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-5.17</v>
+        <v>128.88</v>
       </c>
       <c r="K72" t="n">
-        <v>-223.82</v>
+        <v>-25.98</v>
       </c>
       <c r="L72" t="n">
-        <v>223.88</v>
+        <v>131.48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:20:52</t>
+          <t>09:10:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="F73" t="n">
         <v>6.09</v>
       </c>
       <c r="G73" t="n">
-        <v>101.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>5.8</v>
+        <v>67</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>64.89</v>
+        <v>135.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-147.77</v>
+        <v>-85.13</v>
       </c>
       <c r="L73" t="n">
-        <v>161.39</v>
+        <v>160.21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:33:45</t>
+          <t>09:18:27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>6.09</v>
       </c>
       <c r="G74" t="n">
-        <v>100.9</v>
+        <v>84.3</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>11.09</v>
+        <v>41</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.79</v>
+        <v>-12.57</v>
       </c>
       <c r="L74" t="n">
-        <v>52.97</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:36:05</t>
+          <t>09:19:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="F75" t="n">
         <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>104.7</v>
+        <v>114.3</v>
       </c>
       <c r="H75" t="n">
-        <v>4.5</v>
+        <v>31.9</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>-14</v>
+        <v>-1.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-43.2</v>
+        <v>-31.34</v>
       </c>
       <c r="L75" t="n">
-        <v>45.41</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:37:16</t>
+          <t>09:21:24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="F76" t="n">
-        <v>2.62</v>
+        <v>3.47</v>
       </c>
       <c r="G76" t="n">
-        <v>85.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>6.4</v>
+        <v>64</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>30.33</v>
+        <v>-3.82</v>
       </c>
       <c r="K76" t="n">
-        <v>23.99</v>
+        <v>14.69</v>
       </c>
       <c r="L76" t="n">
-        <v>38.67</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:40:49</t>
+          <t>09:25:23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="F77" t="n">
-        <v>6.09</v>
+        <v>3.02</v>
       </c>
       <c r="G77" t="n">
-        <v>97.90000000000001</v>
+        <v>107.5</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>48.43</v>
+        <v>11.15</v>
       </c>
       <c r="K77" t="n">
-        <v>75.36</v>
+        <v>-36.91</v>
       </c>
       <c r="L77" t="n">
-        <v>89.58</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:43:33</t>
+          <t>09:27:32</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="F78" t="n">
         <v>6.09</v>
       </c>
       <c r="G78" t="n">
-        <v>112.9</v>
+        <v>91.3</v>
       </c>
       <c r="H78" t="n">
-        <v>4.3</v>
+        <v>29.3</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>64.52</v>
+        <v>21.22</v>
       </c>
       <c r="K78" t="n">
-        <v>74.29000000000001</v>
+        <v>46.13</v>
       </c>
       <c r="L78" t="n">
-        <v>98.39</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:44:36</t>
+          <t>09:28:55</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="F79" t="n">
-        <v>4.34</v>
+        <v>3.36</v>
       </c>
       <c r="G79" t="n">
-        <v>96.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="H79" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>63.4</v>
+        <v>-27.91</v>
       </c>
       <c r="K79" t="n">
-        <v>-29.93</v>
+        <v>42.83</v>
       </c>
       <c r="L79" t="n">
-        <v>70.11</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:49:37</t>
+          <t>09:32:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="F80" t="n">
-        <v>4.87</v>
+        <v>6.09</v>
       </c>
       <c r="G80" t="n">
-        <v>83.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I80" t="n">
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>4.88</v>
+        <v>67.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.63</v>
+        <v>30.92</v>
       </c>
       <c r="L80" t="n">
-        <v>83.78</v>
+        <v>73.94</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:51:27</t>
+          <t>09:34:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="F81" t="n">
-        <v>4.6</v>
+        <v>5.64</v>
       </c>
       <c r="G81" t="n">
-        <v>95.3</v>
+        <v>98.2</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.21</v>
+        <v>62.25</v>
       </c>
       <c r="K81" t="n">
-        <v>-107.45</v>
+        <v>-61.7</v>
       </c>
       <c r="L81" t="n">
-        <v>109.72</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:52:28</t>
+          <t>09:36:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="F82" t="n">
         <v>6.09</v>
       </c>
       <c r="G82" t="n">
-        <v>94.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3</v>
+        <v>25.1</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-57.41</v>
+        <v>-90.09999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-116.77</v>
+        <v>-10.43</v>
       </c>
       <c r="L82" t="n">
-        <v>130.12</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:57:08</t>
+          <t>09:40:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="F83" t="n">
-        <v>6.09</v>
+        <v>5.22</v>
       </c>
       <c r="G83" t="n">
-        <v>91.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>1.4</v>
+        <v>42.4</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-21.5</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>193.72</v>
+        <v>57.89</v>
       </c>
       <c r="L83" t="n">
-        <v>194.91</v>
+        <v>98.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:58:38</t>
+          <t>09:42:50</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="F84" t="n">
         <v>6.09</v>
       </c>
       <c r="G84" t="n">
-        <v>86.2</v>
+        <v>101.8</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>23.9</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>28.47</v>
+        <v>-98.25</v>
       </c>
       <c r="K84" t="n">
-        <v>100.94</v>
+        <v>62.48</v>
       </c>
       <c r="L84" t="n">
-        <v>104.88</v>
+        <v>116.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:00:20</t>
+          <t>09:43:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="F85" t="n">
-        <v>5.09</v>
+        <v>6.09</v>
       </c>
       <c r="G85" t="n">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-116.74</v>
+        <v>58.41</v>
       </c>
       <c r="K85" t="n">
-        <v>41.56</v>
+        <v>-94.45999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>123.91</v>
+        <v>111.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:05:28</t>
+          <t>09:47:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="F86" t="n">
-        <v>6.09</v>
+        <v>5.45</v>
       </c>
       <c r="G86" t="n">
-        <v>96.59999999999999</v>
+        <v>100.4</v>
       </c>
       <c r="H86" t="n">
-        <v>5.4</v>
+        <v>56.1</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-57.74</v>
+        <v>137.61</v>
       </c>
       <c r="K86" t="n">
-        <v>180.7</v>
+        <v>-109.5</v>
       </c>
       <c r="L86" t="n">
-        <v>189.7</v>
+        <v>175.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:06:58</t>
+          <t>09:49:12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="F87" t="n">
         <v>6.09</v>
       </c>
       <c r="G87" t="n">
-        <v>100.6</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>186.76</v>
+        <v>129.25</v>
       </c>
       <c r="K87" t="n">
-        <v>-97.81</v>
+        <v>100.24</v>
       </c>
       <c r="L87" t="n">
-        <v>210.82</v>
+        <v>163.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:08:36</t>
+          <t>09:50:43</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="F88" t="n">
-        <v>6.09</v>
+        <v>5.87</v>
       </c>
       <c r="G88" t="n">
-        <v>86.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H88" t="n">
-        <v>2.4</v>
+        <v>51.2</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>201.87</v>
+        <v>-174.66</v>
       </c>
       <c r="K88" t="n">
-        <v>57.76</v>
+        <v>12.42</v>
       </c>
       <c r="L88" t="n">
-        <v>209.97</v>
+        <v>175.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="F14" t="n">
-        <v>3.33</v>
+        <v>6.09</v>
       </c>
       <c r="G14" t="n">
-        <v>79.7</v>
+        <v>104.5</v>
       </c>
       <c r="H14" t="n">
-        <v>61</v>
+        <v>45.8</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.38</v>
+        <v>27.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-26.52</v>
+        <v>-35.87</v>
       </c>
       <c r="L14" t="n">
-        <v>26.62</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:31:53</t>
+          <t>06:30:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>0.88</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="G15" t="n">
-        <v>103.6</v>
+        <v>96.5</v>
       </c>
       <c r="H15" t="n">
-        <v>36.4</v>
+        <v>34.3</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>25.82</v>
+        <v>-18.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.4</v>
+        <v>26.01</v>
       </c>
       <c r="L15" t="n">
-        <v>27.15</v>
+        <v>31.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:34:03</t>
+          <t>06:33:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="F16" t="n">
-        <v>3.68</v>
+        <v>6.09</v>
       </c>
       <c r="G16" t="n">
-        <v>96</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>12.2</v>
+        <v>43.9</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>7.82</v>
+        <v>44.93</v>
       </c>
       <c r="K16" t="n">
-        <v>29.2</v>
+        <v>22.76</v>
       </c>
       <c r="L16" t="n">
-        <v>30.23</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:37:38</t>
+          <t>06:38:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>6.09</v>
       </c>
       <c r="G17" t="n">
-        <v>81.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="H17" t="n">
-        <v>43.7</v>
+        <v>30.4</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>12.16</v>
+        <v>-48.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.03</v>
+        <v>19.42</v>
       </c>
       <c r="L17" t="n">
-        <v>38.03</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:39:35</t>
+          <t>06:39:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="F18" t="n">
-        <v>4.72</v>
+        <v>3.82</v>
       </c>
       <c r="G18" t="n">
-        <v>99.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>17.4</v>
+        <v>41.4</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-33.21</v>
+        <v>-10.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-29.57</v>
+        <v>-48.38</v>
       </c>
       <c r="L18" t="n">
-        <v>44.47</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:40:28</t>
+          <t>06:40:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="F19" t="n">
-        <v>5.22</v>
+        <v>6.09</v>
       </c>
       <c r="G19" t="n">
-        <v>92</v>
+        <v>114.2</v>
       </c>
       <c r="H19" t="n">
-        <v>14.6</v>
+        <v>43.3</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-53.56</v>
+        <v>23.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.33</v>
+        <v>21.02</v>
       </c>
       <c r="L19" t="n">
-        <v>53.61</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>06:43:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="F20" t="n">
-        <v>3.91</v>
+        <v>5.69</v>
       </c>
       <c r="G20" t="n">
-        <v>106.9</v>
+        <v>103.9</v>
       </c>
       <c r="H20" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>15.96</v>
+        <v>62.42</v>
       </c>
       <c r="K20" t="n">
-        <v>67.83</v>
+        <v>-40.29</v>
       </c>
       <c r="L20" t="n">
-        <v>69.68000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:46:35</t>
+          <t>06:46:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="F21" t="n">
         <v>6.09</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>101.7</v>
       </c>
       <c r="H21" t="n">
-        <v>11.8</v>
+        <v>59.2</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>44.91</v>
+        <v>-79.81</v>
       </c>
       <c r="K21" t="n">
-        <v>-27</v>
+        <v>19.45</v>
       </c>
       <c r="L21" t="n">
-        <v>52.4</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:48:42</t>
+          <t>06:47:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="F22" t="n">
-        <v>6.09</v>
+        <v>4.48</v>
       </c>
       <c r="G22" t="n">
-        <v>97.40000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="H22" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>85.78</v>
+        <v>66.22</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.01</v>
+        <v>31.09</v>
       </c>
       <c r="L22" t="n">
-        <v>85.93000000000001</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:52:28</t>
+          <t>06:53:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="F23" t="n">
-        <v>1.82</v>
+        <v>3.01</v>
       </c>
       <c r="G23" t="n">
-        <v>98.40000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="H23" t="n">
-        <v>13.2</v>
+        <v>34.3</v>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>130.39</v>
+        <v>79.95</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.55</v>
+        <v>47.74</v>
       </c>
       <c r="L23" t="n">
-        <v>130.61</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:53:07</t>
+          <t>06:55:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1048,31 +1048,31 @@
         <v>1.58</v>
       </c>
       <c r="F24" t="n">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="G24" t="n">
-        <v>105.9</v>
+        <v>98.5</v>
       </c>
       <c r="H24" t="n">
-        <v>29.7</v>
+        <v>31.6</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-113.94</v>
+        <v>113</v>
       </c>
       <c r="K24" t="n">
-        <v>-37.18</v>
+        <v>65.27</v>
       </c>
       <c r="L24" t="n">
-        <v>119.86</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:55:00</t>
+          <t>06:56:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="F25" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="G25" t="n">
-        <v>82.5</v>
+        <v>84.5</v>
       </c>
       <c r="H25" t="n">
-        <v>25.5</v>
+        <v>42.6</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-143.58</v>
+        <v>86.11</v>
       </c>
       <c r="K25" t="n">
-        <v>115.78</v>
+        <v>-109.54</v>
       </c>
       <c r="L25" t="n">
-        <v>184.45</v>
+        <v>139.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:00:16</t>
+          <t>07:00:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="F26" t="n">
-        <v>1.67</v>
+        <v>4.32</v>
       </c>
       <c r="G26" t="n">
-        <v>101.2</v>
+        <v>93.8</v>
       </c>
       <c r="H26" t="n">
-        <v>47.3</v>
+        <v>61.1</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>343.06</v>
+        <v>75.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-150.67</v>
+        <v>-186.6</v>
       </c>
       <c r="L26" t="n">
-        <v>374.69</v>
+        <v>201.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:01:28</t>
+          <t>07:02:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="F27" t="n">
-        <v>2.19</v>
+        <v>4.51</v>
       </c>
       <c r="G27" t="n">
-        <v>102</v>
+        <v>111.5</v>
       </c>
       <c r="H27" t="n">
-        <v>60.1</v>
+        <v>47.5</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>40.48</v>
+        <v>155.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-129.84</v>
+        <v>-63.12</v>
       </c>
       <c r="L27" t="n">
-        <v>136</v>
+        <v>167.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:03:06</t>
+          <t>07:04:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="F28" t="n">
         <v>6.09</v>
       </c>
       <c r="G28" t="n">
-        <v>94.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>188.48</v>
+        <v>-92.66</v>
       </c>
       <c r="K28" t="n">
-        <v>-52.36</v>
+        <v>-149.62</v>
       </c>
       <c r="L28" t="n">
-        <v>195.62</v>
+        <v>175.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:11:14</t>
+          <t>07:14:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F29" t="n">
-        <v>6.09</v>
+        <v>5.01</v>
       </c>
       <c r="G29" t="n">
-        <v>96.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="H29" t="n">
-        <v>28.1</v>
+        <v>47.1</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.78</v>
+        <v>-17.16</v>
       </c>
       <c r="K29" t="n">
-        <v>38.47</v>
+        <v>-14.88</v>
       </c>
       <c r="L29" t="n">
-        <v>38.66</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:13:36</t>
+          <t>07:16:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="F30" t="n">
         <v>6.09</v>
       </c>
       <c r="G30" t="n">
-        <v>80.59999999999999</v>
+        <v>112.3</v>
       </c>
       <c r="H30" t="n">
-        <v>43.3</v>
+        <v>58.8</v>
       </c>
       <c r="I30" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>13.74</v>
+        <v>-3.88</v>
       </c>
       <c r="K30" t="n">
-        <v>27.09</v>
+        <v>33.33</v>
       </c>
       <c r="L30" t="n">
-        <v>30.38</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:14:33</t>
+          <t>07:18:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="F31" t="n">
-        <v>6.09</v>
+        <v>5.33</v>
       </c>
       <c r="G31" t="n">
-        <v>101.5</v>
+        <v>93.8</v>
       </c>
       <c r="H31" t="n">
-        <v>33.9</v>
+        <v>14.6</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>10.28</v>
+        <v>-21.8</v>
       </c>
       <c r="K31" t="n">
-        <v>34.87</v>
+        <v>-27.54</v>
       </c>
       <c r="L31" t="n">
-        <v>36.35</v>
+        <v>35.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:19:39</t>
+          <t>07:22:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.36</v>
+        <v>2.64</v>
       </c>
       <c r="F32" t="n">
-        <v>5.31</v>
+        <v>6.09</v>
       </c>
       <c r="G32" t="n">
-        <v>93.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="H32" t="n">
-        <v>52.7</v>
+        <v>13.9</v>
       </c>
       <c r="I32" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>2.26</v>
+        <v>-27.59</v>
       </c>
       <c r="K32" t="n">
-        <v>33.43</v>
+        <v>-53.45</v>
       </c>
       <c r="L32" t="n">
-        <v>33.51</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:20:51</t>
+          <t>07:25:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="F33" t="n">
         <v>6.09</v>
       </c>
       <c r="G33" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="H33" t="n">
-        <v>13.9</v>
+        <v>36.6</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-23.99</v>
+        <v>-45.03</v>
       </c>
       <c r="K33" t="n">
-        <v>42.87</v>
+        <v>-6.26</v>
       </c>
       <c r="L33" t="n">
-        <v>49.13</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:21:22</t>
+          <t>07:27:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="F34" t="n">
-        <v>5.06</v>
+        <v>5.59</v>
       </c>
       <c r="G34" t="n">
-        <v>90.7</v>
+        <v>103.3</v>
       </c>
       <c r="H34" t="n">
-        <v>24.2</v>
+        <v>23.1</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-41.72</v>
+        <v>-30.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-35.08</v>
+        <v>-28.64</v>
       </c>
       <c r="L34" t="n">
-        <v>54.5</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:27:08</t>
+          <t>07:30:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="F35" t="n">
-        <v>6.09</v>
+        <v>3.42</v>
       </c>
       <c r="G35" t="n">
-        <v>110.5</v>
+        <v>78</v>
       </c>
       <c r="H35" t="n">
-        <v>47.5</v>
+        <v>39.2</v>
       </c>
       <c r="I35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.77</v>
+        <v>40.25</v>
       </c>
       <c r="K35" t="n">
-        <v>-64.81999999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>65.41</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:29:37</t>
+          <t>07:32:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="F36" t="n">
-        <v>5.42</v>
+        <v>6.09</v>
       </c>
       <c r="G36" t="n">
-        <v>88</v>
+        <v>104.4</v>
       </c>
       <c r="H36" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="I36" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-54.14</v>
+        <v>26.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-20.62</v>
+        <v>56.47</v>
       </c>
       <c r="L36" t="n">
-        <v>57.93</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:30:54</t>
+          <t>07:33:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="F37" t="n">
-        <v>1.98</v>
+        <v>1.49</v>
       </c>
       <c r="G37" t="n">
-        <v>91.90000000000001</v>
+        <v>117.4</v>
       </c>
       <c r="H37" t="n">
-        <v>34.2</v>
+        <v>39.1</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>61.45</v>
+        <v>27.89</v>
       </c>
       <c r="K37" t="n">
-        <v>-18.73</v>
+        <v>-73.94</v>
       </c>
       <c r="L37" t="n">
-        <v>64.23999999999999</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:36:03</t>
+          <t>07:37:49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="F38" t="n">
-        <v>4.33</v>
+        <v>6.09</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3</v>
+        <v>81.7</v>
       </c>
       <c r="H38" t="n">
-        <v>90.7</v>
+        <v>58</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>103.7</v>
+        <v>128.38</v>
       </c>
       <c r="K38" t="n">
-        <v>-59.28</v>
+        <v>-71.39</v>
       </c>
       <c r="L38" t="n">
-        <v>119.45</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:37:24</t>
+          <t>07:40:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="F39" t="n">
-        <v>6.09</v>
+        <v>5.87</v>
       </c>
       <c r="G39" t="n">
-        <v>105.8</v>
+        <v>94</v>
       </c>
       <c r="H39" t="n">
-        <v>58.4</v>
+        <v>29.1</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-30.51</v>
+        <v>3.55</v>
       </c>
       <c r="K39" t="n">
-        <v>-120.63</v>
+        <v>-49.11</v>
       </c>
       <c r="L39" t="n">
-        <v>124.43</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:38:36</t>
+          <t>07:42:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="F40" t="n">
-        <v>5.15</v>
+        <v>5.48</v>
       </c>
       <c r="G40" t="n">
-        <v>109.1</v>
+        <v>112.7</v>
       </c>
       <c r="H40" t="n">
-        <v>36.1</v>
+        <v>32.1</v>
       </c>
       <c r="I40" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-26.88</v>
+        <v>-48.77</v>
       </c>
       <c r="K40" t="n">
-        <v>-117.59</v>
+        <v>-103.71</v>
       </c>
       <c r="L40" t="n">
-        <v>120.62</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:42:00</t>
+          <t>07:48:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1765,28 +1765,28 @@
         <v>6.09</v>
       </c>
       <c r="G41" t="n">
-        <v>108.3</v>
+        <v>94.5</v>
       </c>
       <c r="H41" t="n">
-        <v>53.6</v>
+        <v>25.5</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>23.43</v>
+        <v>162.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-138.44</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>140.41</v>
+        <v>183.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:42:50</t>
+          <t>07:49:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="F42" t="n">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
       <c r="G42" t="n">
-        <v>96.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>78.8</v>
+        <v>51.7</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>113.71</v>
+        <v>-206.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-123.68</v>
+        <v>10.18</v>
       </c>
       <c r="L42" t="n">
-        <v>168.01</v>
+        <v>207.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:44:19</t>
+          <t>07:51:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="F43" t="n">
-        <v>5.83</v>
+        <v>6.09</v>
       </c>
       <c r="G43" t="n">
-        <v>114.9</v>
+        <v>103.5</v>
       </c>
       <c r="H43" t="n">
-        <v>54.8</v>
+        <v>18.9</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>80.3</v>
+        <v>-83.36</v>
       </c>
       <c r="K43" t="n">
-        <v>164.21</v>
+        <v>109.04</v>
       </c>
       <c r="L43" t="n">
-        <v>182.79</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:53:45</t>
+          <t>08:02:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="F44" t="n">
-        <v>6.09</v>
+        <v>3.83</v>
       </c>
       <c r="G44" t="n">
-        <v>103</v>
+        <v>108.6</v>
       </c>
       <c r="H44" t="n">
-        <v>52.7</v>
+        <v>40.6</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>28.92</v>
+        <v>-27.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.64</v>
+        <v>-17.82</v>
       </c>
       <c r="L44" t="n">
-        <v>29.04</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:55:50</t>
+          <t>08:05:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="F45" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="G45" t="n">
-        <v>97.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>9.699999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>36</v>
+        <v>11.88</v>
       </c>
       <c r="K45" t="n">
-        <v>22.59</v>
+        <v>30.39</v>
       </c>
       <c r="L45" t="n">
-        <v>42.5</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:56:38</t>
+          <t>08:06:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="F46" t="n">
-        <v>1.82</v>
+        <v>6.09</v>
       </c>
       <c r="G46" t="n">
-        <v>97.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="H46" t="n">
-        <v>14</v>
+        <v>38.9</v>
       </c>
       <c r="I46" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.83</v>
+        <v>0.7</v>
       </c>
       <c r="K46" t="n">
-        <v>-32.4</v>
+        <v>-36.6</v>
       </c>
       <c r="L46" t="n">
-        <v>33.58</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:00:13</t>
+          <t>08:12:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="F47" t="n">
-        <v>5.69</v>
+        <v>6.09</v>
       </c>
       <c r="G47" t="n">
-        <v>110.4</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>35.9</v>
+        <v>52.7</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-36.92</v>
+        <v>-1.46</v>
       </c>
       <c r="K47" t="n">
-        <v>41.29</v>
+        <v>36.59</v>
       </c>
       <c r="L47" t="n">
-        <v>55.39</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:01:55</t>
+          <t>08:14:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="F48" t="n">
-        <v>1.76</v>
+        <v>6.09</v>
       </c>
       <c r="G48" t="n">
-        <v>93.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="H48" t="n">
-        <v>47.1</v>
+        <v>40.1</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-13.3</v>
+        <v>-38.6</v>
       </c>
       <c r="K48" t="n">
-        <v>-45.29</v>
+        <v>1.55</v>
       </c>
       <c r="L48" t="n">
-        <v>47.2</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:04:25</t>
+          <t>08:16:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="F49" t="n">
-        <v>5.91</v>
+        <v>4.14</v>
       </c>
       <c r="G49" t="n">
-        <v>81.7</v>
+        <v>90.7</v>
       </c>
       <c r="H49" t="n">
-        <v>47.5</v>
+        <v>24.2</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>19.65</v>
+        <v>-47.35</v>
       </c>
       <c r="K49" t="n">
-        <v>41</v>
+        <v>-34.44</v>
       </c>
       <c r="L49" t="n">
-        <v>45.46</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:09:28</t>
+          <t>08:22:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="F50" t="n">
-        <v>4.36</v>
+        <v>6.09</v>
       </c>
       <c r="G50" t="n">
-        <v>102</v>
+        <v>101.2</v>
       </c>
       <c r="H50" t="n">
-        <v>39.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>70.17</v>
+        <v>-52.42</v>
       </c>
       <c r="K50" t="n">
-        <v>9.94</v>
+        <v>61.65</v>
       </c>
       <c r="L50" t="n">
-        <v>70.87</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:10:33</t>
+          <t>08:24:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="F51" t="n">
         <v>6.09</v>
       </c>
       <c r="G51" t="n">
-        <v>99.5</v>
+        <v>82</v>
       </c>
       <c r="H51" t="n">
-        <v>71</v>
+        <v>14.5</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-85.5</v>
+        <v>-14.37</v>
       </c>
       <c r="K51" t="n">
-        <v>31.68</v>
+        <v>81.09</v>
       </c>
       <c r="L51" t="n">
-        <v>91.18000000000001</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:13:02</t>
+          <t>08:25:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="F52" t="n">
-        <v>3.13</v>
+        <v>6.09</v>
       </c>
       <c r="G52" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>34.2</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>73.36</v>
+        <v>74.67</v>
       </c>
       <c r="K52" t="n">
-        <v>-73.41</v>
+        <v>-24.67</v>
       </c>
       <c r="L52" t="n">
-        <v>103.78</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:18:05</t>
+          <t>08:30:31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F53" t="n">
-        <v>5.21</v>
+        <v>4.81</v>
       </c>
       <c r="G53" t="n">
-        <v>93.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="H53" t="n">
-        <v>49.3</v>
+        <v>52.7</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>24.61</v>
+        <v>-93.84999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>93.45</v>
+        <v>41.24</v>
       </c>
       <c r="L53" t="n">
-        <v>96.63</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:19:59</t>
+          <t>08:31:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="F54" t="n">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="G54" t="n">
-        <v>108.3</v>
+        <v>105.8</v>
       </c>
       <c r="H54" t="n">
-        <v>96</v>
+        <v>58.4</v>
       </c>
       <c r="I54" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>38.42</v>
+        <v>-45.08</v>
       </c>
       <c r="K54" t="n">
-        <v>116.47</v>
+        <v>-122.18</v>
       </c>
       <c r="L54" t="n">
-        <v>122.64</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:21:08</t>
+          <t>08:32:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="F55" t="n">
-        <v>5.07</v>
+        <v>5.6</v>
       </c>
       <c r="G55" t="n">
-        <v>99.2</v>
+        <v>94.2</v>
       </c>
       <c r="H55" t="n">
-        <v>7.8</v>
+        <v>67.2</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>120.65</v>
+        <v>-42.49</v>
       </c>
       <c r="K55" t="n">
-        <v>80.12</v>
+        <v>116.46</v>
       </c>
       <c r="L55" t="n">
-        <v>144.83</v>
+        <v>123.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:27:23</t>
+          <t>08:36:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="F56" t="n">
-        <v>6.09</v>
+        <v>4.59</v>
       </c>
       <c r="G56" t="n">
-        <v>96.90000000000001</v>
+        <v>108.3</v>
       </c>
       <c r="H56" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="I56" t="n">
         <v>16</v>
       </c>
-      <c r="I56" t="n">
-        <v>21</v>
-      </c>
       <c r="J56" t="n">
-        <v>-165.29</v>
+        <v>6.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-84.09</v>
+        <v>-150.02</v>
       </c>
       <c r="L56" t="n">
-        <v>185.45</v>
+        <v>150.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:28:24</t>
+          <t>08:37:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.66</v>
+        <v>1.59</v>
       </c>
       <c r="F57" t="n">
         <v>6.09</v>
       </c>
       <c r="G57" t="n">
-        <v>97.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>36.4</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>194.53</v>
+        <v>69.67</v>
       </c>
       <c r="K57" t="n">
-        <v>-126.46</v>
+        <v>-166.96</v>
       </c>
       <c r="L57" t="n">
-        <v>232.02</v>
+        <v>180.91</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:30:43</t>
+          <t>08:38:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="F58" t="n">
-        <v>2.39</v>
+        <v>6.09</v>
       </c>
       <c r="G58" t="n">
-        <v>102</v>
+        <v>114.9</v>
       </c>
       <c r="H58" t="n">
-        <v>57.9</v>
+        <v>54.8</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-204.96</v>
+        <v>66.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-52.94</v>
+        <v>197.91</v>
       </c>
       <c r="L58" t="n">
-        <v>211.68</v>
+        <v>208.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:38:28</t>
+          <t>08:49:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="F59" t="n">
-        <v>5.06</v>
+        <v>6.09</v>
       </c>
       <c r="G59" t="n">
-        <v>98.3</v>
+        <v>103.2</v>
       </c>
       <c r="H59" t="n">
-        <v>50.9</v>
+        <v>52</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-23.79</v>
+        <v>28.72</v>
       </c>
       <c r="K59" t="n">
-        <v>30.18</v>
+        <v>-16.74</v>
       </c>
       <c r="L59" t="n">
-        <v>38.43</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:39:55</t>
+          <t>08:50:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="F60" t="n">
-        <v>6.09</v>
+        <v>2.84</v>
       </c>
       <c r="G60" t="n">
-        <v>93.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>49.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>6.3</v>
+        <v>35.06</v>
       </c>
       <c r="K60" t="n">
-        <v>28.86</v>
+        <v>27.43</v>
       </c>
       <c r="L60" t="n">
-        <v>29.54</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:41:06</t>
+          <t>08:52:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="F61" t="n">
-        <v>6.09</v>
+        <v>2.28</v>
       </c>
       <c r="G61" t="n">
-        <v>109</v>
+        <v>91.3</v>
       </c>
       <c r="H61" t="n">
-        <v>19.8</v>
+        <v>39.2</v>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.91</v>
+        <v>-24.16</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.31</v>
+        <v>11.19</v>
       </c>
       <c r="L61" t="n">
-        <v>30.56</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:44:23</t>
+          <t>08:57:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="F62" t="n">
-        <v>6.09</v>
+        <v>4.75</v>
       </c>
       <c r="G62" t="n">
-        <v>101.1</v>
+        <v>110.4</v>
       </c>
       <c r="H62" t="n">
-        <v>9.699999999999999</v>
+        <v>35.9</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-57.58</v>
+        <v>-42.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.44</v>
+        <v>42.22</v>
       </c>
       <c r="L62" t="n">
-        <v>57.69</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:45:29</t>
+          <t>08:58:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="F63" t="n">
-        <v>6.09</v>
+        <v>1.84</v>
       </c>
       <c r="G63" t="n">
-        <v>104.6</v>
+        <v>82</v>
       </c>
       <c r="H63" t="n">
-        <v>33.2</v>
+        <v>28</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-21.16</v>
+        <v>40.85</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.52</v>
+        <v>34.42</v>
       </c>
       <c r="L63" t="n">
-        <v>58.48</v>
+        <v>53.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:47:11</t>
+          <t>09:01:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="F64" t="n">
         <v>6.09</v>
       </c>
       <c r="G64" t="n">
-        <v>97.5</v>
+        <v>81.7</v>
       </c>
       <c r="H64" t="n">
-        <v>40.7</v>
+        <v>47.5</v>
       </c>
       <c r="I64" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-43.92</v>
+        <v>19.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.67</v>
+        <v>50.43</v>
       </c>
       <c r="L64" t="n">
-        <v>45.99</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:52:31</t>
+          <t>09:05:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="F65" t="n">
-        <v>6.09</v>
+        <v>4.82</v>
       </c>
       <c r="G65" t="n">
-        <v>96</v>
+        <v>92.3</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>49.4</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>68.75</v>
+        <v>60.47</v>
       </c>
       <c r="K65" t="n">
-        <v>24.59</v>
+        <v>-56.4</v>
       </c>
       <c r="L65" t="n">
-        <v>73.02</v>
+        <v>82.69</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:54:40</t>
+          <t>09:07:35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="F66" t="n">
         <v>6.09</v>
       </c>
       <c r="G66" t="n">
-        <v>101.3</v>
+        <v>99.5</v>
       </c>
       <c r="H66" t="n">
-        <v>28.7</v>
+        <v>71</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-60.85</v>
+        <v>-95.81999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-50.63</v>
+        <v>32.65</v>
       </c>
       <c r="L66" t="n">
-        <v>79.15000000000001</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:55:43</t>
+          <t>09:08:42</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="F67" t="n">
-        <v>6.09</v>
+        <v>3.63</v>
       </c>
       <c r="G67" t="n">
-        <v>91.3</v>
+        <v>91.2</v>
       </c>
       <c r="H67" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-29.27</v>
+        <v>23.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-58.76</v>
+        <v>74.73</v>
       </c>
       <c r="L67" t="n">
-        <v>65.64</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:00:52</t>
+          <t>09:12:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="F68" t="n">
-        <v>3.37</v>
+        <v>6.09</v>
       </c>
       <c r="G68" t="n">
-        <v>98.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="H68" t="n">
-        <v>49.7</v>
+        <v>27.9</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>46.05</v>
+        <v>88.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-113.27</v>
+        <v>162.74</v>
       </c>
       <c r="L68" t="n">
-        <v>122.27</v>
+        <v>185.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:01:50</t>
+          <t>09:15:14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="F69" t="n">
-        <v>3.71</v>
+        <v>6.09</v>
       </c>
       <c r="G69" t="n">
-        <v>89</v>
+        <v>103.6</v>
       </c>
       <c r="H69" t="n">
-        <v>49.9</v>
+        <v>71.5</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>20.49</v>
+        <v>85.53</v>
       </c>
       <c r="K69" t="n">
-        <v>104.77</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>106.76</v>
+        <v>125.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:02:31</t>
+          <t>09:16:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="F70" t="n">
-        <v>6.09</v>
+        <v>2.6</v>
       </c>
       <c r="G70" t="n">
-        <v>98.09999999999999</v>
+        <v>107</v>
       </c>
       <c r="H70" t="n">
-        <v>26.6</v>
+        <v>42.4</v>
       </c>
       <c r="I70" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-121.42</v>
+        <v>135.92</v>
       </c>
       <c r="K70" t="n">
-        <v>18.81</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>122.87</v>
+        <v>136.28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:06:33</t>
+          <t>09:20:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="F71" t="n">
-        <v>6.09</v>
+        <v>3.42</v>
       </c>
       <c r="G71" t="n">
-        <v>112.4</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>67.2</v>
+        <v>50.1</v>
       </c>
       <c r="I71" t="n">
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>91.75</v>
+        <v>-21.98</v>
       </c>
       <c r="K71" t="n">
-        <v>151.98</v>
+        <v>186.47</v>
       </c>
       <c r="L71" t="n">
-        <v>177.52</v>
+        <v>187.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:08:29</t>
+          <t>09:22:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="F72" t="n">
-        <v>4.63</v>
+        <v>4.78</v>
       </c>
       <c r="G72" t="n">
-        <v>97.3</v>
+        <v>98.3</v>
       </c>
       <c r="H72" t="n">
-        <v>33.3</v>
+        <v>37.2</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>128.88</v>
+        <v>159.25</v>
       </c>
       <c r="K72" t="n">
-        <v>-25.98</v>
+        <v>-191.29</v>
       </c>
       <c r="L72" t="n">
-        <v>131.48</v>
+        <v>248.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:10:12</t>
+          <t>09:24:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="F73" t="n">
         <v>6.09</v>
       </c>
       <c r="G73" t="n">
-        <v>84.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H73" t="n">
-        <v>67</v>
+        <v>45.3</v>
       </c>
       <c r="I73" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>135.72</v>
+        <v>-144.61</v>
       </c>
       <c r="K73" t="n">
-        <v>-85.13</v>
+        <v>-35.28</v>
       </c>
       <c r="L73" t="n">
-        <v>160.21</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:18:27</t>
+          <t>09:36:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="F74" t="n">
         <v>6.09</v>
       </c>
       <c r="G74" t="n">
-        <v>84.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>29.5</v>
+        <v>40.3</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>41</v>
+        <v>-23.81</v>
       </c>
       <c r="K74" t="n">
-        <v>-12.57</v>
+        <v>31.21</v>
       </c>
       <c r="L74" t="n">
-        <v>42.89</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:19:54</t>
+          <t>09:37:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="F75" t="n">
         <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>114.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>31.9</v>
+        <v>21.4</v>
       </c>
       <c r="I75" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.9</v>
+        <v>18.55</v>
       </c>
       <c r="K75" t="n">
-        <v>-31.34</v>
+        <v>31.57</v>
       </c>
       <c r="L75" t="n">
-        <v>31.4</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:21:24</t>
+          <t>09:39:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="F76" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="G76" t="n">
-        <v>91.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="H76" t="n">
-        <v>64</v>
+        <v>15.1</v>
       </c>
       <c r="I76" t="n">
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.82</v>
+        <v>0.4</v>
       </c>
       <c r="K76" t="n">
-        <v>14.69</v>
+        <v>38.54</v>
       </c>
       <c r="L76" t="n">
-        <v>15.18</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:25:23</t>
+          <t>09:43:52</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="F77" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="G77" t="n">
-        <v>107.5</v>
+        <v>91.5</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>11.15</v>
+        <v>-48.05</v>
       </c>
       <c r="K77" t="n">
-        <v>-36.91</v>
+        <v>28.63</v>
       </c>
       <c r="L77" t="n">
-        <v>38.56</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:27:32</t>
+          <t>09:45:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="F78" t="n">
-        <v>6.09</v>
+        <v>5.97</v>
       </c>
       <c r="G78" t="n">
-        <v>91.3</v>
+        <v>110.4</v>
       </c>
       <c r="H78" t="n">
-        <v>29.3</v>
+        <v>56.1</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>21.22</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>46.13</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>50.78</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:28:55</t>
+          <t>09:47:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="F79" t="n">
-        <v>3.36</v>
+        <v>6.09</v>
       </c>
       <c r="G79" t="n">
-        <v>84.5</v>
+        <v>108.6</v>
       </c>
       <c r="H79" t="n">
-        <v>9.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="I79" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-27.91</v>
+        <v>-54.14</v>
       </c>
       <c r="K79" t="n">
-        <v>42.83</v>
+        <v>45.12</v>
       </c>
       <c r="L79" t="n">
-        <v>51.12</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:32:43</t>
+          <t>09:53:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="F80" t="n">
-        <v>6.09</v>
+        <v>3.96</v>
       </c>
       <c r="G80" t="n">
-        <v>89</v>
+        <v>105.9</v>
       </c>
       <c r="H80" t="n">
-        <v>65.90000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>67.17</v>
+        <v>-44.24</v>
       </c>
       <c r="K80" t="n">
-        <v>30.92</v>
+        <v>-64.65000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>73.94</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:34:44</t>
+          <t>09:55:42</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="F81" t="n">
-        <v>5.64</v>
+        <v>3.91</v>
       </c>
       <c r="G81" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="H81" t="n">
-        <v>69.3</v>
+        <v>34.5</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>62.25</v>
+        <v>-19.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.7</v>
+        <v>83.89</v>
       </c>
       <c r="L81" t="n">
-        <v>87.65000000000001</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:36:54</t>
+          <t>09:57:48</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="F82" t="n">
-        <v>6.09</v>
+        <v>5.55</v>
       </c>
       <c r="G82" t="n">
-        <v>97.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H82" t="n">
-        <v>25.1</v>
+        <v>22.7</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.09999999999999</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.43</v>
+        <v>43.52</v>
       </c>
       <c r="L82" t="n">
-        <v>90.7</v>
+        <v>105.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:40:41</t>
+          <t>10:03:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="F83" t="n">
-        <v>5.22</v>
+        <v>6.09</v>
       </c>
       <c r="G83" t="n">
-        <v>92.90000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="H83" t="n">
-        <v>42.4</v>
+        <v>30</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-80.20999999999999</v>
+        <v>-62.87</v>
       </c>
       <c r="K83" t="n">
-        <v>57.89</v>
+        <v>-152.8</v>
       </c>
       <c r="L83" t="n">
-        <v>98.92</v>
+        <v>165.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:42:50</t>
+          <t>10:05:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="F84" t="n">
         <v>6.09</v>
       </c>
       <c r="G84" t="n">
-        <v>101.8</v>
+        <v>82.3</v>
       </c>
       <c r="H84" t="n">
-        <v>23.9</v>
+        <v>17.1</v>
       </c>
       <c r="I84" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-98.25</v>
+        <v>103.48</v>
       </c>
       <c r="K84" t="n">
-        <v>62.48</v>
+        <v>84.64</v>
       </c>
       <c r="L84" t="n">
-        <v>116.44</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:43:39</t>
+          <t>10:07:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="F85" t="n">
-        <v>6.09</v>
+        <v>5.08</v>
       </c>
       <c r="G85" t="n">
-        <v>95.3</v>
+        <v>90.7</v>
       </c>
       <c r="H85" t="n">
-        <v>42.3</v>
+        <v>18.8</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>58.41</v>
+        <v>26.81</v>
       </c>
       <c r="K85" t="n">
-        <v>-94.45999999999999</v>
+        <v>139.61</v>
       </c>
       <c r="L85" t="n">
-        <v>111.06</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:47:41</t>
+          <t>10:11:48</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="F86" t="n">
-        <v>5.45</v>
+        <v>6.09</v>
       </c>
       <c r="G86" t="n">
-        <v>100.4</v>
+        <v>97.5</v>
       </c>
       <c r="H86" t="n">
-        <v>56.1</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>137.61</v>
+        <v>24.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-109.5</v>
+        <v>-182.82</v>
       </c>
       <c r="L86" t="n">
-        <v>175.86</v>
+        <v>184.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:49:12</t>
+          <t>10:13:13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F87" t="n">
-        <v>6.09</v>
+        <v>4.9</v>
       </c>
       <c r="G87" t="n">
-        <v>87.40000000000001</v>
+        <v>108.2</v>
       </c>
       <c r="H87" t="n">
-        <v>42.5</v>
+        <v>38</v>
       </c>
       <c r="I87" t="n">
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>129.25</v>
+        <v>-111.83</v>
       </c>
       <c r="K87" t="n">
-        <v>100.24</v>
+        <v>172.85</v>
       </c>
       <c r="L87" t="n">
-        <v>163.57</v>
+        <v>205.87</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:50:43</t>
+          <t>10:14:41</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="F88" t="n">
-        <v>5.87</v>
+        <v>6.09</v>
       </c>
       <c r="G88" t="n">
-        <v>95.2</v>
+        <v>109</v>
       </c>
       <c r="H88" t="n">
-        <v>51.2</v>
+        <v>64</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-174.66</v>
+        <v>147.27</v>
       </c>
       <c r="K88" t="n">
-        <v>12.42</v>
+        <v>-122.74</v>
       </c>
       <c r="L88" t="n">
-        <v>175.1</v>
+        <v>191.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-06.xlsx
+++ b/output/2024-09-06.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>31.31</v>
+        <v>30.96</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.01</v>
+        <v>-9.9</v>
       </c>
       <c r="L14" t="n">
-        <v>32.88</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-22.21</v>
+        <v>-22.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.37</v>
+        <v>-24.2</v>
       </c>
       <c r="L15" t="n">
-        <v>32.97</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>40.29</v>
+        <v>37.32</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.39</v>
+        <v>-19.81</v>
       </c>
       <c r="L16" t="n">
-        <v>45.61</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-34.66</v>
+        <v>-35.81</v>
       </c>
       <c r="K17" t="n">
-        <v>33.49</v>
+        <v>34.59</v>
       </c>
       <c r="L17" t="n">
-        <v>48.2</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.78</v>
+        <v>-20.9</v>
       </c>
       <c r="K18" t="n">
-        <v>32.47</v>
+        <v>32.66</v>
       </c>
       <c r="L18" t="n">
-        <v>38.55</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.14</v>
+        <v>-26.2</v>
       </c>
       <c r="K19" t="n">
-        <v>54</v>
+        <v>50.28</v>
       </c>
       <c r="L19" t="n">
-        <v>60.9</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>75.56999999999999</v>
+        <v>74.08</v>
       </c>
       <c r="K20" t="n">
-        <v>52.82</v>
+        <v>51.78</v>
       </c>
       <c r="L20" t="n">
-        <v>92.2</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>23.41</v>
+        <v>25.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-55.4</v>
+        <v>-60.15</v>
       </c>
       <c r="L21" t="n">
-        <v>60.14</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>89.56</v>
+        <v>87.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-46.84</v>
+        <v>-45.6</v>
       </c>
       <c r="L22" t="n">
-        <v>101.07</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-65.2</v>
+        <v>-77.51000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>26.9</v>
+        <v>31.98</v>
       </c>
       <c r="L23" t="n">
-        <v>70.53</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>79.75</v>
+        <v>87.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-55.23</v>
+        <v>-60.67</v>
       </c>
       <c r="L24" t="n">
-        <v>97.01000000000001</v>
+        <v>106.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>138.58</v>
+        <v>134.73</v>
       </c>
       <c r="K25" t="n">
-        <v>123.79</v>
+        <v>120.35</v>
       </c>
       <c r="L25" t="n">
-        <v>185.82</v>
+        <v>180.66</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-155.42</v>
+        <v>-166.14</v>
       </c>
       <c r="K26" t="n">
-        <v>27.59</v>
+        <v>29.5</v>
       </c>
       <c r="L26" t="n">
-        <v>157.85</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.79</v>
+        <v>-17.68</v>
       </c>
       <c r="K27" t="n">
-        <v>127.84</v>
+        <v>152.79</v>
       </c>
       <c r="L27" t="n">
-        <v>128.69</v>
+        <v>153.81</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>84.45999999999999</v>
+        <v>98.27</v>
       </c>
       <c r="K28" t="n">
-        <v>69.29000000000001</v>
+        <v>80.62</v>
       </c>
       <c r="L28" t="n">
-        <v>109.24</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-20.64</v>
+        <v>-21.35</v>
       </c>
       <c r="K29" t="n">
-        <v>23.94</v>
+        <v>24.77</v>
       </c>
       <c r="L29" t="n">
-        <v>31.61</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.54</v>
+        <v>-37.09</v>
       </c>
       <c r="K30" t="n">
-        <v>-12.24</v>
+        <v>-11.78</v>
       </c>
       <c r="L30" t="n">
-        <v>40.43</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>39.49</v>
+        <v>36.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="L31" t="n">
-        <v>39.51</v>
+        <v>36.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>22.49</v>
+        <v>21.54</v>
       </c>
       <c r="K32" t="n">
-        <v>47.86</v>
+        <v>45.83</v>
       </c>
       <c r="L32" t="n">
-        <v>52.88</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.67</v>
+        <v>-4.46</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.02</v>
+        <v>-44.91</v>
       </c>
       <c r="L33" t="n">
-        <v>47.25</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>31.98</v>
+        <v>30.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-44.84</v>
+        <v>-42.81</v>
       </c>
       <c r="L34" t="n">
-        <v>55.08</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>29.55</v>
+        <v>30.7</v>
       </c>
       <c r="K35" t="n">
-        <v>-56.18</v>
+        <v>-58.36</v>
       </c>
       <c r="L35" t="n">
-        <v>63.48</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-83.73</v>
+        <v>-85.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-24.32</v>
+        <v>-24.75</v>
       </c>
       <c r="L36" t="n">
-        <v>87.19</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>81.84</v>
+        <v>84.34</v>
       </c>
       <c r="K37" t="n">
-        <v>56.72</v>
+        <v>58.45</v>
       </c>
       <c r="L37" t="n">
-        <v>99.56999999999999</v>
+        <v>102.61</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>22.17</v>
+        <v>26.18</v>
       </c>
       <c r="K38" t="n">
-        <v>-62.52</v>
+        <v>-73.84</v>
       </c>
       <c r="L38" t="n">
-        <v>66.34</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-19.5</v>
+        <v>-22.82</v>
       </c>
       <c r="K39" t="n">
-        <v>15.04</v>
+        <v>17.61</v>
       </c>
       <c r="L39" t="n">
-        <v>24.63</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>77.04000000000001</v>
+        <v>78.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-95.48999999999999</v>
+        <v>-97.53</v>
       </c>
       <c r="L40" t="n">
-        <v>122.69</v>
+        <v>125.32</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>56.71</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-111.76</v>
+        <v>-131.14</v>
       </c>
       <c r="L41" t="n">
-        <v>125.32</v>
+        <v>147.06</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-95.42</v>
+        <v>-102.8</v>
       </c>
       <c r="K42" t="n">
-        <v>111.98</v>
+        <v>120.64</v>
       </c>
       <c r="L42" t="n">
-        <v>147.12</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-39.31</v>
+        <v>-46.3</v>
       </c>
       <c r="K43" t="n">
-        <v>116.99</v>
+        <v>137.81</v>
       </c>
       <c r="L43" t="n">
-        <v>123.42</v>
+        <v>145.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>61.57</v>
+        <v>54.03</v>
       </c>
       <c r="K44" t="n">
-        <v>10.26</v>
+        <v>9</v>
       </c>
       <c r="L44" t="n">
-        <v>62.42</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="45">
@@ -1945,10 +1945,10 @@
         <v>0.13</v>
       </c>
       <c r="K45" t="n">
-        <v>25.76</v>
+        <v>27.25</v>
       </c>
       <c r="L45" t="n">
-        <v>25.76</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-31.56</v>
+        <v>-28.22</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.62</v>
+        <v>-46.16</v>
       </c>
       <c r="L46" t="n">
-        <v>60.5</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>68.43000000000001</v>
+        <v>61.59</v>
       </c>
       <c r="K47" t="n">
-        <v>31.37</v>
+        <v>28.23</v>
       </c>
       <c r="L47" t="n">
-        <v>75.28</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-61.58</v>
+        <v>-58.05</v>
       </c>
       <c r="K48" t="n">
-        <v>26.75</v>
+        <v>25.22</v>
       </c>
       <c r="L48" t="n">
-        <v>67.14</v>
+        <v>63.29</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.29</v>
+        <v>-43.94</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.17</v>
+        <v>-14.38</v>
       </c>
       <c r="L49" t="n">
-        <v>45.55</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-80.01000000000001</v>
+        <v>-76.42</v>
       </c>
       <c r="K50" t="n">
-        <v>62.3</v>
+        <v>59.5</v>
       </c>
       <c r="L50" t="n">
-        <v>101.41</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="K51" t="n">
-        <v>118.95</v>
+        <v>113.47</v>
       </c>
       <c r="L51" t="n">
-        <v>119.03</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>42.58</v>
+        <v>42.22</v>
       </c>
       <c r="K52" t="n">
-        <v>89.17</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>98.81999999999999</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-13.13</v>
+        <v>-13.76</v>
       </c>
       <c r="K53" t="n">
-        <v>105.79</v>
+        <v>110.85</v>
       </c>
       <c r="L53" t="n">
-        <v>106.6</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-29.13</v>
+        <v>-30.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-94.04000000000001</v>
+        <v>-99.48999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>98.45</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-98.17</v>
+        <v>-104.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.05</v>
+        <v>-12.81</v>
       </c>
       <c r="L55" t="n">
-        <v>98.91</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>119.34</v>
+        <v>131.11</v>
       </c>
       <c r="K56" t="n">
-        <v>110.41</v>
+        <v>121.29</v>
       </c>
       <c r="L56" t="n">
-        <v>162.58</v>
+        <v>178.61</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-146.18</v>
+        <v>-154.46</v>
       </c>
       <c r="K57" t="n">
-        <v>-73.29000000000001</v>
+        <v>-77.44</v>
       </c>
       <c r="L57" t="n">
-        <v>163.52</v>
+        <v>172.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>103.17</v>
+        <v>112.17</v>
       </c>
       <c r="K58" t="n">
-        <v>-120.42</v>
+        <v>-130.92</v>
       </c>
       <c r="L58" t="n">
-        <v>158.57</v>
+        <v>172.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.94</v>
+        <v>-15.3</v>
       </c>
       <c r="K59" t="n">
-        <v>28.95</v>
+        <v>29.64</v>
       </c>
       <c r="L59" t="n">
-        <v>32.58</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>41.3</v>
+        <v>38.67</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.23</v>
+        <v>-24.56</v>
       </c>
       <c r="L60" t="n">
-        <v>48.92</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>45.87</v>
+        <v>42.87</v>
       </c>
       <c r="K61" t="n">
-        <v>12.8</v>
+        <v>11.96</v>
       </c>
       <c r="L61" t="n">
-        <v>47.62</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>22.47</v>
+        <v>21.18</v>
       </c>
       <c r="K62" t="n">
-        <v>-52.96</v>
+        <v>-49.91</v>
       </c>
       <c r="L62" t="n">
-        <v>57.53</v>
+        <v>54.22</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>13.34</v>
+        <v>11.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-68.67</v>
+        <v>-61.45</v>
       </c>
       <c r="L63" t="n">
-        <v>69.95</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.28</v>
+        <v>-25.76</v>
       </c>
       <c r="K64" t="n">
-        <v>59.6</v>
+        <v>54.29</v>
       </c>
       <c r="L64" t="n">
-        <v>65.97</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-75.8</v>
+        <v>-79.2</v>
       </c>
       <c r="K65" t="n">
-        <v>-19.47</v>
+        <v>-20.35</v>
       </c>
       <c r="L65" t="n">
-        <v>78.26000000000001</v>
+        <v>81.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-73.58</v>
+        <v>-75.16</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.96</v>
+        <v>-19.37</v>
       </c>
       <c r="L66" t="n">
-        <v>75.98999999999999</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.55</v>
+        <v>-3.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-66.28</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>66.38</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.54</v>
+        <v>-109.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-43.73</v>
+        <v>-44.25</v>
       </c>
       <c r="L68" t="n">
-        <v>117.02</v>
+        <v>118.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-51.47</v>
+        <v>-57.2</v>
       </c>
       <c r="K69" t="n">
-        <v>-65</v>
+        <v>-72.22</v>
       </c>
       <c r="L69" t="n">
-        <v>82.91</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="K70" t="n">
-        <v>-124.86</v>
+        <v>-124.72</v>
       </c>
       <c r="L70" t="n">
-        <v>125.28</v>
+        <v>125.14</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>109.91</v>
+        <v>121.08</v>
       </c>
       <c r="K71" t="n">
-        <v>105.86</v>
+        <v>116.62</v>
       </c>
       <c r="L71" t="n">
-        <v>152.6</v>
+        <v>168.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-109.73</v>
+        <v>-133.21</v>
       </c>
       <c r="K72" t="n">
-        <v>24.56</v>
+        <v>29.81</v>
       </c>
       <c r="L72" t="n">
-        <v>112.45</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>37.68</v>
+        <v>40.35</v>
       </c>
       <c r="K73" t="n">
-        <v>152.99</v>
+        <v>163.82</v>
       </c>
       <c r="L73" t="n">
-        <v>157.56</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-32.92</v>
+        <v>-34.07</v>
       </c>
       <c r="K74" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="L74" t="n">
-        <v>32.92</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-29.3</v>
+        <v>-27.53</v>
       </c>
       <c r="K75" t="n">
-        <v>29.98</v>
+        <v>28.17</v>
       </c>
       <c r="L75" t="n">
-        <v>41.92</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>48.52</v>
+        <v>44.24</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.14</v>
+        <v>-41.15</v>
       </c>
       <c r="L76" t="n">
-        <v>66.27</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.64</v>
+        <v>-11.24</v>
       </c>
       <c r="K77" t="n">
-        <v>55.2</v>
+        <v>53.32</v>
       </c>
       <c r="L77" t="n">
-        <v>56.41</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>28.95</v>
+        <v>27.56</v>
       </c>
       <c r="K78" t="n">
-        <v>52.82</v>
+        <v>50.28</v>
       </c>
       <c r="L78" t="n">
-        <v>60.23</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>64.40000000000001</v>
+        <v>61.74</v>
       </c>
       <c r="L79" t="n">
-        <v>64.41</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>58.69</v>
+        <v>64.22</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.11</v>
+        <v>-7.78</v>
       </c>
       <c r="L80" t="n">
-        <v>59.12</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>47.96</v>
+        <v>51.5</v>
       </c>
       <c r="K81" t="n">
-        <v>-31.26</v>
+        <v>-33.56</v>
       </c>
       <c r="L81" t="n">
-        <v>57.25</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.92</v>
+        <v>-45.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-88.70999999999999</v>
+        <v>-87.79000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>99.90000000000001</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-24.62</v>
+        <v>-24.53</v>
       </c>
       <c r="K83" t="n">
-        <v>151.62</v>
+        <v>151.08</v>
       </c>
       <c r="L83" t="n">
-        <v>153.61</v>
+        <v>153.06</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>6.42</v>
+        <v>7.36</v>
       </c>
       <c r="K84" t="n">
-        <v>76.98999999999999</v>
+        <v>88.22</v>
       </c>
       <c r="L84" t="n">
-        <v>77.26000000000001</v>
+        <v>88.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-93.17</v>
+        <v>-102.57</v>
       </c>
       <c r="K85" t="n">
-        <v>30.94</v>
+        <v>34.06</v>
       </c>
       <c r="L85" t="n">
-        <v>98.18000000000001</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-72.04000000000001</v>
+        <v>-84.42</v>
       </c>
       <c r="K86" t="n">
-        <v>116.68</v>
+        <v>136.73</v>
       </c>
       <c r="L86" t="n">
-        <v>137.13</v>
+        <v>160.69</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>111.47</v>
+        <v>128.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-65.04000000000001</v>
+        <v>-74.97</v>
       </c>
       <c r="L87" t="n">
-        <v>129.06</v>
+        <v>148.77</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>151.35</v>
+        <v>168.97</v>
       </c>
       <c r="K88" t="n">
-        <v>45.71</v>
+        <v>51.03</v>
       </c>
       <c r="L88" t="n">
-        <v>158.11</v>
+        <v>176.5</v>
       </c>
     </row>
   </sheetData>
